--- a/media/price_lists/electrocity.xlsx
+++ b/media/price_lists/electrocity.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D385"/>
+  <dimension ref="A1:D381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>156028.95</v>
+        <v>171645.05</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2079</v>
+        <v>2050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1225</v>
+        <v>1255</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38166</v>
+        <v>39502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>368800</v>
+        <v>405679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -601,4160 +601,4160 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01BUL00300</t>
+          <t>01MIL00310</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pelacables automático frontal p/cables de 0.25 a 6mm2 (BULIT)</t>
+          <t>Set de Puntas de Alto Impacto con Mango Kit x 12 Milwaukee 4832-4507</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18534</v>
+        <v>29917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pelacables-automatico-frontal-pcables-de-025-a-6mm2/</t>
+          <t>https://electrocity.com.ar/productos/set-de-puntas-de-alto-impacto-con-mango-kit-x-12-milwaukee-4832-4507/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01JAI00071</t>
+          <t>01BUL00300</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Soldador de estaño tipo lapiz 40w 220v (JA)</t>
+          <t>Pelacables automático frontal p/cables de 0.25 a 6mm2 (BULIT)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12102</v>
+        <v>19182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-40w-220v/</t>
+          <t>https://electrocity.com.ar/productos/pelacables-automatico-frontal-pcables-de-025-a-6mm2/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01VIY00055</t>
+          <t>01HRT09100</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica 15 mts 4mm viyilant</t>
+          <t>Multi Herramienta Plegable De Aluminio 18 En 1 MTT121 (BAHCO)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6350.4</v>
+        <v>34328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-15-mts-4mm-viyilant/</t>
+          <t>https://electrocity.com.ar/productos/multi-herramienta-plegable-de-aluminio-18-en-1-mtt121-bahco/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01JAI00060</t>
+          <t>01JAI00071</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EST7017 ESTAÑO EN TUBO 60/40 1MM 17GR -JA-</t>
+          <t>Soldador de estaño tipo lapiz 40w 220v (JA)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4547</v>
+        <v>11930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/est7017-estanio-en-tubo-6040-1mm-17gr-ja/</t>
+          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-40w-220v/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01MIL00122</t>
+          <t>01VIY00055</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caja Modular con Puerta Frontal Packout Milwaukee 4822-8445</t>
+          <t>Cinta pasacable plástica 15 mts 4mm viyilant</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>471655</v>
+        <v>6350.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/caja-modular-con-puerta-frontal-packout-milwaukee-4822-8445/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-15-mts-4mm-viyilant/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01HRT05128</t>
+          <t>01JAI00060</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Juego 2 Destornilladores Premium Blister P-3000/2h BAHCO</t>
+          <t>EST7017 ESTAÑO EN TUBO 60/40 1MM 17GR -JA-</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16335</v>
+        <v>4483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-2-destornilladores-premium-blister-p-3000-2h-bahco/</t>
+          <t>https://electrocity.com.ar/productos/est7017-estanio-en-tubo-6040-1mm-17gr-ja/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01JAI00402</t>
+          <t>01MIL00122</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Set herramientas 11 pzas aisladas 1000v c/valija (JA)</t>
+          <t>Caja Modular con Puerta Frontal Packout Milwaukee 4822-8445</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>61388</v>
+        <v>528254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-herramientas-11-pzas-aisladas-1000v-cvalija/</t>
+          <t>https://electrocity.com.ar/productos/caja-modular-con-puerta-frontal-packout-milwaukee-4822-8445/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01VIY00110</t>
+          <t>01HRT05128</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma acero ø4mm 20 metros</t>
+          <t>Juego 2 Destornilladores Premium Blister P-3000/2h BAHCO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20423</v>
+        <v>16335</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-20-metros/</t>
+          <t>https://electrocity.com.ar/productos/juego-2-destornilladores-premium-blister-p-3000-2h-bahco/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01MIL00614</t>
+          <t>01JAI00402</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Placa Compacta para Caja Packout Milwaukee 4822-8608</t>
+          <t>Set herramientas 11 pzas aisladas 1000v c/valija (JA)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>59732.2</v>
+        <v>60514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/placa-compacta-para-caja-packout-milwaukee-4822-8608-1sjqc/</t>
+          <t>https://electrocity.com.ar/productos/set-herramientas-11-pzas-aisladas-1000v-cvalija/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01BUL00080</t>
+          <t>01VIY00110</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Destornillador profesional #2x38mm punta phillips (BULIT)</t>
+          <t>Cinta pasacable plástica con alma acero ø4mm 20 metros</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9164</v>
+        <v>20423</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-2x38mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-20-metros/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01HRT06650</t>
+          <t>01MIL00614</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Punta de atornillar phillips 1/4 n°1 49mm p/taladro blister x 3unidades</t>
+          <t>Placa Compacta para Caja Packout Milwaukee 4822-8608</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7850</v>
+        <v>65711.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-de-atornillar-phillips-14-n1-49mm-ptaladro-blister-3unidades/</t>
+          <t>https://electrocity.com.ar/productos/placa-compacta-para-caja-packout-milwaukee-4822-8608-1sjqc/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01SEG08010</t>
+          <t>01BUL00080</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guante tactil nylon - poliuretano talle 8 (TACTIL)</t>
+          <t>Destornillador profesional #2x38mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2079</v>
+        <v>9485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/guante-tactil-nylon-poliuretano-talle-8/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-2x38mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01SIC06081</t>
+          <t>01HRT06650</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Destornillador buscapolo chico ø3 140mm 100/250 vca (SICA)</t>
+          <t>Punta de atornillar phillips 1/4 n°1 49mm p/taladro blister x 3unidades</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2398</v>
+        <v>7850</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-buscapolo-chico-3-140mm-100250-vca/</t>
+          <t>https://electrocity.com.ar/productos/punta-de-atornillar-phillips-14-n1-49mm-ptaladro-blister-3unidades/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01VIY00100</t>
+          <t>01SEG08010</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma acero ø4mm 10 metros</t>
+          <t>Guante tactil nylon - poliuretano talle 8 (TACTIL)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11630</v>
+        <v>2050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-10-metros/</t>
+          <t>https://electrocity.com.ar/productos/guante-tactil-nylon-poliuretano-talle-8/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01VIY00105</t>
+          <t>01SIC06081</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma acero ø4mm 15 metros</t>
+          <t>Destornillador buscapolo chico ø3 140mm 100/250 vca (SICA)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16000</v>
+        <v>2363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-15-metros/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-buscapolo-chico-3-140mm-100250-vca/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01BUL02480</t>
+          <t>01VIY00100</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DES BP A DESTORNILLADOR BUSCAPOLO AISLADO 140MM PLANO 100 A 500V (BULIT)</t>
+          <t>Cinta pasacable plástica con alma acero ø4mm 10 metros</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6453</v>
+        <v>11630</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/des-bp-a-destornillador-buscapolo-aislado-140mm-plano-100-a-500v/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-10-metros/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01HRT09050</t>
+          <t>01VIY00105</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pinza Alicate Corte Diagonal Bahco</t>
+          <t>Cinta pasacable plástica con alma acero ø4mm 15 metros</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23653</v>
+        <v>16000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-alicate-corte-diagonal-bahco/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-15-metros/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>01MIL00603</t>
+          <t>01BUL02480</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amoladora Inalámbrica Milwaukee 2880-20 M18 4 1/2</t>
+          <t>DES BP A DESTORNILLADOR BUSCAPOLO AISLADO 140MM PLANO 100 A 500V (BULIT)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1045619</v>
+        <v>6679</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/amoladora-inalambrica-milwaukee-2880-20-m18-4-1-2-wosid/</t>
+          <t>https://electrocity.com.ar/productos/des-bp-a-destornillador-buscapolo-aislado-140mm-plano-100-a-500v/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>01BUL00064</t>
+          <t>01MIL00624</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SET DE 6 DESTORNILLADORES AISLADOS 1000V PUNTA RECTA Y PHILLIPS (BULIT)</t>
+          <t>Combo Taladro Atornillador + Atornillador de Impacto M18 Milwaukee 2691-259A</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48129</v>
+        <v>1176739</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-aislados-1000v-punta-recta-y-phillips/</t>
+          <t>https://electrocity.com.ar/productos/combo-taladro-atornillador-atornillador-de-impacto-m18-milwaukee-2691-259a-sw3tn/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>01BUL00127</t>
+          <t>01MIL00636</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Set de llaves allen de 9 piezas en mm (BULIT)</t>
+          <t>Combo Taladro Percutor + Atornillador de Impacto M12 Milwaukee 2497-259A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>19713</v>
+        <v>1306642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-llaves-allen-de-9-piezas-en-mm/</t>
+          <t>https://electrocity.com.ar/productos/combo-taladro-percutor-atornillador-de-impacto-m12-milwaukee-2497-259a-14ceb/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01SIC06080</t>
+          <t>01HRT09050</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Destornillador buscapolo grande ø3.5 190mm 100/250 vca</t>
+          <t>Pinza Alicate Corte Diagonal Bahco</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3051</v>
+        <v>23653</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-buscapolo-grande-35-190mm-100250-vca/</t>
+          <t>https://electrocity.com.ar/productos/pinza-alicate-corte-diagonal-bahco/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01BAW11250</t>
+          <t>01MIL00603</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Multimetro Tester Digital BAW Medidor Display Led BAWm02</t>
+          <t>Amoladora Inalámbrica Milwaukee 2880-20 M18 4 1/2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18913</v>
+        <v>1165180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-tester-digital-baw-medidor-display-led-bawm02/</t>
+          <t>https://electrocity.com.ar/productos/amoladora-inalambrica-milwaukee-2880-20-m18-4-1-2-wosid/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>01JAI00076</t>
+          <t>01BUL00064</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BASE SOPORTE PARA SOLDADOR</t>
+          <t>SET DE 6 DESTORNILLADORES AISLADOS 1000V PUNTA RECTA Y PHILLIPS (BULIT)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7146</v>
+        <v>49814</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soporte-multiproposito-con-lupa-ja/</t>
+          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-aislados-1000v-punta-recta-y-phillips/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01MIL00040</t>
+          <t>01BUL00127</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TALADRO C/PERCUSION ATORNILLADOR 13MM 680W 220V 3000RPM MILWAUKEE 5374-59A</t>
+          <t>Set de llaves allen de 9 piezas en mm (BULIT)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>206685</v>
+        <v>20403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-cpercusion-atornillador-13mm-680w-220v-3000rpm-milwaukee-537459a/</t>
+          <t>https://electrocity.com.ar/productos/set-de-llaves-allen-de-9-piezas-en-mm/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>01MIL00601</t>
+          <t>01SIC06080</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ATORNILLADOR TALADRO MILWAUKEE 2606-20 M18 3MM 1800RPM</t>
+          <t>Destornillador buscapolo grande ø3.5 190mm 100/250 vca</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>615016</v>
+        <v>3008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/atornillador-taladro-sin-baterias-13mm-1800rpm-milwaukee-260620/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-buscapolo-grande-35-190mm-100250-vca/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>01MIL00609</t>
+          <t>01JAI00076</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Batería Compacta RedLithium 3.0 M12 Milwaukee 4811-2430</t>
+          <t>BASE SOPORTE PARA SOLDADOR</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>119469</v>
+        <v>7044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-compacta-redlithium-3-0-m12-milwaukee-4811-2430-1f8gs/</t>
+          <t>https://electrocity.com.ar/productos/soporte-multiproposito-con-lupa-ja/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01MIL00615</t>
+          <t>01MIL00040</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Placa de Pared Compacta Packout Milwaukee 4822-8496</t>
+          <t>TALADRO C/PERCUSION ATORNILLADOR 13MM 680W 220V 3000RPM MILWAUKEE 5374-59A</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>82078.39999999999</v>
+        <v>248041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/placa-de-pared-compacta-packout-milwaukee-4822-8496-1rr49/</t>
+          <t>https://electrocity.com.ar/productos/taladro-cpercusion-atornillador-13mm-680w-220v-3000rpm-milwaukee-537459a/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01MIL00212</t>
+          <t>01MIL00601</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bateria Milwaukee M18 De Litio 3.0 Ah 4811-1835</t>
+          <t>ATORNILLADOR TALADRO MILWAUKEE 2606-20 M18 3MM 1800RPM</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>207448</v>
+        <v>691499</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-milwaukee-m18-de-litio-3-0-ah-4811-1835-cyiny/</t>
+          <t>https://electrocity.com.ar/productos/atornillador-taladro-sin-baterias-13mm-1800rpm-milwaukee-260620/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01HRT09046</t>
+          <t>01MIL00609</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pinza Alicate Punta Plana Larga Bahco</t>
+          <t>Batería Compacta RedLithium 3.0 M12 Milwaukee 4811-2430</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>28983</v>
+        <v>131426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-alicate-punta-plana-larga-bahco/</t>
+          <t>https://electrocity.com.ar/productos/bateria-compacta-redlithium-3-0-m12-milwaukee-4811-2430-1f8gs/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01MIL00072</t>
+          <t>01MIL00615</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Atornillador Hexagonal 12v con Cargador y 2 Baterías Milwaukee 2401-259A</t>
+          <t>Placa de Pared Compacta Packout Milwaukee 4822-8496</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>431434</v>
+        <v>90294.39999999999</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/atornillador-hexagonal-12v-con-cargador-y-2-baterias-milwaukee-2401-259a/</t>
+          <t>https://electrocity.com.ar/productos/placa-de-pared-compacta-packout-milwaukee-4822-8496-1rr49/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>01MIL00607</t>
+          <t>01MIL00212</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ATORNILLADOR DE IMPACTO MILWAUKEE 3453-20 M12 FUEL</t>
+          <t>Bateria Milwaukee M18 De Litio 3.0 Ah 4811-1835</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>462796</v>
+        <v>232277</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/atornillador-de-impacto-milwaukee-3453-20-m12-fuel-137ol/</t>
+          <t>https://electrocity.com.ar/productos/bateria-milwaukee-m18-de-litio-3-0-ah-4811-1835-cyiny/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>01BUL00256</t>
+          <t>01HRT09046</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Martillo galponero con mango de goma (BULIT)</t>
+          <t>Pinza Alicate Punta Plana Larga Bahco</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25600</v>
+        <v>28983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/martillo-galponero-con-mango-de-goma/</t>
+          <t>https://electrocity.com.ar/productos/pinza-alicate-punta-plana-larga-bahco/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>01BUL00465</t>
+          <t>01MIL00072</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Repuesto hoja para cutter profesional grande ( x5 unidades )</t>
+          <t>Atornillador Hexagonal 12v con Cargador y 2 Baterías Milwaukee 2401-259A</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3188</v>
+        <v>474615</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/repuesto-hoja-para-cutter-profesional-grande-x5-unidades-/</t>
+          <t>https://electrocity.com.ar/productos/atornillador-hexagonal-12v-con-cargador-y-2-baterias-milwaukee-2401-259a/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>01BUL01650</t>
+          <t>01MIL00607</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Remachadora uso intensivo serie 500 bulit (BULIT)</t>
+          <t>ATORNILLADOR DE IMPACTO MILWAUKEE 3453-20 M12 FUEL</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>28410</v>
+        <v>518374</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/remachadora-uso-intensivo-serie-500-bulit/</t>
+          <t>https://electrocity.com.ar/productos/atornillador-de-impacto-milwaukee-3453-20-m12-fuel-137ol/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01BUL02266</t>
+          <t>01BUL00256</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pinza pta.sem.red. curva 6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Martillo galponero con mango de goma (BULIT)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12382</v>
+        <v>26496</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-ptasemred-curva-6-acerocarbono-serie-600-bulit/</t>
+          <t>https://electrocity.com.ar/productos/martillo-galponero-con-mango-de-goma/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01JAI00385</t>
+          <t>01BUL00465</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Set destornilladores 6 pzas 1000v aislados (JA)</t>
+          <t>Repuesto hoja para cutter profesional grande ( x5 unidades )</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21957</v>
+        <v>3299</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-destornilladores-6-pzas-1000v-aislados/</t>
+          <t>https://electrocity.com.ar/productos/repuesto-hoja-para-cutter-profesional-grande-x5-unidades-/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01SIC00090</t>
+          <t>01BUL01650</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pinza amperometrica digital con termocupla SICA</t>
+          <t>Remachadora uso intensivo serie 500 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>79722</v>
+        <v>29404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-con-termocupla-sica/</t>
+          <t>https://electrocity.com.ar/productos/remachadora-uso-intensivo-serie-500-bulit/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>01VIY00050</t>
+          <t>01BUL02266</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica 10 mts 4mm</t>
+          <t>Pinza pta.sem.red. curva 6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6241</v>
+        <v>12815</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-10-mts-4mm/</t>
+          <t>https://electrocity.com.ar/productos/pinza-ptasemred-curva-6-acerocarbono-serie-600-bulit/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>01JAI00306</t>
+          <t>01JAI00385</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TESTER MULTIMETRO DIGITAL PROFESIONAL 600CC/CA C/BUZZ. DIODO Y TRANS. S/BAT.9V -JA- (JA)</t>
+          <t>Set destornilladores 6 pzas 1000v aislados (JA)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15306</v>
+        <v>21644</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-profesional-600ccca-cbuzz-diodo-y-trans-sbat9v-ja/</t>
+          <t>https://electrocity.com.ar/productos/set-destornilladores-6-pzas-1000v-aislados/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>01MIL00210</t>
+          <t>01SIC00090</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BATERIA M18 18v 2Ah MILWAUKEE (MILWAUKEE)</t>
+          <t>Pinza amperometrica digital con termocupla SICA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>167913</v>
+        <v>78587</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-m18-18v-2ah-milwaukee/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-con-termocupla-sica/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01BUL00025</t>
+          <t>01VIY00050</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cinta metrica c/freno metálica 3mt. x 16mm (BULIT)</t>
+          <t>Cinta pasacable plástica 10 mts 4mm</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>13596</v>
+        <v>6241</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-cfreno-metalica-3mt-16mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-10-mts-4mm/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>01MIL00634</t>
+          <t>01JAI00306</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Taladro Atornillador M18 Milwaukee 2606-20</t>
+          <t>TESTER MULTIMETRO DIGITAL PROFESIONAL 600CC/CA C/BUZZ. DIODO Y TRANS. S/BAT.9V -JA- (JA)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>216757.5</v>
+        <v>15088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-atornillador-m18-milwaukee-2606-20-577re/</t>
+          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-profesional-600ccca-cbuzz-diodo-y-trans-sbat9v-ja/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01MIL00629</t>
+          <t>01MIL00210</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sierra Sable Inalámbrica Batería 12v Milwaukee 2420-259A</t>
+          <t>BATERIA M18 18v 2Ah MILWAUKEE (MILWAUKEE)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>446191.35</v>
+        <v>184719</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sierra-sable-inalambrica-bateria-12v-milwaukee-2420-259a-dc95c/</t>
+          <t>https://electrocity.com.ar/productos/bateria-m18-18v-2ah-milwaukee/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01MIL00211</t>
+          <t>01BUL00025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Batería M12 2ah Litio para Herramientas Milwaukee 4811-2420</t>
+          <t>Cinta metrica c/freno metálica 3mt. x 16mm (BULIT)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>89699.39999999999</v>
+        <v>12848</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-m12-2ah-litio-para-herramientas-milwaukee-4811-2420-va1z1/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-cfreno-metalica-3mt-16mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01HRT09026</t>
+          <t>01MIL00634</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pinza Universal Aislación 1000v Bahco</t>
+          <t>Taladro Atornillador M18 Milwaukee 2606-20</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>58800</v>
+        <v>238452</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-aislacion-1000v-bahco/</t>
+          <t>https://electrocity.com.ar/productos/taladro-atornillador-m18-milwaukee-2606-20-577re/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01HRT09016</t>
+          <t>01MIL00629</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kit Destornilladores x 5 Piezas 1000v Bahco 800IEC/5-RN</t>
+          <t>Sierra Sable Inalámbrica Batería 12v Milwaukee 2420-259A</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>63573</v>
+        <v>446191.35</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-destornilladores-x-5-piezas-1000v-bahco-800iec-5-rn/</t>
+          <t>https://electrocity.com.ar/productos/sierra-sable-inalambrica-bateria-12v-milwaukee-2420-259a-dc95c/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01MIL00350</t>
+          <t>01MIL00631</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Set de Destornilladores Premium 6 Piezas Milwaukee 4822-2706</t>
+          <t>Batería M12 XC 3Ah RedLithuim Milwaukee 4811-2402</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56393</v>
+        <v>128733.3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-destornilladores-premium-6-piezas-milwaukee-4822-2706/</t>
+          <t>https://electrocity.com.ar/productos/bateria-m12-xc-3ah-redlithuim-milwaukee-4811-2402-1fe5j/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01MIL00303</t>
+          <t>01MIL00211</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Punta Atornillador Phillips Impacto Ph2 x 50mm Kit x 5 Milwaukee 4832-4602</t>
+          <t>Batería M12 2ah Litio para Herramientas Milwaukee 4811-2420</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10802</v>
+        <v>89699.39999999999</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph2-x-50mm-kit-x-5-milwaukee-4832-4602/</t>
+          <t>https://electrocity.com.ar/productos/bateria-m12-2ah-litio-para-herramientas-milwaukee-4811-2420-va1z1/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01BUL00030</t>
+          <t>01HRT09026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mini arco de sierra 6 -serie 200- (BULIT)</t>
+          <t>Pinza Universal Aislación 1000v Bahco</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>14389</v>
+        <v>58800</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mini-arco-de-sierra-6-serie-200/</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-aislacion-1000v-bahco/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01BUL00456</t>
+          <t>01HRT09016</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cutter navaja con repuestos serie 600 (BULIT)</t>
+          <t>Kit Destornilladores x 5 Piezas 1000v Bahco 800IEC/5-RN</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23880</v>
+        <v>63573</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-navaja-con-repuestos-serie-600/</t>
+          <t>https://electrocity.com.ar/productos/kit-destornilladores-x-5-piezas-1000v-bahco-800iec-5-rn/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01BUL00464</t>
+          <t>01MIL00350</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hojas de repuesto p/cutter profesional serie 800 (BULIT)</t>
+          <t>Set de Destornilladores Premium 6 Piezas Milwaukee 4822-2706</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6371</v>
+        <v>62036</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/hojas-de-repuesto-pcutter-profesional-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/set-de-destornilladores-premium-6-piezas-milwaukee-4822-2706/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>01BUL00891</t>
+          <t>01MIL00303</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 segmentado 115mm bulit (BULIT)</t>
+          <t>Punta Atornillador Phillips Impacto Ph2 x 50mm Kit x 5 Milwaukee 4832-4602</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10639</v>
+        <v>11885</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-segmentado-115mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph2-x-50mm-kit-x-5-milwaukee-4832-4602/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>01BUL02170</t>
+          <t>01BUL00030</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Llave ajustable 6 cromada c/mango ergonomico antideslizante (BULIT)</t>
+          <t>Mini arco de sierra 6 -serie 200- (BULIT)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>17734</v>
+        <v>14892</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-ajustable-6-cromada-cmango-ergonomico-antideslizante/</t>
+          <t>https://electrocity.com.ar/productos/mini-arco-de-sierra-6-serie-200/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>01BUL02270</t>
+          <t>01BUL00456</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pinza pta. plana 6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Cutter navaja con repuestos serie 600 (BULIT)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15454</v>
+        <v>24716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pta-plana-6-acerocarbono-serie-600-bulit/</t>
+          <t>https://electrocity.com.ar/productos/cutter-navaja-con-repuestos-serie-600/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>01HRT05115</t>
+          <t>01BUL00464</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Destornillador phillips standard chico 6 x 75mm (BAHCO)</t>
+          <t>Hojas de repuesto p/cutter profesional serie 800 (BULIT)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6236</v>
+        <v>6594</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-phillips-standard-chico-6-75mm/</t>
+          <t>https://electrocity.com.ar/productos/hojas-de-repuesto-pcutter-profesional-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01HRT05610</t>
+          <t>01BUL00891</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø25 mm 1</t>
+          <t>Disco diamantado serie 400 segmentado 115mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>12475</v>
+        <v>10905</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-25-mm-1/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-segmentado-115mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01JAI00300</t>
+          <t>01BUL02170</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tester multimetro digital 750ca / 1000cc c/buzz. s/pila</t>
+          <t>Llave ajustable 6 cromada c/mango ergonomico antideslizante (BULIT)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8068</v>
+        <v>18355</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-750ca-1000cc-cbuzz-spila/</t>
+          <t>https://electrocity.com.ar/productos/llave-ajustable-6-cromada-cmango-ergonomico-antideslizante/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>01JAI00383</t>
+          <t>01BUL02270</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Set destornilladores 7 pzas 1000v aislados (JA)</t>
+          <t>Pinza pta. plana 6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38847</v>
+        <v>15995</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-destornilladores-7-pzas-1000v-aislados/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pta-plana-6-acerocarbono-serie-600-bulit/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01JAI01404</t>
+          <t>01HRT05115</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pinza crimpeadora metálica p/terminales aislados 0.5/6mm</t>
+          <t>Destornillador phillips standard chico 6 x 75mm (BAHCO)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37548</v>
+        <v>6236</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-metalica-pterminales-aislados-056mm/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-phillips-standard-chico-6-75mm/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>01JAI01420</t>
+          <t>01HRT05610</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pinza pelacable automatico universal 0.2/6mm c/cortacable -ja- (JA)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø25 mm 1</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>18839</v>
+        <v>12475</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pelacable-automatico-universal-026mm-ccortacable-ja/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-25-mm-1/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>01SIC00104</t>
+          <t>01JAI00300</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Detector indicador luminoso de voltaje catiii 70-1000vca (SICA)</t>
+          <t>Tester multimetro digital 750ca / 1000cc c/buzz. s/pila</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>23322</v>
+        <v>7953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/detector-indicador-luminoso-de-voltaje-catiii-701000vca/</t>
+          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-750ca-1000cc-cbuzz-spila/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>01BAW10950</t>
+          <t>01JAI00383</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Juego de puntas de prueba para tester (BAW)</t>
+          <t>Set destornilladores 7 pzas 1000v aislados (JA)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5064</v>
+        <v>38294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-de-puntas-de-prueba-para-tester/</t>
+          <t>https://electrocity.com.ar/productos/set-destornilladores-7-pzas-1000v-aislados/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>01BAW11282</t>
+          <t>01JAI01404</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SM852B SECUENCIMETRO COMPROBADOR DE ROTACION DE FASES BAW (BAW)</t>
+          <t>Pinza crimpeadora metálica p/terminales aislados 0.5/6mm</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>61175</v>
+        <v>37013</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sm852b-secuencimetro-comprobador-de-rotacion-de-fases-baw/</t>
+          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-metalica-pterminales-aislados-056mm/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>01BAW11285</t>
+          <t>01JAI01420</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TÉLEMETRO DIGITAL LASER DISTANCIA-AREA-VOLUMEN LCD BAWTL40M (BAW)</t>
+          <t>Pinza pelacable automatico universal 0.2/6mm c/cortacable -ja- (JA)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>74699</v>
+        <v>18571</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/telemetro-digital-laser-distanciaareavolumen-lcd-bawtl40m/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pelacable-automatico-universal-026mm-ccortacable-ja/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>01BUL02090</t>
+          <t>01SIC00104</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NVL S6 3B 40 A NIVEL 3 BURBUJAS 400MM ALUMINIO BULIT (BULIT)</t>
+          <t>Detector indicador luminoso de voltaje catiii 70-1000vca (SICA)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>26899</v>
+        <v>22990</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/nvl-s6-3b-40-a-nivel-3-burbujas-400mm-aluminio-bulit/</t>
+          <t>https://electrocity.com.ar/productos/detector-indicador-luminoso-de-voltaje-catiii-701000vca/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>01JAI00075</t>
+          <t>01BAW10950</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DESOLDADOR A PISTON METALICO CHICO JA (JA)</t>
+          <t>Juego de puntas de prueba para tester (BAW)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6626</v>
+        <v>4992</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/desoldador-a-piston-metalico-chico-ja/</t>
+          <t>https://electrocity.com.ar/productos/juego-de-puntas-de-prueba-para-tester/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>01BUL00028</t>
+          <t>01BAW11282</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cinta metrica doble freno metálica 7.5mt. x 25mm (BULIT)</t>
+          <t>SM852B SECUENCIMETRO COMPROBADOR DE ROTACION DE FASES BAW (BAW)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>36687</v>
+        <v>60304</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-doble-freno-metalica-75mt-25mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/sm852b-secuencimetro-comprobador-de-rotacion-de-fases-baw/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>01BUL00052</t>
+          <t>01BAW11285</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v phillips cromo-vanadio 2 x 150mm serie 800 (BULIT)</t>
+          <t>TÉLEMETRO DIGITAL LASER DISTANCIA-AREA-VOLUMEN LCD BAWTL40M (BAW)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9998</v>
+        <v>65965</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-phillips-cromovanadio-2-150mm-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/telemetro-digital-laser-distanciaareavolumen-lcd-bawtl40m/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>01MIL00635</t>
+          <t>01BUL02090</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Llave Criquet de Impacto 1/2" M12 Fuel Milwaukee 2565-20</t>
+          <t>NVL S6 3B 40 A NIVEL 3 BURBUJAS 400MM ALUMINIO BULIT (BULIT)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1496471</v>
+        <v>27841</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-criquet-de-impacto-1-2-m12-fuel-milwaukee-2565-20-uiat6/</t>
+          <t>https://electrocity.com.ar/productos/nvl-s6-3b-40-a-nivel-3-burbujas-400mm-aluminio-bulit/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>01MIL00213</t>
+          <t>01JAI00075</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Súper Cargador Simultáneo Doble Compartimento M18 Milwaukee 48-59-1859A</t>
+          <t>DESOLDADOR A PISTON METALICO CHICO JA (JA)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>667054.5</v>
+        <v>6532</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/super-cargador-simultaneo-doble-compartimento-m18-milwaukee-48-59-1859a-rf8s4/</t>
+          <t>https://electrocity.com.ar/productos/desoldador-a-piston-metalico-chico-ja/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>01MIL00613</t>
+          <t>01BUL00028</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Soporte para Baterías M18 Packout Milwaukee 4822-8603</t>
+          <t>Cinta metrica doble freno metálica 7.5mt. x 25mm (BULIT)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>56667.5</v>
+        <v>34669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soporte-para-baterias-m18-packout-milwaukee-4822-8603-1f31p/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-doble-freno-metalica-75mt-25mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>01BLO00026</t>
+          <t>01BUL00052</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bloqueador Eléctrico a Tornillo Universal Blook RTET600S-M</t>
+          <t>Destornillador aislado 1000v phillips cromo-vanadio 2 x 150mm serie 800 (BULIT)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>22916</v>
+        <v>10348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bloqueador-electrico-a-tornillo-universal-blook-rtet600s-m-h7v6u/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-phillips-cromovanadio-2-150mm-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>01HRT09076</t>
+          <t>01MIL00635</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Destornillador Perillero Phillips PH0 60 mm Bahco KR3000/50</t>
+          <t>Llave Criquet de Impacto 1/2" M12 Fuel Milwaukee 2565-20</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5912</v>
+        <v>996042</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-perillero-phillips-ph0-60-mm-bahco-kr3000-50/</t>
+          <t>https://electrocity.com.ar/productos/llave-criquet-de-impacto-1-2-m12-fuel-milwaukee-2565-20-uiat6/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>01MIL00304</t>
+          <t>01MIL00213</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Punta Atornillador Phillips Impacto Ph3 x 25mm Kit x 2 Milwaukee 4832-4413</t>
+          <t>Súper Cargador Simultáneo Doble Compartimento M18 Milwaukee 48-59-1859A</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2937</v>
+        <v>667054.5</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph3-x-25mm-kit-x-2-milwaukee-4832-4413/</t>
+          <t>https://electrocity.com.ar/productos/super-cargador-simultaneo-doble-compartimento-m18-milwaukee-48-59-1859a-rf8s4/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>01MIL00064</t>
+          <t>01MIL00613</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TALADRO PERCUTOR 12V C/CARGADOR + 2 BATERIAS MILWAUKEE 2408-259A</t>
+          <t>Soporte para Baterías M18 Packout Milwaukee 4822-8603</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>570225</v>
+        <v>62339</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-percutor-12v-c-cargador-2-baterias-milwaukee-2408-259a/</t>
+          <t>https://electrocity.com.ar/productos/soporte-para-baterias-m18-packout-milwaukee-4822-8603-1f31p/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01HRT05126</t>
+          <t>01BLO00026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Juego Destornilladores 12 Piezas 3000/12h (BAHCO)</t>
+          <t>Bloqueador Eléctrico a Tornillo Universal Blook RTET600S-M</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>81079</v>
+        <v>22590</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-destornilladores-12-piezas-3000-12h-bahco/</t>
+          <t>https://electrocity.com.ar/productos/bloqueador-electrico-a-tornillo-universal-blook-rtet600s-m-h7v6u/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>01BUL00063</t>
+          <t>01HRT09076</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SET DE 3 DESTORNILLADORES AISLADOS 1000V PUNTA RECTA (BULIT)</t>
+          <t>Destornillador Perillero Phillips PH0 60 mm Bahco KR3000/50</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>23776</v>
+        <v>5912</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-3-destornilladores-aislados-1000v-punta-recta/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-perillero-phillips-ph0-60-mm-bahco-kr3000-50/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>01BUL00074</t>
+          <t>01HRT09020</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Destornillador profesional #0x75mm punta phillips (BULIT)</t>
+          <t>Pinza Alicate 7 Aislación 1000v Bahco 2151S-7A-RN</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4671</v>
+        <v>75834</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-0x75mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/pinza-alicate-7-aislacion-1000v-bahco-2151s-7a-rn/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>01BUL00082</t>
+          <t>01MIL00304</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Destornillador profesional #1x300mm punta phillips (BULIT)</t>
+          <t>Punta Atornillador Phillips Impacto Ph3 x 25mm Kit x 2 Milwaukee 4832-4413</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9256</v>
+        <v>3231</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-1x300mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph3-x-25mm-kit-x-2-milwaukee-4832-4413/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01BUL00100</t>
+          <t>01MIL00302</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Destornillador profesional #6x150mm punta plana (BULIT)</t>
+          <t>Punta Atornillador Phillips Impacto Ph2 x 25mm Kit x 5 Milwaukee 4832-4601</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11168</v>
+        <v>6111</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-6x150mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph2-x-25mm-kit-x-5-milwaukee-4832-4601/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>01BUL00128</t>
+          <t>01MIL00064</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Set de llaves allen de 9 piezas en pulgadas (BULIT)</t>
+          <t>TALADRO PERCUTOR 12V C/CARGADOR + 2 BATERIAS MILWAUKEE 2408-259A</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>19713</v>
+        <v>627298</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-llaves-allen-de-9-piezas-en-pulgadas/</t>
+          <t>https://electrocity.com.ar/productos/taladro-percutor-12v-c-cargador-2-baterias-milwaukee-2408-259a/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>01BUL00694</t>
+          <t>01HRT05126</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Alicate de corte frontal de precision de 45 p/artesanias y electrónica (BULIT)</t>
+          <t>Juego Destornilladores 12 Piezas 3000/12h (BAHCO)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10913</v>
+        <v>81079</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/alicate-de-corte-frontal-de-precision-de-45-partesanias-y-electronica/</t>
+          <t>https://electrocity.com.ar/productos/juego-destornilladores-12-piezas-3000-12h-bahco/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>01BUL00780</t>
+          <t>01BUL00063</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pinza pico de loro profesional de 10 serie 700 (BULIT)</t>
+          <t>SET DE 3 DESTORNILLADORES AISLADOS 1000V PUNTA RECTA (BULIT)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>32652</v>
+        <v>24608</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pico-de-loro-profesional-de-10-serie-700/</t>
+          <t>https://electrocity.com.ar/productos/set-de-3-destornilladores-aislados-1000v-punta-recta/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>01BUL00782</t>
+          <t>01BUL00074</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pinza pico de loro cromada acero 6 (BULIT)</t>
+          <t>Destornillador profesional #0x75mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17828</v>
+        <v>4834</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pico-de-loro-cromada-acero-6/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-0x75mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>01BUL00808</t>
+          <t>01BUL00082</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pistola encoladora dosificadora de pegamento 30w profesional (SUPRABOND)</t>
+          <t>Destornillador profesional #1x300mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>72266</v>
+        <v>9580</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-encoladora-dosificadora-de-pegamento-30w-profesional/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-1x300mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>01BUL00810</t>
+          <t>01BUL00100</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pistola dosificadora de pegamento 40w 220v c/pico aislante (SUPRABOND)</t>
+          <t>Destornillador profesional #6x150mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>29156</v>
+        <v>11559</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-dosificadora-de-pegamento-40w-220v-cpico-aislante/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-6x150mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>01BUL00892</t>
+          <t>01BUL00128</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 turbo 115mm bulit (BULIT)</t>
+          <t>Set de llaves allen de 9 piezas en pulgadas (BULIT)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12575</v>
+        <v>20403</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-115mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/set-de-llaves-allen-de-9-piezas-en-pulgadas/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>01BUL01625</t>
+          <t>01BUL00694</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KIT 3 LIMAS DE 8 ENTREFINAS ACERO FORJADO PLANA + REDONDA + MEDIA CAÑA MANGO ERGONOMICO</t>
+          <t>Alicate de corte frontal de precision de 45 p/artesanias y electrónica (BULIT)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>46363</v>
+        <v>11295</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-3-limas-de-8-entrefinas-acero-forjado-plana-redonda-media-cania-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/alicate-de-corte-frontal-de-precision-de-45-partesanias-y-electronica/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>01BUL01720</t>
+          <t>01BUL00780</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Llave p/caños con mordazas 1 c/tope seguridad</t>
+          <t>Pinza pico de loro profesional de 10 serie 700 (BULIT)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>31816</v>
+        <v>33794</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-pcanios-con-mordazas-1-ctope-seguridad/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pico-de-loro-profesional-de-10-serie-700/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>01BUL02068</t>
+          <t>01BUL00782</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kit llaves criquet juego de 5 llaves c/20 medidas serie 700 (BULIT)</t>
+          <t>Pinza pico de loro cromada acero 6 (BULIT)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>69863.39999999999</v>
+        <v>18452</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-llaves-criquet-juego-de-5-llaves-c20-medidas-serie-700/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pico-de-loro-cromada-acero-6/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>01EXP00001</t>
+          <t>01BUL00808</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 10 metros c/porta-pasacable</t>
+          <t>Pistola encoladora dosificadora de pegamento 30w profesional (SUPRABOND)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>53857</v>
+        <v>74796</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-10-metros-cportapasacable/</t>
+          <t>https://electrocity.com.ar/productos/pistola-encoladora-dosificadora-de-pegamento-30w-profesional/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>01HRT04715</t>
+          <t>01BUL00810</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pinza semi-automatica p/terminales desnudos hasta 10mm</t>
+          <t>Pistola dosificadora de pegamento 40w 220v c/pico aislante (SUPRABOND)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>165398</v>
+        <v>30176</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-semiautomatica-pterminales-desnudos-hasta-10mm/</t>
+          <t>https://electrocity.com.ar/productos/pistola-dosificadora-de-pegamento-40w-220v-cpico-aislante/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>01HRT05106</t>
+          <t>01BUL00892</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Destornillador plano standard chico 6.5 x 150mm (BAHCO)</t>
+          <t>Disco diamantado serie 400 turbo 115mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>7567</v>
+        <v>12890</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-plano-standard-chico-65-150mm/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-115mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>01HRT05110</t>
+          <t>01BUL01625</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Destornillador phillips standard chico 3 x 75mm (BAHCO)</t>
+          <t>KIT 3 LIMAS DE 8 ENTREFINAS ACERO FORJADO PLANA + REDONDA + MEDIA CAÑA MANGO ERGONOMICO</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6236</v>
+        <v>47986</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-phillips-standard-chico-3-75mm/</t>
+          <t>https://electrocity.com.ar/productos/kit-3-limas-de-8-entrefinas-acero-forjado-plana-redonda-media-cania-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>01HRT05600</t>
+          <t>01BUL01720</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sierra copa bimetálica traspasadora hss ø19mm 3/4</t>
+          <t>Llave p/caños con mordazas 1 c/tope seguridad</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>9778</v>
+        <v>32930</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sierra-copa-bimetalica-traspasadora-hss-19mm-34/</t>
+          <t>https://electrocity.com.ar/productos/llave-pcanios-con-mordazas-1-ctope-seguridad/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>01HRT05605</t>
+          <t>01BUL02068</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø22mm 7/8</t>
+          <t>Kit llaves criquet juego de 5 llaves c/20 medidas serie 700 (BULIT)</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>11126</v>
+        <v>72308.7</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-22mm-78/</t>
+          <t>https://electrocity.com.ar/productos/kit-llaves-criquet-juego-de-5-llaves-c20-medidas-serie-700/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>01HRT05625</t>
+          <t>01EXP00001</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø51mm 2</t>
+          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 10 metros c/porta-pasacable</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>24359</v>
+        <v>53857</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-51mm-2/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-10-metros-cportapasacable/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>01HRT05628</t>
+          <t>01HRT04715</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø79mm 3 1/8</t>
+          <t>Pinza semi-automatica p/terminales desnudos hasta 10mm</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>37509</v>
+        <v>163043</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-79mm-3-18/</t>
+          <t>https://electrocity.com.ar/productos/pinza-semiautomatica-pterminales-desnudos-hasta-10mm/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01HRT05630</t>
+          <t>01HRT05105</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Soporte para sierra de copa bimtalica traspasadora de 14 a 30mm 3/8 (SIN-PAR)</t>
+          <t>Destornillador plano standard chico 5.5 x 125mm (BAHCO)</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>21494</v>
+        <v>7567</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soporte-para-sierra-de-copa-bimtalica-traspasadora-de-14-a-30mm-38/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-plano-standard-chico-55-125mm/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01HRT05635</t>
+          <t>01HRT05106</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Soporte para sierra de copa bimtalica traspasadora de 33 a 152mm 1/2 (IMPORTADO)</t>
+          <t>Destornillador plano standard chico 6.5 x 150mm (BAHCO)</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>28237</v>
+        <v>7567</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soporte-para-sierra-de-copa-bimtalica-traspasadora-de-33-a-152mm-12/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-plano-standard-chico-65-150mm/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01INS00015</t>
+          <t>01HRT05110</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Multimetro digital 600v + frecuencia + diodo fluke-107 esp (FLUKE)</t>
+          <t>Destornillador phillips standard chico 3 x 75mm (BAHCO)</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>530293</v>
+        <v>6236</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-digital-600v-frecuencia-diodo-fluke107-esp/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-phillips-standard-chico-3-75mm/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>01INS00280</t>
+          <t>01HRT05600</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Detector comprobador electronico luminoso sonoro 90/1000v 1ac-a1-ii-5pk (FLUKE)</t>
+          <t>Sierra copa bimetálica traspasadora hss ø19mm 3/4</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>137590</v>
+        <v>9778</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/detector-comprobador-electronico-luminoso-sonoro-901000v-1aca1ii5pk/</t>
+          <t>https://electrocity.com.ar/productos/sierra-copa-bimetalica-traspasadora-hss-19mm-34/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01JAI00072</t>
+          <t>01HRT05625</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Soldador de estaño tipo lapiz 60w 220v (JA)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø51mm 2</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>13229</v>
+        <v>24359</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-60w-220v/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-51mm-2/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>01RED04062</t>
+          <t>01HRT05628</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø10MM 160MM LARGO</t>
+          <t>Mecha copa bimetálica traspasadora hss ø79mm 3 1/8</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6514</v>
+        <v>37509</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-10mm-160mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-79mm-3-18/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>01RED04064</t>
+          <t>01HRT05630</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø12MM 160MM LARGO</t>
+          <t>Soporte para sierra de copa bimtalica traspasadora de 14 a 30mm 3/8 (SIN-PAR)</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>9086</v>
+        <v>21494</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-12mm-160mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/soporte-para-sierra-de-copa-bimtalica-traspasadora-de-14-a-30mm-38/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>01RED04066</t>
+          <t>01HRT05635</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø20MM 460MM LARGO</t>
+          <t>Soporte para sierra de copa bimtalica traspasadora de 33 a 152mm 1/2 (IMPORTADO)</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>45097</v>
+        <v>28237</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-20mm-460mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/soporte-para-sierra-de-copa-bimtalica-traspasadora-de-33-a-152mm-12/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>01SIC00091</t>
+          <t>01INS00015</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Multimetro digital 600v con termocupla SICA</t>
+          <t>Multimetro digital 600v + frecuencia + diodo fluke-107 esp (FLUKE)</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>41393</v>
+        <v>523386</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-digital-600v-con-termocupla-sica/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-digital-600v-frecuencia-diodo-fluke107-esp/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01SIC00100</t>
+          <t>01INS00280</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Detector 3 en 1 - detección de tabiques metal y tensión- SICA</t>
+          <t>Detector comprobador electronico luminoso sonoro 90/1000v 1ac-a1-ii-5pk (FLUKE)</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>45327</v>
+        <v>135797</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/detector-3-en-1-deteccion-de-tabiques-metal-y-tension-sica/</t>
+          <t>https://electrocity.com.ar/productos/detector-comprobador-electronico-luminoso-sonoro-901000v-1aca1ii5pk/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01TOO01020</t>
+          <t>01JAI00072</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Porta-herramientas cartuchera p/electricistas grande</t>
+          <t>Soldador de estaño tipo lapiz 60w 220v (JA)</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>47025</v>
+        <v>13041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-grande/</t>
+          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-60w-220v/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>01TOO01092</t>
+          <t>01RED04062</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Porta-herramientas cartuchera p/electricistas mediano (TOOLMEN)</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø10MM 160MM LARGO</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>31572</v>
+        <v>6514</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-mediano/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-10mm-160mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>01TOO01093</t>
+          <t>01RED04064</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Porta herramientas electricista super (TOOLMEN)</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø12MM 160MM LARGO</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>60146</v>
+        <v>9086</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/porta-herramientas-electricista-super/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-12mm-160mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>01TOO01110</t>
+          <t>01RED04066</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Porta taladro - atornilladora - cartuchera durlock (TOOLMEN)</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø20MM 460MM LARGO</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>26279</v>
+        <v>45097</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/porta-taladro-atornilladora-cartuchera-durlock/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-20mm-460mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>01USH00030</t>
+          <t>01SIC00091</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dobladora de caños tipo tijera dos palancas para caños 5/8" 3/4" 7/8"</t>
+          <t>Multimetro digital 600v con termocupla SICA</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>350656</v>
+        <v>40804</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/dobladora-de-canios-tipo-tijera-dos-palancas-para-canios-58-34-78/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-digital-600v-con-termocupla-sica/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>01VIY00015</t>
+          <t>01SIC00100</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cinta pasacable nylon ø4mm resistencia 165kgf 15 metros</t>
+          <t>Detector 3 en 1 - detección de tabiques metal y tensión- SICA</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>31012</v>
+        <v>44681</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-nylon-4mm-resistencia-165kgf-15-metros/</t>
+          <t>https://electrocity.com.ar/productos/detector-3-en-1-deteccion-de-tabiques-metal-y-tension-sica/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>01VIY00115</t>
+          <t>01TOO01020</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma acero ø4mm 30 metros</t>
+          <t>Porta-herramientas cartuchera p/electricistas grande</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>29332</v>
+        <v>47025</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-30-metros/</t>
+          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-grande/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>01VIY00205</t>
+          <t>01TOO01092</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cinta pasacable poliester ø5mm resistencia 150kgf 15 metros</t>
+          <t>Porta-herramientas cartuchera p/electricistas mediano (TOOLMEN)</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>52390</v>
+        <v>31572</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-poliester-5mm-resistencia-150kgf-15-metros/</t>
+          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-mediano/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>01BAW06037</t>
+          <t>01TOO01093</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Multimetro multirrango manual 600vcc/vca (BAW)</t>
+          <t>Porta herramientas electricista super (TOOLMEN)</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>32715</v>
+        <v>60146</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-600vccvca/</t>
+          <t>https://electrocity.com.ar/productos/porta-herramientas-electricista-super/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>01BAW06044</t>
+          <t>01TOO01110</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Meghometro digital hasta 1000v / 2 g ohms + display lcd</t>
+          <t>Porta taladro - atornilladora - cartuchera durlock (TOOLMEN)</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>210867</v>
+        <v>26279</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/meghometro-digital-hasta-1000v-2-g-ohms-display-lcd/</t>
+          <t>https://electrocity.com.ar/productos/porta-taladro-atornilladora-cartuchera-durlock/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>01RED04121</t>
+          <t>01USH00030</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MECHA ACERO RAPIDO Ø 8MM EZETA</t>
+          <t>Dobladora de caños tipo tijera dos palancas para caños 5/8" 3/4" 7/8"</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10574</v>
+        <v>380061</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-8mm-ezeta/</t>
+          <t>https://electrocity.com.ar/productos/dobladora-de-canios-tipo-tijera-dos-palancas-para-canios-58-34-78/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>01RED04101</t>
+          <t>01USH00040</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MECHA ACERO RAPIDO Ø 3MM EZETA</t>
+          <t>Dobladora de caños 7/8" y 1" con trípode y resorte adaptador para caños 3/4"</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3600</v>
+        <v>649475</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-3mm-ezeta/</t>
+          <t>https://electrocity.com.ar/productos/dobladora-de-canios-78-y-1-con-tripode-y-resorte-adaptador-para-canios-34/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>01BUL00041</t>
+          <t>01VIY00015</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ENGRAMPADORA USO INTENSIVO P/6MM-8MM BULIT (BULIT)</t>
+          <t>Cinta pasacable nylon ø4mm resistencia 165kgf 15 metros</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>39089</v>
+        <v>31012</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/engrampadora-uso-intensivo-p6mm8mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-nylon-4mm-resistencia-165kgf-15-metros/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>01JAI00074</t>
+          <t>01VIY00115</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SOLDADOR PUNTA CHANFLE TIPO LAPIZ 100W 220V PREMIUN -JA-</t>
+          <t>Cinta pasacable plástica con alma acero ø4mm 30 metros</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>25059</v>
+        <v>29332</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-punta-chanfle-tipo-lapiz-100w-220v-premiun-ja/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-30-metros/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>01BUL00698</t>
+          <t>01VIY00205</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SET DE 5 PINZAS DE 4.5" + ESTUCHE BORDADO BULIT PZA S6 SET PRE</t>
+          <t>Cinta pasacable poliester ø5mm resistencia 150kgf 15 metros</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>52764</v>
+        <v>52390</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-5-pinzas-de-45-estuche-bordado-bulit-pza-s6-set-pre/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-poliester-5mm-resistencia-150kgf-15-metros/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>01MIL00300</t>
+          <t>01BAW06037</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Punta Shockwave Impact Phillips Ph1 X 5 Milwaukee 4832-4661 (MILWAUKEE)</t>
+          <t>Multimetro multirrango manual 600vcc/vca (BAW)</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5436</v>
+        <v>32249</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-shockwave-impact-phillips-ph1-5-milwaukee-48324661/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-600vccvca/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>01BAW06033</t>
+          <t>01BAW06044</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 400aca 600vca/cc 200k (BAW)</t>
+          <t>Meghometro digital hasta 1000v / 2 g ohms + display lcd</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>17571</v>
+        <v>186588</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-400aca-600vcacc-200k-baw/</t>
+          <t>https://electrocity.com.ar/productos/meghometro-digital-hasta-1000v-2-g-ohms-display-lcd/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01BUL00026</t>
+          <t>01RED04121</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cinta metrica c/freno metálica 5mt. x 19mm (BULIT)</t>
+          <t>MECHA ACERO RAPIDO Ø 8MM EZETA</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>22576</v>
+        <v>10574</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-cfreno-metalica-5mt-19mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-8mm-ezeta/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>01BUL00053</t>
+          <t>01RED04101</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v punta phillips #0 x 75mm (BULIT)</t>
+          <t>MECHA ACERO RAPIDO Ø 3MM EZETA</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6332</v>
+        <v>3600</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-punta-phillips-0-75mm/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-3mm-ezeta/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>01BUL00054</t>
+          <t>01BUL00041</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v punta phillips #1 x 100mm (BULIT)</t>
+          <t>ENGRAMPADORA USO INTENSIVO P/6MM-8MM BULIT (BULIT)</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8024</v>
+        <v>40457</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-punta-phillips-1-100mm/</t>
+          <t>https://electrocity.com.ar/productos/engrampadora-uso-intensivo-p6mm8mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>01BUL00126</t>
+          <t>01JAI00074</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Set de llaves torx de 9 piezas (BULIT)</t>
+          <t>SOLDADOR PUNTA CHANFLE TIPO LAPIZ 100W 220V PREMIUN -JA-</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>19713</v>
+        <v>24702</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-llaves-torde-9-piezas/</t>
+          <t>https://electrocity.com.ar/productos/soldador-punta-chanfle-tipo-lapiz-100w-220v-premiun-ja/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>01BUL00463</t>
+          <t>01BUL00698</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Cutter profesional grande metalico p/corte de fuerza (BULIT)</t>
+          <t>SET DE 5 PINZAS DE 4.5" + ESTUCHE BORDADO BULIT PZA S6 SET PRE</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>20272</v>
+        <v>54611</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-profesional-grande-metalico-pcorte-de-fuerza/</t>
+          <t>https://electrocity.com.ar/productos/set-de-5-pinzas-de-45-estuche-bordado-bulit-pza-s6-set-pre/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>01BUL01985</t>
+          <t>01MIL00300</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Juego 8 destornilladores philips y plano aislados 1000v + mango + linterna +estuche (BULIT)</t>
+          <t>Punta Shockwave Impact Phillips Ph1 X 5 Milwaukee 4832-4661 (MILWAUKEE)</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>63894</v>
+        <v>5978</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-8-destornilladores-philips-y-plano-aislados-1000v-mango-linterna-estuche/</t>
+          <t>https://electrocity.com.ar/productos/punta-shockwave-impact-phillips-ph1-5-milwaukee-48324661/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>01MIL00633</t>
+          <t>01BAW06033</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Pistola Aplicadora para Silicona M18 Milwaukee 2641-159A</t>
+          <t>Pinza amperometrica 400aca 600vca/cc 200k (BAW)</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>791171.5</v>
+        <v>15353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-aplicadora-para-silicona-m18-milwaukee-2641-159a-1wha8/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-400aca-600vcacc-200k-baw/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>01MIL00012</t>
+          <t>01BUL00026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Amoladora Gatillo Doble M18 Fuel One Key 5" Milwaukee 2986-20</t>
+          <t>Cinta metrica c/freno metálica 5mt. x 19mm (BULIT)</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>924015.6</v>
+        <v>21334</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/amoladora-gatillo-doble-m18-fuel-one-key-5-milwaukee-2986-20-1phqz/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-cfreno-metalica-5mt-19mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>01MIL00630</t>
+          <t>01BUL00053</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Batería M12 RedLithium CP1.5 Ah Milwaukee 4811-2401</t>
+          <t>Destornillador aislado 1000v punta phillips #0 x 75mm (BULIT)</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>64541.35</v>
+        <v>6553</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-m12-redlithium-cp1-5-ah-milwaukee-4811-2401-tjhq2/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-punta-phillips-0-75mm/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>01MIL00628</t>
+          <t>01BUL00054</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rotomartillo SDS Max 1100W 3 Modos Milwaukee 5317-59A</t>
+          <t>Destornillador aislado 1000v punta phillips #1 x 100mm (BULIT)</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1165662</v>
+        <v>8305</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/rotomartillo-sds-max-1100w-3-modos-milwaukee-5317-59a-i5xat/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-punta-phillips-1-100mm/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>01MIL00627</t>
+          <t>01BUL00126</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Amoladora Angular 115mm 1550w Velocidad Variable Milwaukee 6117-59A</t>
+          <t>Set de llaves torx de 9 piezas (BULIT)</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>375924.4</v>
+        <v>20403</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/amoladora-angular-115mm-1550w-velocidad-variable-milwaukee-6117-59a-10u5a/</t>
+          <t>https://electrocity.com.ar/productos/set-de-llaves-torde-9-piezas/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>01MIL00616</t>
+          <t>01BUL00463</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Taladro Rotopercutor SDS Bateria M18 Fuel Milwaukee 2717-20 M18</t>
+          <t>Cutter profesional grande metalico p/corte de fuerza (BULIT)</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1274348.05</v>
+        <v>20272</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-rotopercutor-sds-bateria-m18-fuel-milwaukee-2717-20-m18-r9smp/</t>
+          <t>https://electrocity.com.ar/productos/cutter-profesional-grande-metalico-pcorte-de-fuerza/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01BUL00805</t>
+          <t>01BUL01985</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Pistola Encoladora Inalámbrica 10w con Base y Cable USB Suprabond C PHX B10</t>
+          <t>Juego 8 destornilladores philips y plano aislados 1000v + mango + linterna +estuche (BULIT)</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>75954</v>
+        <v>66130</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-encoladora-inalambrica-10w-con-base-y-cable-usb-suprabond-c-phx-b10-z9nj7/</t>
+          <t>https://electrocity.com.ar/productos/juego-8-destornilladores-philips-y-plano-aislados-1000v-mango-linterna-estuche/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01BLO00032</t>
+          <t>01MIL00633</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Bloqueador de Térmica Bipolar Transparente E2 Blook ELE-2111</t>
+          <t>Pistola Aplicadora para Silicona M18 Milwaukee 2641-159A</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>41036</v>
+        <v>870358.35</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bloqueador-de-termica-bipolar-transparente-e2-blook-ele-2111-rdbhj/</t>
+          <t>https://electrocity.com.ar/productos/pistola-aplicadora-para-silicona-m18-milwaukee-2641-159a-1wha8/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01BLO00024</t>
+          <t>01MIL00012</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Bloqueador Eléctrico Rojo a Tornillo Bioseif ELE-1140</t>
+          <t>Amoladora Gatillo Doble M18 Fuel One Key 5" Milwaukee 2986-20</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>34197</v>
+        <v>924015.6</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bloqueador-electrico-rojo-a-tornillo-bioseif-ele-1140-ubvdp/</t>
+          <t>https://electrocity.com.ar/productos/amoladora-gatillo-doble-m18-fuel-one-key-5-milwaukee-2986-20-1phqz/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01ZOL04207</t>
+          <t>01MIL00630</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Pinza Crimpeadora Terminales Tiff para Cables 0.25 a 10mm Zoloda CRIMP-10</t>
+          <t>Batería M12 RedLithium CP1.5 Ah Milwaukee 4811-2401</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>157717</v>
+        <v>64541.35</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-terminales-tiff-para-cables-0-25-a-10mm-zoloda-crimp-10-sqxcn/</t>
+          <t>https://electrocity.com.ar/productos/bateria-m12-redlithium-cp1-5-ah-milwaukee-4811-2401-tjhq2/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01JAI01424</t>
+          <t>01MIL00628</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Pinza Pelacable Redondo hasta 240 mm de Diámetro Ja PZC5360</t>
+          <t>Rotomartillo SDS Max 1100W 3 Modos Milwaukee 5317-59A</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>194235</v>
+        <v>1174987.8</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pelacable-redondo-hasta-240-mm-de-diametro-ja-pzc5360/</t>
+          <t>https://electrocity.com.ar/productos/rotomartillo-sds-max-1100w-3-modos-milwaukee-5317-59a-i5xat/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>01JAI00304</t>
+          <t>01MIL00627</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Tester Multimetro Digital Compacto Ja INT0033</t>
+          <t>Amoladora Angular 115mm 1550w Velocidad Variable Milwaukee 6117-59A</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>19577</v>
+        <v>389112.15</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-compacto-ja-int0033/</t>
+          <t>https://electrocity.com.ar/productos/amoladora-angular-115mm-1550w-velocidad-variable-milwaukee-6117-59a-10u5a/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01BAW06047</t>
+          <t>01MIL00616</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Termómetro Infrarrojo Láser +800°C Baw RM800PRO</t>
+          <t>Taladro Rotopercutor SDS Bateria M18 Fuel Milwaukee 2717-20 M18</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>93725</v>
+        <v>1274348.05</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/termometro-infrarrojo-laser-800c-baw-rm800pro/</t>
+          <t>https://electrocity.com.ar/productos/taladro-rotopercutor-sds-bateria-m18-fuel-milwaukee-2717-20-m18-r9smp/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>01BAW06038</t>
+          <t>01BUL00805</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Tester Multimetro Multirango Manual Baw RM113D</t>
+          <t>Pistola Encoladora Inalámbrica 10w con Base y Cable USB Suprabond C PHX B10</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>57362</v>
+        <v>78612</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tester-multimetro-multirango-manual-baw-rm113d/</t>
+          <t>https://electrocity.com.ar/productos/pistola-encoladora-inalambrica-10w-con-base-y-cable-usb-suprabond-c-phx-b10-z9nj7/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>01HRT09010</t>
+          <t>01BLO00032</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Destornillador Punta Plana Aislado 1000v Bahco</t>
+          <t>Bloqueador de Térmica Bipolar Transparente E2 Blook ELE-2111</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>26027</v>
+        <v>40452</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-aislado-1000v-bahco/</t>
+          <t>https://electrocity.com.ar/productos/bloqueador-de-termica-bipolar-transparente-e2-blook-ele-2111-rdbhj/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>01HRT05602</t>
+          <t>01BLO00024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Sierra Copa Bimetálica 20mm Profesional HRT 885347</t>
+          <t>Bloqueador Eléctrico Rojo a Tornillo Bioseif ELE-1140</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>10115</v>
+        <v>33710</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sierra-copa-bimetalica-20mm-profesional-hrt-885347/</t>
+          <t>https://electrocity.com.ar/productos/bloqueador-electrico-rojo-a-tornillo-bioseif-ele-1140-ubvdp/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>01MIL00306</t>
+          <t>01ZOL04207</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Punta Atornillador Phillips Impacto Ph3 x 50mm Kit x Unidad Milwaukee 4832-4463</t>
+          <t>Pinza Crimpeadora Terminales Tiff para Cables 0.25 a 10mm Zoloda CRIMP-10</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3943</v>
+        <v>155663</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph3-x-50mm-kit-x-unidad-milwaukee-4832-4463/</t>
+          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-terminales-tiff-para-cables-0-25-a-10mm-zoloda-crimp-10-sqxcn/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>01MIL00063</t>
+          <t>01JAI01424</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Taladro Angular Recto con Batería Milwaukee 2415-159A</t>
+          <t>Pinza Pelacable Redondo hasta 240 mm de Diámetro Ja PZC5360</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>467999</v>
+        <v>191470</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-angular-recto-con-bateria-milwaukee-2415-159a/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pelacable-redondo-hasta-240-mm-de-diametro-ja-pzc5360/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01HRT09103</t>
+          <t>01JAI00304</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cinta Métrica Retráctil Con Bloqueo 5m x 19mm Mtg-5-19ar (BAHCO)</t>
+          <t>Tester Multimetro Digital Compacto Ja INT0033</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>16992</v>
+        <v>19298</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-retractil-con-bloqueo-5m-x-19mm-mtg-5-19ar-bahco/</t>
+          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-compacto-ja-int0033/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>01HRT09102</t>
+          <t>01BAW06047</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Juego De Llaves Combinadas 11 Piezas Con Estuche Pu 95 (BAHCO)</t>
+          <t>Termómetro Infrarrojo Láser +800°C Baw RM800PRO</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>135382</v>
+        <v>92391</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-de-llaves-combinadas-11-piezas-con-estuche-pu-95-bahco/</t>
+          <t>https://electrocity.com.ar/productos/termometro-infrarrojo-laser-800c-baw-rm800pro/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>01HRT05130</t>
+          <t>01BAW06038</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Juego 6 Destornilladores Premium Blister P-3000/6h (BAHCO)</t>
+          <t>Tester Multimetro Multirango Manual Baw RM113D</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>49253</v>
+        <v>56546</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-6-destornilladores-premium-blister-p-3000-6h-bahco/</t>
+          <t>https://electrocity.com.ar/productos/tester-multimetro-multirango-manual-baw-rm113d/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>01HRT05124</t>
+          <t>01HRT09010</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Juego Destornilladores 6 Piezas 3000/6h (BAHCO)</t>
+          <t>Destornillador Punta Plana Aislado 1000v Bahco</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>49253</v>
+        <v>26027</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-destornilladores-6-piezas-3000-6h-bahco/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-aislado-1000v-bahco/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>01HRT05122</t>
+          <t>01HRT05602</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Juego Destornilladores 5 Piezas Blister BAHCO</t>
+          <t>Sierra Copa Bimetálica 20mm Profesional HRT 885347</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>33822</v>
+        <v>10115</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-destornilladores-5-piezas-blister-bahco/</t>
+          <t>https://electrocity.com.ar/productos/sierra-copa-bimetalica-20mm-profesional-hrt-885347/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>01LQF02370</t>
+          <t>01MIL00306</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DESTONILLADOR MULTIPUNTA ENCASTRE 1/4 CON 33 PUNTAS - TRUPER -13595</t>
+          <t>Punta Atornillador Phillips Impacto Ph3 x 50mm Kit x Unidad Milwaukee 4832-4463</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>18103</v>
+        <v>4337</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destonillador-multipunta-encastre-14-con-33-puntas-truper-13595/</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph3-x-50mm-kit-x-unidad-milwaukee-4832-4463/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>01HRT06061</t>
+          <t>01MIL00063</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DESTORNILLADOR PLANO 3.5 X 75MM AISLADOS 1000V STANLEY STMT60163 (STANLEY)</t>
+          <t>Taladro Angular Recto con Batería Milwaukee 2415-159A</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>9197</v>
+        <v>514840</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-plano-35-75mm-aislados-1000v-stanley-stmt60163/</t>
+          <t>https://electrocity.com.ar/productos/taladro-angular-recto-con-bateria-milwaukee-2415-159a/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>01BUL00017</t>
+          <t>01HRT09103</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Engrampadora profesional potencia regulable p/grampas 8 a 12mm y clavos 15mm (BULIT)</t>
+          <t>Cinta Métrica Retráctil Con Bloqueo 5m x 19mm Mtg-5-19ar (BAHCO)</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>87048</v>
+        <v>16992</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/engrampadora-profesional-potencia-regulable-p-grampas-8-a-12mm-y-clavos-15mm/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-retractil-con-bloqueo-5m-x-19mm-mtg-5-19ar-bahco/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>01BUL00023</t>
+          <t>01HRT09102</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Hoja de sierra junior sin-par (SIN-PAR)</t>
+          <t>Juego De Llaves Combinadas 11 Piezas Con Estuche Pu 95 (BAHCO)</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>994</v>
+        <v>135382</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/hoja-de-sierra-junior-sin-par/</t>
+          <t>https://electrocity.com.ar/productos/juego-de-llaves-combinadas-11-piezas-con-estuche-pu-95-bahco/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>01BUL00028</t>
+          <t>01HRT05130</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Cinta metrica doble freno metálica 7.5mt. x 25mm bulit</t>
+          <t>Juego 6 Destornilladores Premium Blister P-3000/6h (BAHCO)</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>36687</v>
+        <v>49253</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-doble-freno-metalica-7-5mt-x-25mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/juego-6-destornilladores-premium-blister-p-3000-6h-bahco/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>01BUL00031</t>
+          <t>01HRT05124</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Sie s2 12 mini arco de sierra 12 serie 200 (BULIT)</t>
+          <t>Juego Destornilladores 6 Piezas 3000/6h (BAHCO)</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>18799</v>
+        <v>49253</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sie-s2-12-mini-arco-de-sierra-12-serie-200/</t>
+          <t>https://electrocity.com.ar/productos/juego-destornilladores-6-piezas-3000-6h-bahco/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>01BUL00078</t>
+          <t>01HRT05122</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Destornillador profesional #1x75mm punta phillips (BULIT)</t>
+          <t>Juego Destornilladores 5 Piezas Blister BAHCO</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>5529</v>
+        <v>33822</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-1x75mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/juego-destornilladores-5-piezas-blister-bahco/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>01BUL00084</t>
+          <t>01LQF02370</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Destornillador profesional #2x100mm punta phillips (BULIT)</t>
+          <t>DESTONILLADOR MULTIPUNTA ENCASTRE 1/4 CON 33 PUNTAS - TRUPER -13595</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>9329</v>
+        <v>18103</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-2x100mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destonillador-multipunta-encastre-14-con-33-puntas-truper-13595/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>01BUL00086</t>
+          <t>01HRT06061</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Destornillador profesional #3x125mm punta phillips (BULIT)</t>
+          <t>DESTORNILLADOR PLANO 3.5 X 75MM AISLADOS 1000V STANLEY STMT60163 (STANLEY)</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>14848</v>
+        <v>9197</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-3x125mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-plano-35-75mm-aislados-1000v-stanley-stmt60163/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>01BUL00088</t>
+          <t>01BUL00017</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x100mm punta plana (BULIT)</t>
+          <t>Engrampadora profesional potencia regulable p/grampas 8 a 12mm y clavos 15mm (BULIT)</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5011</v>
+        <v>90095</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x100mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/engrampadora-profesional-potencia-regulable-p-grampas-8-a-12mm-y-clavos-15mm/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>01BUL00090</t>
+          <t>01BUL00023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x150mm punta plana (BULIT)</t>
+          <t>Hoja de sierra junior sin-par (SIN-PAR)</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>6332</v>
+        <v>994</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x150mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/hoja-de-sierra-junior-sin-par/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>01BUL00092</t>
+          <t>01BUL00028</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x200mm punta plana (BULIT)</t>
+          <t>Cinta metrica doble freno metálica 7.5mt. x 25mm bulit</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>6348</v>
+        <v>34669</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x200mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-doble-freno-metalica-7-5mt-x-25mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>01BUL00096</t>
+          <t>01BUL00078</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Destornillador profesional #5x150mm punta plana (BULIT)</t>
+          <t>Destornillador profesional #1x75mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>7570</v>
+        <v>5723</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-5x150mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-1x75mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>01BUL00098</t>
+          <t>01BUL00086</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Destornillador profesional #6x38mm punta plana (BULIT)</t>
+          <t>Destornillador profesional #3x125mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>9519</v>
+        <v>15367</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-6x38mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-3x125mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>01BUL00102</t>
+          <t>01BUL00088</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Destornillador profesional #8x150mm punta plana (BULIT)</t>
+          <t>Destornillador profesional #4x100mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>15248</v>
+        <v>5187</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-8x150mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x100mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>01BUL00104</t>
+          <t>01BUL00090</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x150mm punta recta (BULIT)</t>
+          <t>Destornillador profesional #4x150mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>6189</v>
+        <v>6553</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x150mm-punta-recta/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x150mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>01BUL00106</t>
+          <t>01BUL00092</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x75mm punta recta (BULIT)</t>
+          <t>Destornillador profesional #4x200mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5529</v>
+        <v>6570</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x75mm-punta-recta/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x200mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>01BUL00108</t>
+          <t>01BUL00098</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x200mm punta recta (BULIT)</t>
+          <t>Destornillador profesional #6x38mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>7452</v>
+        <v>9853</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x200mm-punta-recta/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-6x38mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>01BUL00110</t>
+          <t>01BUL00102</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SET DE 11 DESTORNILLADORES PROFESIONAL PUNTA PLANA Y PHILLIPS (BULIT)</t>
+          <t>Destornillador profesional #8x150mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>92413</v>
+        <v>15781</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-11-destornilladores-profesional-punta-plana-y-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-8x150mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>01BUL00111</t>
+          <t>01BUL00104</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SET DE 6 DESTORNILLADORES PROFESIONAL PUNTA PHILLIPS (BULIT)</t>
+          <t>Destornillador profesional #4x150mm punta recta (BULIT)</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>52796</v>
+        <v>6405</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-profesional-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x150mm-punta-recta/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>01BUL00113</t>
+          <t>01BUL00106</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SET DE 6 DESTORNILLADORES PROFESIONAL PUNTA PHILLIPS Y RECTO (BULIT)</t>
+          <t>Destornillador profesional #4x75mm punta recta (BULIT)</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>71967</v>
+        <v>5723</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-profesional-punta-phillips-y-recto/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x75mm-punta-recta/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>01BUL00164</t>
+          <t>01BUL00108</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Llave ajustable pavonada de 8 francesa profesional (BULIT)</t>
+          <t>Destornillador profesional #4x200mm punta recta (BULIT)</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>37604</v>
+        <v>7713</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-ajustable-pavonada-de-8-francesa-profesional/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x200mm-punta-recta/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>01BUL00466</t>
+          <t>01BUL00164</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Cutter reforzado automático chico con repuesto serie 500 (BULIT)</t>
+          <t>Llave ajustable pavonada de 8 francesa profesional (BULIT)</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>10359</v>
+        <v>38920</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-reforzado-automatico-chico-con-repuesto-serie-500/</t>
+          <t>https://electrocity.com.ar/productos/llave-ajustable-pavonada-de-8-francesa-profesional/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>01BUL00670</t>
+          <t>01BUL00466</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Pinza universal de presicion de 45 p/artesanias y electrónica (BULIT)</t>
+          <t>Cutter reforzado automático chico con repuesto serie 500 (BULIT)</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>10042</v>
+        <v>10721</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-de-presicion-de-45-partesanias-y-electronica/</t>
+          <t>https://electrocity.com.ar/productos/cutter-reforzado-automatico-chico-con-repuesto-serie-500/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>01BUL00672</t>
+          <t>01BUL00670</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pinza de punta semi redonda de precision de 45 p/artesanias y electrónica (BULIT)</t>
+          <t>Pinza universal de presicion de 45 p/artesanias y electrónica (BULIT)</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>9993</v>
+        <v>10394</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-de-punta-semi-redonda-de-precision-de-45-partesanias-y-electronica/</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-de-presicion-de-45-partesanias-y-electronica/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>01BUL00674</t>
+          <t>01BUL00672</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pinza de punta redonda de precision de 45 p/artesanias y electrónica</t>
+          <t>Pinza de punta semi redonda de precision de 45 p/artesanias y electrónica (BULIT)</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>11777</v>
+        <v>10343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-de-punta-redonda-de-precision-de-45-partesanias-y-electronica/</t>
+          <t>https://electrocity.com.ar/productos/pinza-de-punta-semi-redonda-de-precision-de-45-partesanias-y-electronica/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>01BUL00695</t>
+          <t>01BUL00674</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SET COMBO PINZAS PRESICION UNIVERSAL + PUNTA SEMI REDONDA + ALICATE 45 P/ARTESANIAS Y E</t>
+          <t>Pinza de punta redonda de precision de 45 p/artesanias y electrónica</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>30948</v>
+        <v>12189</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-combo-pinzas-presicion-universal-punta-semi-redonda-alicate-45-partesanias-y-e/</t>
+          <t>https://electrocity.com.ar/productos/pinza-de-punta-redonda-de-precision-de-45-partesanias-y-electronica/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>01BUL00696</t>
+          <t>01BUL00695</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SET COMBO PINZAS PRESICION UNIVERSAL + PUNTA REDONDA + PUNTA SEMI REDONDA + ALICATE FRONTA (BULIT)</t>
+          <t>SET COMBO PINZAS PRESICION UNIVERSAL + PUNTA SEMI REDONDA + ALICATE 45 P/ARTESANIAS Y E</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>42725</v>
+        <v>32031</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-combo-pinzas-presicion-universal-punta-redonda-punta-semi-redonda-alicate-fronta/</t>
+          <t>https://electrocity.com.ar/productos/set-combo-pinzas-presicion-universal-punta-semi-redonda-alicate-45-partesanias-y-e/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>01BUL00809</t>
+          <t>01BUL00696</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Pistola encoladora dosificadora de pegamento 10w (SUPRABOND)</t>
+          <t>SET COMBO PINZAS PRESICION UNIVERSAL + PUNTA REDONDA + PUNTA SEMI REDONDA + ALICATE FRONTA (BULIT)</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>19645</v>
+        <v>44220</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-encoladora-dosificadora-de-pegamento-10w/</t>
+          <t>https://electrocity.com.ar/productos/set-combo-pinzas-presicion-universal-punta-redonda-punta-semi-redonda-alicate-fronta/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>01BUL00893</t>
+          <t>01BUL00809</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 turbo fino 115mm bulit (BULIT)</t>
+          <t>Pistola encoladora dosificadora de pegamento 10w (SUPRABOND)</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>26507</v>
+        <v>20333</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-fino-115mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/pistola-encoladora-dosificadora-de-pegamento-10w/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>01BUL00894</t>
+          <t>01BUL00893</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 continuo 180mm bulit (BULIT)</t>
+          <t>Disco diamantado serie 400 turbo fino 115mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>20509</v>
+        <v>27170</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-continuo-180mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-fino-115mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>01BUL00895</t>
+          <t>01BUL00894</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 segmentado 180mm bulit (BULIT)</t>
+          <t>Disco diamantado serie 400 continuo 180mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>23208</v>
+        <v>21021</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-segmentado-180mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-continuo-180mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>01BUL00896</t>
+          <t>01BUL00895</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 turbo 180mm bulit (BULIT)</t>
+          <t>Disco diamantado serie 400 segmentado 180mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>27139</v>
+        <v>23788</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-180mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-segmentado-180mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>01BUL00905</t>
+          <t>01BUL00896</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Disco corte extra fino 1 115mm serie 400 bulit (BULIT)</t>
+          <t>Disco diamantado serie 400 turbo 180mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1225</v>
+        <v>27818</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-corte-extra-fino-1-115mm-serie-400-bulit/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-180mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>01BUL01620</t>
+          <t>01BUL00905</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Lima plana entrefina acero frojado 8 mango ergonómico (BULIT)</t>
+          <t>Disco corte extra fino 1 115mm serie 400 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>16252</v>
+        <v>1255</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/lima-plana-entrefina-acero-frojado-8-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/disco-corte-extra-fino-1-115mm-serie-400-bulit/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>01BUL01621</t>
+          <t>01BUL01620</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lima redonda entrefina acero forjado 8 mango ergonómico (BULIT)</t>
+          <t>Lima plana entrefina acero frojado 8 mango ergonómico (BULIT)</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>13144</v>
+        <v>16821</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/lima-redonda-entrefina-acero-forjado-8-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/lima-plana-entrefina-acero-frojado-8-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>01BUL01622</t>
+          <t>01BUL01621</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Lima media caña entrefina acero forjado 8 mango ergonómico (BULIT)</t>
+          <t>Lima redonda entrefina acero forjado 8 mango ergonómico (BULIT)</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>16968</v>
+        <v>13604</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/lima-media-cania-entrefina-acero-forjado-8-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/lima-redonda-entrefina-acero-forjado-8-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>01BUL01632</t>
+          <t>01BUL01622</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Serrucho profesional 500mm dientes cementados hoja extra ancha (BULIT)</t>
+          <t>Lima media caña entrefina acero forjado 8 mango ergonómico (BULIT)</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>26601</v>
+        <v>17561</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/serrucho-profesional-500mm-dientes-cementados-hoja-extra-ancha/</t>
+          <t>https://electrocity.com.ar/productos/lima-media-cania-entrefina-acero-forjado-8-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>01BUL01635</t>
+          <t>01BUL01632</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Serrucho profesional costilla 300mm dientes cementados hoja extra ancha (BULIT)</t>
+          <t>Serrucho profesional 500mm dientes cementados hoja extra ancha (BULIT)</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>18106</v>
+        <v>27533</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/serrucho-profesional-costilla-300mm-dientes-cementados-hoja-extra-ancha/</t>
+          <t>https://electrocity.com.ar/productos/serrucho-profesional-500mm-dientes-cementados-hoja-extra-ancha/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>01BUL01636</t>
+          <t>01BUL01635</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Serrucho turbo pro p/durlero 165mm c/punta de corte y mango ergonomico (BULIT)</t>
+          <t>Serrucho profesional costilla 300mm dientes cementados hoja extra ancha (BULIT)</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>29628</v>
+        <v>18739</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/serrucho-turbo-pro-pdurlero-165mm-cpunta-de-corte-y-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/serrucho-profesional-costilla-300mm-dientes-cementados-hoja-extra-ancha/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>01BUL01721</t>
+          <t>01BUL01636</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Llave p/caños con mordazas 1 1/2 c/tope seguridad</t>
+          <t>Serrucho turbo pro p/durlero 165mm c/punta de corte y mango ergonomico (BULIT)</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>49422</v>
+        <v>30665</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-pcanios-con-mordazas-1-12-ctope-seguridad/</t>
+          <t>https://electrocity.com.ar/productos/serrucho-turbo-pro-pdurlero-165mm-cpunta-de-corte-y-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>01BUL01840</t>
+          <t>01BUL01721</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA PROFESIONAL DE PEGAMENTO + BARRAS TRANSP. 112MM X 10CM X 1kg EN BLIST</t>
+          <t>Llave p/caños con mordazas 1 1/2 c/tope seguridad</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>133347</v>
+        <v>51152</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-de-pegamento-barras-transp-112mm-10cm-1kg-en-blist/</t>
+          <t>https://electrocity.com.ar/productos/llave-pcanios-con-mordazas-1-12-ctope-seguridad/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>01BUL01844</t>
+          <t>01BUL01840</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA PROFESIONAL DE PEGAMENTO + BARRAS TRANSP. 112MM X 10CM X 5kg EN BLIST</t>
+          <t>KIT - PISTOLA PROFESIONAL DE PEGAMENTO + BARRAS TRANSP. 112MM X 10CM X 1kg EN BLIST</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>102807</v>
+        <v>138014</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-de-pegamento-barras-transp-112mm-10cm-5kg-en-blist/</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-de-pegamento-barras-transp-112mm-10cm-1kg-en-blist/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>01BUL01846</t>
+          <t>01BUL01844</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA DE PEG. 10W EDICION LUNARES + BARRAS TRANSP.074x10CM x 100Grs EN BLISTER (SUPRABOND)</t>
+          <t>KIT - PISTOLA PROFESIONAL DE PEGAMENTO + BARRAS TRANSP. 112MM X 10CM X 5kg EN BLIST</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>25753</v>
+        <v>106405</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-de-peg-10w-edicion-lunares-barras-transp074x10cm-100grs-en-blister/</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-de-pegamento-barras-transp-112mm-10cm-5kg-en-blist/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>01BUL01981</t>
+          <t>01BUL01846</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Set 7 destornilladores precisión serie 1000 (BULIT)</t>
+          <t>KIT - PISTOLA DE PEG. 10W EDICION LUNARES + BARRAS TRANSP.074x10CM x 100Grs EN BLISTER (SUPRABOND)</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>29844</v>
+        <v>26655</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-7-destornilladores-precision-serie-1000/</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-de-peg-10w-edicion-lunares-barras-transp074x10cm-100grs-en-blister/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>01BUL01989</t>
+          <t>01BUL01981</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Set de llaves tipo t de 16 unidades bulit</t>
+          <t>Set 7 destornilladores precisión serie 1000 (BULIT)</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>106568</v>
+        <v>30888</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-llaves-tipo-t-de-16-unidades-bulit/</t>
+          <t>https://electrocity.com.ar/productos/set-7-destornilladores-precision-serie-1000/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>01BUL02070</t>
+          <t>01BUL01989</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Kit de 7 llaves criquet mm articuladas serie 800</t>
+          <t>Set de llaves tipo t de 16 unidades bulit</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>103500</v>
+        <v>110298</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-de-7-llaves-criquet-mm-articuladas-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/set-de-llaves-tipo-t-de-16-unidades-bulit/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>01BUL02171</t>
+          <t>01BUL02070</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Llave ajustable 8 cromada c/mango ergonomico antideslizante (BULIT)</t>
+          <t>Kit de 7 llaves criquet mm articuladas serie 800</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>25824</v>
+        <v>107122</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-ajustable-8-cromada-cmango-ergonomico-antideslizante/</t>
+          <t>https://electrocity.com.ar/productos/kit-de-7-llaves-criquet-mm-articuladas-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>01BUL02172</t>
+          <t>01BUL02171</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Llave ajustable 10 cromada c/mango ergonomico antideslizante (BULIT)</t>
+          <t>Llave ajustable 8 cromada c/mango ergonomico antideslizante (BULIT)</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>32691</v>
+        <v>26728</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-ajustable-10-cromada-cmango-ergonomico-antideslizante/</t>
+          <t>https://electrocity.com.ar/productos/llave-ajustable-8-cromada-cmango-ergonomico-antideslizante/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>01BUL02330</t>
+          <t>01BUL02172</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CUTTER PROFESIONAL AUTOMATICO BULIT + REPUESTOS HOJAS (BULIT)</t>
+          <t>Llave ajustable 10 cromada c/mango ergonomico antideslizante (BULIT)</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>28202</v>
+        <v>33835</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-profesional-automatico-bulit-repuestos-hojas/</t>
+          <t>https://electrocity.com.ar/productos/llave-ajustable-10-cromada-cmango-ergonomico-antideslizante/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>01BUL02332</t>
+          <t>01BUL02330</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CUTTER PROFESIONAL METALICO BULIT + REPUESTOS (BULIT)</t>
+          <t>CUTTER PROFESIONAL AUTOMATICO BULIT + REPUESTOS HOJAS (BULIT)</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>26642</v>
+        <v>29189</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-profesional-metalico-bulit-repuestos/</t>
+          <t>https://electrocity.com.ar/productos/cutter-profesional-automatico-bulit-repuestos-hojas/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>01BUL02335</t>
+          <t>01BUL02332</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DESTORNILLADOR RECTO 4X150 + DESTORNILLADOR RECTO 4X75 + DESTORNILLADOR RECTO 4X200 (BULIT)</t>
+          <t>CUTTER PROFESIONAL METALICO BULIT + REPUESTOS (BULIT)</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>19170</v>
+        <v>26865</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-recto-4x150-destornillador-recto-4x75-destornillador-recto-4x200/</t>
+          <t>https://electrocity.com.ar/productos/cutter-profesional-metalico-bulit-repuestos/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>01EXP00002</t>
+          <t>01BUL02335</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 20 metros c/porta-pasacable</t>
+          <t>DESTORNILLADOR RECTO 4X150 + DESTORNILLADOR RECTO 4X75 + DESTORNILLADOR RECTO 4X200 (BULIT)</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>86522</v>
+        <v>19840</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-20-metros-cportapasacable/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-recto-4x150-destornillador-recto-4x75-destornillador-recto-4x200/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>01EXP00004</t>
+          <t>01EXP00002</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 15 metros c/porta-pasacable</t>
+          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 20 metros c/porta-pasacable</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>69924</v>
+        <v>86522</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-15-metros-cportapasacable/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-20-metros-cportapasacable/</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>165398</v>
+        <v>163043</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>393804</v>
+        <v>388198</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>569047</v>
+        <v>560947</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>323909</v>
+        <v>319690</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1069185</v>
+        <v>1055260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>518827</v>
+        <v>512070</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>481563</v>
+        <v>475291</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>200651</v>
+        <v>198038</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>646598</v>
+        <v>638176</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>640795</v>
+        <v>632448</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>739544</v>
+        <v>729911</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2598634</v>
+        <v>2564788</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>590488</v>
+        <v>582797</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>768208</v>
+        <v>758203</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>644951</v>
+        <v>636551</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>784188</v>
+        <v>773974</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>11687</v>
+        <v>11521</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>23374</v>
+        <v>23041</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>16729</v>
+        <v>16491</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>71588</v>
+        <v>70569</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>18391</v>
+        <v>18129</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>20268</v>
+        <v>19979</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>14162</v>
+        <v>13960</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>38587</v>
+        <v>38038</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>33390</v>
+        <v>32915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -5561,300 +5561,300 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>01SEG07010</t>
+          <t>01RED10550</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Guante de seguridad dielectrico 2500v talle mediano iram 3604:1998 (KRAFTEK)</t>
+          <t>Mecha acero broca tipo escalonada de 7 medidas 14-16-18-20-22-24-25mm p/taladros (DEWALT)</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>122916</v>
+        <v>109882</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/guante-de-seguridad-dielectrico-2500v-talle-mediano-iram-36041998/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-broca-tipo-escalonada-de-7-medidas-14161820222425mm-ptaladros/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>01SIC00103</t>
+          <t>01SEG07010</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Puntas de prueba de tensón 100/500vca SICA</t>
+          <t>Guante de seguridad dielectrico 2500v talle mediano iram 3604:1998 (KRAFTEK)</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>7429</v>
+        <v>121166</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/puntas-de-prueba-de-tenson-100500vca-sica/</t>
+          <t>https://electrocity.com.ar/productos/guante-de-seguridad-dielectrico-2500v-talle-mediano-iram-36041998/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>01SIC11520</t>
+          <t>01SIC00103</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>KIT - 4 DESTORNILLADORES PUNTA PLANA CERO CROMO-VAN SICA (SICA)</t>
+          <t>Puntas de prueba de tensón 100/500vca SICA</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>11218</v>
+        <v>7323</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-4-destornilladores-punta-plana-cero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/puntas-de-prueba-de-tenson-100500vca-sica/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>01SIC23590</t>
+          <t>01SIC11520</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Destornillador punta plana 4x75mm acero cromo-van SICA</t>
+          <t>KIT - 4 DESTORNILLADORES PUNTA PLANA CERO CROMO-VAN SICA (SICA)</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>2506</v>
+        <v>11058</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-4x75mm-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/kit-4-destornilladores-punta-plana-cero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>01SIC23591</t>
+          <t>01SIC23590</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Destornillador punta plana 5.5x100mm acero cromo-van SICA</t>
+          <t>Destornillador punta plana 4x75mm acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3229</v>
+        <v>2471</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-55x100mm-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-4x75mm-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>01SIC23592</t>
+          <t>01SIC23591</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Destornillador punta plana 6.5x100mm acero cromo-van SICA</t>
+          <t>Destornillador punta plana 5.5x100mm acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3588</v>
+        <v>3183</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-65x100mm-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-55x100mm-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>01SIC23600</t>
+          <t>01SIC23592</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Destornillador punta plana 6.5x150mm acero cromo-van SICA</t>
+          <t>Destornillador punta plana 6.5x100mm acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>3875</v>
+        <v>3537</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-65x150mm-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-65x100mm-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>01SIC23642</t>
+          <t>01SIC23600</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Pinza de punta 8 200mm 1000v acero cromo-van SICA</t>
+          <t>Destornillador punta plana 6.5x150mm acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>43372</v>
+        <v>3820</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-de-punta-8-200mm-1000v-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-65x150mm-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>01SIC24160</t>
+          <t>01SIC23642</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Pistola encoladora 100w p/barras adhesivas 11mm 220v 170°</t>
+          <t>Pinza de punta 8 200mm 1000v acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>25212</v>
+        <v>42755</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-encoladora-100w-pbarras-adhesivas-11mm-220v-170/</t>
+          <t>https://electrocity.com.ar/productos/pinza-de-punta-8-200mm-1000v-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>01TOO01125</t>
+          <t>01SIC24160</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PORTA CINTA METRICA P/5 8 10 Y 15METROS (TOOLMEN)</t>
+          <t>Pistola encoladora 100w p/barras adhesivas 11mm 220v 170°</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>18617</v>
+        <v>24853</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/porta-cinta-metrica-p5-8-10-y-15metros/</t>
+          <t>https://electrocity.com.ar/productos/pistola-encoladora-100w-pbarras-adhesivas-11mm-220v-170/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>01BAW06036</t>
+          <t>01TOO01125</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Multimetro multirrango manual h/600vcc/vca 10acc 20m cat iii 600v - BAW</t>
+          <t>PORTA CINTA METRICA P/5 8 10 Y 15METROS (TOOLMEN)</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>27411</v>
+        <v>18617</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-h600vccvca-10acc-20m-cat-iii-600v-baw/</t>
+          <t>https://electrocity.com.ar/productos/porta-cinta-metrica-p5-8-10-y-15metros/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>01BAW06039</t>
+          <t>01ZOL04200</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Multimetro multirrango manual vca: 80mv/800mv/8v/80v/750.0v. cat iii 600v 1 rms (BAW)</t>
+          <t>Pinza pelacable 0.2 a 6mm autoajustable - regulable 5 a 12mm</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>67556</v>
+        <v>123031</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-vca-80mv800mv8v80v7500v-cat-iii-600v-1-rms/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pelacable-02-a-6mm-autoajustable-regulable-5-a-12mm/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>01BAW06040</t>
+          <t>01BAW06036</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Comprobador digital cables y terminales de red rj45 y usb (BAW)</t>
+          <t>Multimetro multirrango manual h/600vcc/vca 10acc 20m cat iii 600v - BAW</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>61175</v>
+        <v>27021</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/comprobador-digital-cables-y-terminales-de-red-rj45-y-usb/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-h600vccvca-10acc-20m-cat-iii-600v-baw/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>01BAW06054</t>
+          <t>01BAW06039</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 1 rms para ambas corrientes ca/cc 60a/600a (BAW)</t>
+          <t>Multimetro multirrango manual vca: 80mv/800mv/8v/80v/750.0v. cat iii 600v 1 rms (BAW)</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>133851</v>
+        <v>66594</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-para-ambas-corrientes-cacc-60a600a/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-vca-80mv800mv8v80v7500v-cat-iii-600v-1-rms/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>01BAW11252</t>
+          <t>01BAW06040</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>BAWMS115 MULTIMETRO MEDICION AUTORRANGO SMART 1 RMS (BAW)</t>
+          <t>Comprobador digital cables y terminales de red rj45 y usb (BAW)</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>77764</v>
+        <v>60304</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bawms115-multimetro-medicion-autorrango-smart-1-rms/</t>
+          <t>https://electrocity.com.ar/productos/comprobador-digital-cables-y-terminales-de-red-rj45-y-usb/</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>24036</v>
+        <v>23694</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>60274</v>
+        <v>59416</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>18865</v>
+        <v>18597</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>18865</v>
+        <v>18597</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>77667</v>
+        <v>76561</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>45633</v>
+        <v>47230</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>103318</v>
+        <v>85908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>255033</v>
+        <v>212775</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>20952</v>
+        <v>21476</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>509841</v>
+        <v>502584</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>87048</v>
+        <v>90095</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>12795</v>
+        <v>13242</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>15442</v>
+        <v>15983</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>18272</v>
+        <v>18911</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>13019</v>
+        <v>13475</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>9919</v>
+        <v>10266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>6348</v>
+        <v>6570</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>8419</v>
+        <v>8713</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>9009</v>
+        <v>9324</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>21831</v>
+        <v>22595</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>65469</v>
+        <v>67760</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>385205</v>
+        <v>379722</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>292635.15</v>
+        <v>327777.55</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>683829.95</v>
+        <v>752274.6</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>483124</v>
+        <v>451747</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>111889</v>
+        <v>123088</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>566485</v>
+        <v>623183</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>9061</v>
+        <v>8932</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -6621,1498 +6621,1418 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>01MIL00310</t>
+          <t>01MIL00623</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Set de Puntas de Alto Impacto con Mango Kit x 12 Milwaukee 4832-4507</t>
+          <t>Caja Herramientas 2 Cajones Packout Milwaukee 4822-8442</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>29917</v>
+        <v>505461.75</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-puntas-de-alto-impacto-con-mango-kit-x-12-milwaukee-4832-4507/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/caja-herramientas-2-cajones-packout-milwaukee-4822-8442-an020/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>01MIL00623</t>
+          <t>01BAW11250</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Caja Herramientas 2 Cajones Packout Milwaukee 4822-8442</t>
+          <t>Multimetro Tester Digital BAW Medidor Display Led BAWm02</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>421184.4</v>
+        <v>18644</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/caja-herramientas-2-cajones-packout-milwaukee-4822-8442-an020/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/multimetro-tester-digital-baw-medidor-display-led-bawm02/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>01HRT09100</t>
+          <t>01MIL00352</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Multi Herramienta Plegable De Aluminio 18 En 1 MTT121 (BAHCO)</t>
+          <t>Set de Destornilladores Premium 10 Piezas Milwaukee 4822-2710</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>34328</v>
+        <v>85674</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multi-herramienta-plegable-de-aluminio-18-en-1-mtt121-bahco/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-de-destornilladores-premium-10-piezas-milwaukee-4822-2710/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>01MIL00624</t>
+          <t>01MIL00320</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Combo Taladro Atornillador + Atornillador de Impacto M18 Milwaukee 2691-259A</t>
+          <t>Set Puntas Tubos Impacto x 26 Piezas Milwaukee 4832-4408</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>1136854</v>
+        <v>99249</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-taladro-atornillador-atornillador-de-impacto-m18-milwaukee-2691-259a-sw3tn/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-puntas-tubos-impacto-x-26-piezas-milwaukee-4832-4408/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>01MIL00636</t>
+          <t>01HOM01200</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Combo Taladro Percutor + Atornillador de Impacto M12 Milwaukee 2497-259A</t>
+          <t>MECHA ESCALONADA CALADORA MULTIPLE P/CAJAS plásticaS</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>1187761</v>
+        <v>92143</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-taladro-percutor-atornillador-de-impacto-m12-milwaukee-2497-259a-14ceb/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-escalonada-caladora-multiple-pcajas-plasticas/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>01MIL00352</t>
+          <t>01RED04453</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Set de Destornilladores Premium 10 Piezas Milwaukee 4822-2710</t>
+          <t>MECHA WIDIA Ø 6MM STANDARD CORTA 100MM FISCHER</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>71390</v>
+        <v>3824</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-destornilladores-premium-10-piezas-milwaukee-4822-2710/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-6mm-standard-corta-100mm-fischer/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>01MIL00320</t>
+          <t>01MIL00617</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Set Puntas Tubos Impacto x 26 Piezas Milwaukee 4832-4408</t>
+          <t>Taladro Atornillador Percutor a Batería 18v Milwaukee 2607-259A</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>90218</v>
+        <v>886200.65</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-puntas-tubos-impacto-x-26-piezas-milwaukee-4832-4408/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/taladro-atornillador-percutor-a-bateria-18v-milwaukee-2607-259a-1uq1y/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>01HOM01200</t>
+          <t>01BAW11254</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>MECHA ESCALONADA CALADORA MULTIPLE P/CAJAS plásticaS</t>
+          <t>Pinza Amperométrica Digital Autorrango True Rms 600v Baw CM05</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>92143</v>
+        <v>35477</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-escalonada-caladora-multiple-pcajas-plasticas/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-autorrango-true-rms-600v-baw-cm05/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>01RED04453</t>
+          <t>01MIL00612</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>MECHA WIDIA Ø 6MM STANDARD CORTA 100MM FISCHER</t>
+          <t>Caja Organizador Chato Packout Milwaukee 4822-8431</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>3824</v>
+        <v>135327.5</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-6mm-standard-corta-100mm-fischer/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/caja-organizador-chato-packout-milwaukee-4822-8431-ign4n/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>01MIL00617</t>
+          <t>01MIL00618</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Taladro Atornillador Percutor a Batería 18v Milwaukee 2607-259A</t>
+          <t>Llave de Impacto 3/4'' M18 Fuel Milwaukee 2864-20 SIN BATERIA</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>805571.35</v>
+        <v>1433092</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-atornillador-percutor-a-bateria-18v-milwaukee-2607-259a-1uq1y/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/llave-de-impacto-fuel-encastre-1-2-one-key-milwaukee-2863-20-mwmi8/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>01BAW11254</t>
+          <t>01TOO01094</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Pinza Amperométrica Digital Autorrango True Rms 600v Baw CM05</t>
+          <t>Cinturón Portaherramientas Toolmen T37</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>35990</v>
+        <v>69658</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-autorrango-true-rms-600v-baw-cm05/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/cinturon-portaherramientas-toolmen-t37-jrliq/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>01SIC24155</t>
+          <t>01HRT06662</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Soldador de estaño 40w de punta tipo lapiz con mango plástico y soporte</t>
+          <t>Juego de Puntas x 31 Piezas Torx Phillips Plano Bahco 59S31B</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>19475</v>
+        <v>36612</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-de-estanio-40w-de-punta-tipo-lapiz-con-mango-plastico-y-soporte/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/juego-de-puntas-x-31-piezas-torx-phillips-plano-bahco-59s31b/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>01MIL00631</t>
+          <t>01HRT05640</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Batería M12 XC 3Ah RedLithuim Milwaukee 4811-2402</t>
+          <t>Mecha de acero repuesto para sierra copa bimetálica soporte a1 y a2</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>130023</v>
+        <v>6920</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-m12-xc-3ah-redlithuim-milwaukee-4811-2402-1fe5j/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-de-acero-repuesto-para-sierra-copa-bimetalica-soporte-a1-y-a2/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>01MIL00612</t>
+          <t>01HRT09022</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Caja Organizador Chato Packout Milwaukee 4822-8431</t>
+          <t>Pinza Punta Semiredonda 6 Aislada 1000v Bahco 2430S-160A-RN</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>112763.1</v>
+        <v>61765</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/caja-organizador-chato-packout-milwaukee-4822-8431-ign4n/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-punta-semiredonda-6-aislada-1000v-bahco-2430s-160a-rn/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>01MIL00618</t>
+          <t>01MIL00400</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Llave de Impacto 3/4'' M18 Fuel Milwaukee 2864-20 SIN BATERIA</t>
+          <t>Conservadora Compacta Packout 15 Litros Milwaukee 4822-8460</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1302706</v>
+        <v>326526</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-de-impacto-fuel-encastre-1-2-one-key-milwaukee-2863-20-mwmi8/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/conservadora-compacta-packout-15-litros-milwaukee-4822-8460/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>01TOO01094</t>
+          <t>01BUL01854</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Cinturón Portaherramientas Toolmen T37</t>
+          <t>KIT - PISTOLA PROFESIONAL PEGAMENTO + 8 BARRAS 112MM X 30CM SUPRABOND</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>69658</v>
+        <v>91686</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinturon-portaherramientas-toolmen-t37-jrliq/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-pegamento-8-barras-112mm-30cm-suprabond/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>01HRT06662</t>
+          <t>01BUL02264</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Juego de Puntas x 31 Piezas Torx Phillips Plano Bahco 59S31B</t>
+          <t>Pinza pta. redonda 6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>36612</v>
+        <v>13516</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-de-puntas-x-31-piezas-torx-phillips-plano-bahco-59s31b/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-pta-redonda-6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>01HRT05640</t>
+          <t>01HRT05605</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Mecha de acero repuesto para sierra copa bimetálica soporte a1 y a2</t>
+          <t>Mecha copa bimetálica traspasadora hss ø22mm 7/8</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>6920</v>
+        <v>11126</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-de-acero-repuesto-para-sierra-copa-bimetalica-soporte-a1-y-a2/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-22mm-78/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>01HRT09022</t>
+          <t>01INS00100</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Pinza Punta Semiredonda 6 Aislada 1000v Bahco 2430S-160A-RN</t>
+          <t>Pinza amperometrica 400a ac 600 vca/vcc fluke-302 (FLUKE)</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>61765</v>
+        <v>455487</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-punta-semiredonda-6-aislada-1000v-bahco-2430s-160a-rn/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-400a-ac-600-vcavcc-fluke302/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>01HRT09020</t>
+          <t>01TOO01024</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Pinza Alicate 7 Aislación 1000v Bahco 2151S-7A-RN</t>
+          <t>Porta-herramientas cartuchera p/electricistas mini (TOOLMEN)</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>75834</v>
+        <v>15157</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-alicate-7-aislacion-1000v-bahco-2151s-7a-rn/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-mini/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>01MIL00400</t>
+          <t>01TOO01095</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Conservadora Compacta Packout 15 Litros Milwaukee 4822-8460</t>
+          <t>Cinto de 50mm p/ sujetar porta-herramientas naranja (TOOLMEN)</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>291517</v>
+        <v>20431</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/conservadora-compacta-packout-15-litros-milwaukee-4822-8460/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/cinto-de-50mm-p-sujetar-portaherramientas-naranja/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>01MIL00302</t>
+          <t>01BAW06056</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Punta Atornillador Phillips Impacto Ph2 x 25mm Kit x 5 Milwaukee 4832-4601</t>
+          <t>Pinza amperometrica 1 rms para corriente alterna 60a/600a/1000a (BAW)</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>5554</v>
+        <v>149541</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph2-x-25mm-kit-x-5-milwaukee-4832-4601/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-para-corriente-alterna-60a600a1000a/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>01BUL01854</t>
+          <t>01MIL00638</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA PROFESIONAL PEGAMENTO + 8 BARRAS 112MM X 30CM SUPRABOND</t>
+          <t>Combo Versátil Packout 4 Cajas Milwaukee</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>88586</v>
+        <v>944100.5</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-pegamento-8-barras-112mm-30cm-suprabond/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/combo-versatil-packout-4-cajas-milwaukee-jyp50/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>01BUL02264</t>
+          <t>01MIL00502</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Pinza pta. redonda 6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Combo Completo Packout 6 Cajas Milwaukee</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>13059</v>
+        <v>1100359.35</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pta-redonda-6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/combo-completo-packout-6-cajas-milwaukee-pwa2i/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>01HRT05105</t>
+          <t>01MIL00504</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Destornillador plano standard chico 5.5 x 125mm (BAHCO)</t>
+          <t>Combo Básico Packout 3 Cajas Milwaukee 8424 + 8425 + 8427</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>7567</v>
+        <v>809816.1</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-plano-standard-chico-55-125mm/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/combo-basico-packout-milwaukee-3-cajas-8424-8425-8427-bq0m1/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>01INS00100</t>
+          <t>01MIL00610</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 400a ac 600 vca/vcc fluke-302 (FLUKE)</t>
+          <t>Batería Capacidad Extendida M18 RedLithium XC 4.0 Milwaukee 4811-1840</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>461498</v>
+        <v>245637</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-400a-ac-600-vcavcc-fluke302/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/bateria-capacidad-extendida-m18-redlithium-xc-4-0-milwaukee-4811-1840-1h696/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>01TOO01024</t>
+          <t>01MIL00622</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Porta-herramientas cartuchera p/electricistas mini (TOOLMEN)</t>
+          <t>Cinta Métrica Magnetica Retráctil 8 Metros Milwaukee 4822-1026M</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>15157</v>
+        <v>66938</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-mini/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-magnetica-retractil-8-metros-milwaukee-4822-1026m-1qoyn/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>01TOO01095</t>
+          <t>01BLO00030</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Cinto de 50mm p/ sujetar porta-herramientas naranja (TOOLMEN)</t>
+          <t>Bloqueador de Térmica Unipolar Transparente E1 Blook ELE-2110</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>20431</v>
+        <v>20971</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinto-de-50mm-p-sujetar-portaherramientas-naranja/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/bloqueador-de-termica-unipolar-transparente-e1-blook-ele-2110-z8wpw/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>01USH00040</t>
+          <t>01BLO00002</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Dobladora de caños 7/8" y 1" con trípode y resorte adaptador para caños 3/4"</t>
+          <t>Candado Dieléctrico Arandela Plástica 40mm Bioseif CAN-1010</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>604232</v>
+        <v>22911</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/dobladora-de-canios-78-y-1-con-tripode-y-resorte-adaptador-para-canios-34/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/candado-dielectrico-arandela-plastica-40mm-bioseif-can-1010-9l1aq/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>01BAW06056</t>
+          <t>01BUL02250</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 1 rms para corriente alterna 60a/600a/1000a (BAW)</t>
+          <t>Alicate Extra Ancho 7" Serie 600 Bulit PZA S6 AL7 E</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>151700</v>
+        <v>19514</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-para-corriente-alterna-60a600a1000a/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/alicate-extra-ancho-7-serie-600-bulit-pza-s6-al7-e/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>01MIL00638</t>
+          <t>01HRT06664</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Combo Versátil Packout 4 Cajas Milwaukee</t>
+          <t>Punta Atornillador Pozidriv Largo 25mm Pz2 HRT 258253</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>858202.45</v>
+        <v>598</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-versatil-packout-4-cajas-milwaukee-jyp50/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-pozidriv-largo-25mm-pz2-hrt-258253/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>01MIL00502</t>
+          <t>01MIL00605</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Combo Completo Packout 6 Cajas Milwaukee</t>
+          <t>Taladro Atornillador Milwaukee 2607-20 Percutor</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>1000243.6</v>
+        <v>361069</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-completo-packout-6-cajas-milwaukee-pwa2i/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/taladro-atornillador-milwaukee-2607-20-percutor-g8oop/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>01MIL00504</t>
+          <t>01HRT05132</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Combo Básico Packout 3 Cajas Milwaukee 8424 + 8425 + 8427</t>
+          <t>Destornillador Crique Portapunta De 1/4 Stubby 808050S (BAHCO)</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>736136.95</v>
+        <v>38269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-basico-packout-milwaukee-3-cajas-8424-8425-8427-bq0m1/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/destornillador-crique-portapunta-de-1-4-stubby-808050s-bahco/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>01MIL00610</t>
+          <t>01BAW06030</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Batería Capacidad Extendida M18 RedLithium XC 4.0 Milwaukee 4811-1840</t>
+          <t>Pinza amperometrica 1 rms ca cat iii 600v - BAW rm901d</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>223289</v>
+        <v>53401</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-capacidad-extendida-m18-redlithium-xc-4-0-milwaukee-4811-1840-1h696/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-ca-cat-iii-600v-baw-rm901d/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>01MIL00622</t>
+          <t>01BAW06031</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Cinta Métrica Magnetica Retráctil 8 Metros Milwaukee 4822-1026M</t>
+          <t>Pinza amperometrica 1 rms ca vca/cc: 0001~600v- BAW rm900a</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>55777</v>
+        <v>63548</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-magnetica-retractil-8-metros-milwaukee-4822-1026m-1qoyn/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-ca-vca-cc-0001600v-baw-rm900a/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>01BLO00030</t>
+          <t>01BUL00031</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Bloqueador de Térmica Unipolar Transparente E1 Blook ELE-2110</t>
+          <t>Sie s2 12 mini arco de sierra 12 serie 200 (BULIT)</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>21274</v>
+        <v>19457</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bloqueador-de-termica-unipolar-transparente-e1-blook-ele-2110-z8wpw/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/sie-s2-12-mini-arco-de-sierra-12-serie-200/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>01BLO00002</t>
+          <t>01BUL00084</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Candado Dieléctrico Arandela Plástica 40mm Bioseif CAN-1010</t>
+          <t>Destornillador profesional #2x100mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>23242</v>
+        <v>9656</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/candado-dielectrico-arandela-plastica-40mm-bioseif-can-1010-9l1aq/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-2x100mm-punta-phillips/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>01BUL02250</t>
+          <t>01BUL00096</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Alicate Extra Ancho 7" Serie 600 Bulit PZA S6 AL7 E</t>
+          <t>Destornillador profesional #5x150mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>18854</v>
+        <v>7835</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/alicate-extra-ancho-7-serie-600-bulit-pza-s6-al7-e/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-5x150mm-punta-plana/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>01HRT06664</t>
+          <t>01BUL00110</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Punta Atornillador Pozidriv Largo 25mm Pz2 HRT 258253</t>
+          <t>SET DE 11 DESTORNILLADORES PROFESIONAL PUNTA PLANA Y PHILLIPS (BULIT)</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>598</v>
+        <v>95648</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-pozidriv-largo-25mm-pz2-hrt-258253/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-de-11-destornilladores-profesional-punta-plana-y-phillips/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>01MIL00605</t>
+          <t>01BUL00111</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Taladro Atornillador Milwaukee 2607-20 Percutor</t>
+          <t>SET DE 6 DESTORNILLADORES PROFESIONAL PUNTA PHILLIPS (BULIT)</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>314649</v>
+        <v>54644</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-atornillador-milwaukee-2607-20-percutor-g8oop/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-profesional-punta-phillips/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>01HRT05132</t>
+          <t>01BUL00113</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Destornillador Crique Portapunta De 1/4 Stubby 808050S (BAHCO)</t>
+          <t>SET DE 6 DESTORNILLADORES PROFESIONAL PUNTA PHILLIPS Y RECTO (BULIT)</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>38269</v>
+        <v>74485</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-crique-portapunta-de-1-4-stubby-808050s-bahco/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-profesional-punta-phillips-y-recto/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>01BAW06030</t>
+          <t>01BUL01848</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 1 rms ca cat iii 600v - BAW rm901d</t>
+          <t>KIT - PISTOLA DE PEGAMENTO 40W + 10 BARRAS TRANSPARENTE 112x30CM EN BLISTER</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>54172</v>
+        <v>51289</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-ca-cat-iii-600v-baw-rm901d/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-de-pegamento-40w-10-barras-transparente-112x30cm-en-blister/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>01BAW06031</t>
+          <t>01BUL01849</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 1 rms ca vca/cc: 0001~600v- BAW rm900a</t>
+          <t>PISTOLA DE PEGAMENTO BULIT 40W + 50 BARRAS TRANSPARENTE 112x30CM</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>64466</v>
+        <v>135741</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-ca-vca-cc-0001600v-baw-rm900a/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pistola-de-pegamento-bulit-40w-50-barras-transparente-112x30cm/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>01BUL01848</t>
+          <t>01BUL02249</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA DE PEGAMENTO 40W + 10 BARRAS TRANSPARENTE 112x30CM EN BLISTER</t>
+          <t>Alicate 6 aisl. acero-carbono mango aislado serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>49555</v>
+        <v>14736</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-de-pegamento-40w-10-barras-transparente-112x30cm-en-blister/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/alicate-6-aisl-acerocarbono-mango-aislado-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>01BUL01849</t>
+          <t>01BUL02254</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PISTOLA DE PEGAMENTO BULIT 40W + 50 BARRAS TRANSPARENTE 112x30CM</t>
+          <t>Pinza universal 6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>131151</v>
+        <v>17870</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-de-pegamento-bulit-40w-50-barras-transparente-112x30cm/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>01BUL02249</t>
+          <t>01BUL02256</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Alicate 6 aisl. acero-carbono mango aislado serie 600 bulit (BULIT)</t>
+          <t>Pinza universal 7 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>14237</v>
+        <v>19942</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/alicate-6-aisl-acerocarbono-mango-aislado-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-7-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>01BUL02254</t>
+          <t>01BUL02258</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Pinza universal 6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Pinza universal 8 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>17266</v>
+        <v>22590</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-8-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>01BUL02256</t>
+          <t>01BUL02260</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Pinza universal 7 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Pinza pta.semi-red.6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>19267</v>
+        <v>14330</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-7-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-ptasemired6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>01BUL02258</t>
+          <t>01BUL02262</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Pinza universal 8 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Pinza pta.semi-red. 8 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>21826</v>
+        <v>18273</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-8-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-ptasemired-8-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>01BUL02260</t>
+          <t>01EXP00004</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Pinza pta.semi-red.6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 15 metros c/porta-pasacable</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>13845</v>
+        <v>69924</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-ptasemired6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-15-metros-cportapasacable/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>01BUL02262</t>
+          <t>01HRT04920</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Pinza pta.semi-red. 8 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Pinza corta pela-cable de cobre o aluminio hasta ø35mm</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>17655</v>
+        <v>93168</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-ptasemired-8-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-corta-pelacable-de-cobre-o-aluminio-hasta-35mm/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>01HRT04920</t>
+          <t>01INS00200</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Pinza corta pela-cable de cobre o aluminio hasta ø35mm</t>
+          <t>Comprobador tension continua 12v-690v h/400 fluke-t90</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>94513</v>
+        <v>393247</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-corta-pelacable-de-cobre-o-aluminio-hasta-35mm/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/comprobador-tension-continua-12v690v-h400-fluket90/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>01INS00200</t>
+          <t>01INS01805</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Comprobador tension continua 12v-690v h/400 fluke-t90</t>
+          <t>Crimpeadora rj-11/12/45 pelacable cortadora fluke (FLUKE)</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>398436</v>
+        <v>486377</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/comprobador-tension-continua-12v690v-h400-fluket90/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/crimpeadora-rj111245-pelacable-cortadora-fluke/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>01INS01805</t>
+          <t>01INS01807</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Crimpeadora rj-11/12/45 pelacable cortadora fluke (FLUKE)</t>
+          <t>Herramienta de impacto 110/66 c/cuchilla fluke</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>492796</v>
+        <v>613393</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/crimpeadora-rj111245-pelacable-cortadora-fluke/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/herramienta-de-impacto-11066-ccuchilla-fluke/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>01INS01807</t>
+          <t>01INS01854</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Herramienta de impacto 110/66 c/cuchilla fluke</t>
+          <t>KIT - CRIMPEADORA PELACABLE-CORTADOR + COMPROBADOR + GENERADR TONOS + HERR. IMPACTO - FLUK (FLUKE)</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>621488</v>
+        <v>2494523</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/herramienta-de-impacto-11066-ccuchilla-fluke/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-crimpeadora-pelacablecortador-comprobador-generadr-tonos-herr-impacto-fluk/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>01INS01854</t>
+          <t>01RED10551</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>KIT - CRIMPEADORA PELACABLE-CORTADOR + COMPROBADOR + GENERADR TONOS + HERR. IMPACTO - FLUK (FLUKE)</t>
+          <t>Mecha acero broca tipo escalonada de 8 medidas 20-22-24-26-28-30-32-34mm p/taladros (DEWALT)</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>2527442</v>
+        <v>179353</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-crimpeadora-pelacablecortador-comprobador-generadr-tonos-herr-impacto-fluk/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-broca-tipo-escalonada-de-8-medidas-2022242628303234mm-ptaladros/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>01RED10550</t>
+          <t>01SIC11524</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Mecha acero broca tipo escalonada de 7 medidas 14-16-18-20-22-24-25mm p/taladros (DEWALT)</t>
+          <t>KIT - 4 DESTORNILLADORES PUNTA PLANA + 2 PUNTA PHILIPS ACERO CROMO-VAN SICA (SICA)</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>111469</v>
+        <v>11058</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-broca-tipo-escalonada-de-7-medidas-14161820222425mm-ptaladros/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-4-destornilladores-punta-plana-2-punta-philips-acero-cromovan-sica/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>01RED10551</t>
+          <t>01TOO00220</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Mecha acero broca tipo escalonada de 8 medidas 20-22-24-26-28-30-32-34mm p/taladros (DEWALT)</t>
+          <t>Kit portaherramienta grande + cinto 50mm toolmen (TOOLMEN)</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>181943</v>
+        <v>67456</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-broca-tipo-escalonada-de-8-medidas-2022242628303234mm-ptaladros/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-portaherramienta-grande-cinto-50mm-toolmen/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>01SIC11522</t>
+          <t>01TOO01010</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>KIT - 2 DESTORNILLADORES PUNTA PHILIPS ACERO CROMO-VAN SICA (SICA)</t>
+          <t>Porta celular funda smart-phone grande hasta 160mm (TOOLMEN)</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>12298</v>
+        <v>19802</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-2-destornilladores-punta-philips-acero-cromovan-sica/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/porta-celular-funda-smartphone-grande-hasta-160mm/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>01SIC11524</t>
+          <t>01USH00020</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>KIT - 4 DESTORNILLADORES PUNTA PLANA + 2 PUNTA PHILIPS ACERO CROMO-VAN SICA (SICA)</t>
+          <t>Dobladora de caños 3/4" una palanca con resorte adaptador para caños de 5/8"</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>23516</v>
+        <v>117674</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-4-destornilladores-punta-plana-2-punta-philips-acero-cromovan-sica/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/dobladora-de-canios-34-una-palanca-con-resorte-adaptador-para-canios-de-58/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>01SIC23640</t>
+          <t>01BAW06054</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Pinza universal 7 185mm 1000v acero cromo-van SICA</t>
+          <t>Pinza amperometrica 1 rms para ambas corrientes ca/cc 60a/600a (BAW)</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>45688</v>
+        <v>131945</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-7-185mm-1000v-acero-cromovan-sica/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-para-ambas-corrientes-cacc-60a600a/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>01SIC23644</t>
+          <t>01BAW11252</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Pinza alicate 6 160mm 1000v acero cromo-van SICA</t>
+          <t>BAWMS115 MULTIMETRO MEDICION AUTORRANGO SMART 1 RMS (BAW)</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>44711</v>
+        <v>76657</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-alicate-6-160mm-1000v-acero-cromovan-sica/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/bawms115-multimetro-medicion-autorrango-smart-1-rms/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>01TOO00220</t>
+          <t>01SIC23630</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Kit portaherramienta grande + cinto 50mm toolmen (TOOLMEN)</t>
+          <t>PINZA PELACABLES 6.5" CABLES DE 0.75 A 6MM SICA (SICA)</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>67456</v>
+        <v>25754</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-portaherramienta-grande-cinto-50mm-toolmen/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/380200-pinza-pelacables-65-pcables-de-075-a-6mm-sica/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>01TOO01010</t>
+          <t>01JAI00066</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Porta celular funda smart-phone grande hasta 160mm (TOOLMEN)</t>
+          <t>EST7280 ESTAÑO EN CARRETE 60/40 0.8MM 250GR -JA- (JA)</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>19802</v>
+        <v>42264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/porta-celular-funda-smartphone-grande-hasta-160mm/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/est7280-estanio-en-carrete-6040-08mm-250gr-ja/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>01USH00020</t>
+          <t>01NIP00040</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Dobladora de caños 3/4" una palanca con resorte adaptador para caños de 5/8"</t>
+          <t>PINZA PUNTA 145MM MANGO BICOLOR ACERO/VANADIO KNIPEX (KNIPEX)</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>109779</v>
+        <v>164894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/dobladora-de-canios-34-una-palanca-con-resorte-adaptador-para-canios-de-58/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-punta-145mm-mango-bicolor-acerovanadio-knipex/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>01ZOL04200</t>
+          <t>01NIP00018</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Pinza pelacable 0.2 a 6mm autoajustable - regulable 5 a 12mm</t>
+          <t>ALICATE PUNTA LARGA SEMI - REDONDA 160MM MANGO BICOLOR ACERO/VANADIO KNIPEX (KNIPEX)</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>124654</v>
+        <v>138145</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pelacable-02-a-6mm-autoajustable-regulable-5-a-12mm/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/alicate-punta-larga-semi-redonda-160mm-mango-bicolor-acerovanadio-knipex/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>01SIC23630</t>
+          <t>01BUL02252</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PINZA PELACABLES 6.5" CABLES DE 0.75 A 6MM SICA (SICA)</t>
+          <t>Alicate 7 aisl. Acero/carbono mango aislado serie 600 bulit</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>26125</v>
+        <v>18698</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/380200-pinza-pelacables-65-pcables-de-075-a-6mm-sica/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/alicate-7-aisl-acerocarbono-mango-aislado-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>01JAI00066</t>
+          <t>01BUL00135</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>EST7280 ESTAÑO EN CARRETE 60/40 0.8MM 250GR -JA- (JA)</t>
+          <t>KIT COMBO HERRAMIENTAS P/ELECTRICISTAS ECONOMICO DE 9 PIEZAS (BULIT)</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>42875</v>
+        <v>65801</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/est7280-estanio-en-carrete-6040-08mm-250gr-ja/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-combo-herramientas-pelectricistas-economico-de-9-piezas/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>01NIP00040</t>
+          <t>01BUL02280</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PINZA PUNTA 145MM MANGO BICOLOR ACERO/VANADIO KNIPEX (KNIPEX)</t>
+          <t>KIT - PINZA UNIVERSAL 6 + ALICATE 6 +PUNTA 6 SERIE 600 BULIT (BULIT)</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>167275</v>
+        <v>46936</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-punta-145mm-mango-bicolor-acerovanadio-knipex/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-pinza-universal-6-alicate-6-punta-6-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>01NIP00018</t>
+          <t>01SIC11526</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ALICATE PUNTA LARGA SEMI - REDONDA 160MM MANGO BICOLOR ACERO/VANADIO KNIPEX (KNIPEX)</t>
+          <t>KIT - 6 DESTORNILLADORES PLANOS Y PHILIPS + PINZA UNIVERSAL +PUNTA +ALICATE SICA (SICA)</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>140140</v>
+        <v>11058</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/alicate-punta-larga-semi-redonda-160mm-mango-bicolor-acerovanadio-knipex/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-6-destornilladores-planos-y-philips-pinza-universal-punta-alicate-sica/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>01BUL02252</t>
+          <t>01BUL02274</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Alicate 7 aisl. Acero/carbono mango aislado serie 600 bulit</t>
+          <t>SET 3 PINZAS ALICATE + UNIVERSAL +SEMI REDONDA 6" BULIT (BULIT)</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>18066</v>
+        <v>44597</v>
       </c>
       <c r="D381" t="inlineStr">
-        <is>
-          <t>https://electrocity.com.ar/productos/alicate-7-aisl-acerocarbono-mango-aislado-serie-600-bulit/?openNotificationDialog=true</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>01BUL00135</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>KIT COMBO HERRAMIENTAS P/ELECTRICISTAS ECONOMICO DE 9 PIEZAS (BULIT)</t>
-        </is>
-      </c>
-      <c r="C382" t="n">
-        <v>63576</v>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>https://electrocity.com.ar/productos/kit-combo-herramientas-pelectricistas-economico-de-9-piezas/?openNotificationDialog=true</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>01BUL02280</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>KIT - PINZA UNIVERSAL 6 + ALICATE 6 +PUNTA 6 SERIE 600 BULIT (BULIT)</t>
-        </is>
-      </c>
-      <c r="C383" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>https://electrocity.com.ar/productos/kit-pinza-universal-6-alicate-6-punta-6-serie-600-bulit/?openNotificationDialog=true</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>01SIC11526</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>KIT - 6 DESTORNILLADORES PLANOS Y PHILIPS + PINZA UNIVERSAL +PUNTA +ALICATE SICA (SICA)</t>
-        </is>
-      </c>
-      <c r="C384" t="n">
-        <v>98961</v>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>https://electrocity.com.ar/productos/kit-6-destornilladores-planos-y-philips-pinza-universal-punta-alicate-sica/?openNotificationDialog=true</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>01BUL02274</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>SET 3 PINZAS ALICATE + UNIVERSAL +SEMI REDONDA 6" BULIT (BULIT)</t>
-        </is>
-      </c>
-      <c r="C385" t="n">
-        <v>43089</v>
-      </c>
-      <c r="D385" t="inlineStr">
         <is>
           <t>https://electrocity.com.ar/productos/set-3-pinzas-alicate-universal-semi-redonda-6-bulit/?openNotificationDialog=true</t>
         </is>

--- a/media/price_lists/electrocity.xlsx
+++ b/media/price_lists/electrocity.xlsx
@@ -541,1200 +541,1200 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01BUL00308</t>
+          <t>01BAW06010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pelacable automático lateral serie 600 (BULIT)</t>
+          <t>Buscapolo inductivo detector de tension BAW sonido y luz</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39502</v>
+        <v>8932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pelacable-automatico-lateral-serie-600/</t>
+          <t>https://electrocity.com.ar/productos/buscapolo-inductivo-detector-de-tension-baw-sonido-y-luz/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01MIL00020</t>
+          <t>01BUL00308</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ROTOMARTILLO 24MM 800W SDS PLUS 3 MODOS 220V MILWAUKEE 5485-59A</t>
+          <t>Pelacable automático lateral serie 600 (BULIT)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>405679</v>
+        <v>39502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/rotomartillo-24mm-800w-sds-plus-3-modos-220v-milwaukee-548559a/</t>
+          <t>https://electrocity.com.ar/productos/pelacable-automatico-lateral-serie-600/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01HRT09040</t>
+          <t>01MIL00020</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pinzas Universal Corte Lateral Bahco</t>
+          <t>ROTOMARTILLO 24MM 800W SDS PLUS 3 MODOS 220V MILWAUKEE 5485-59A</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29895</v>
+        <v>405679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinzas-universal-corte-lateral-bahco/</t>
+          <t>https://electrocity.com.ar/productos/rotomartillo-24mm-800w-sds-plus-3-modos-220v-milwaukee-548559a/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01MIL00310</t>
+          <t>01HRT09040</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Set de Puntas de Alto Impacto con Mango Kit x 12 Milwaukee 4832-4507</t>
+          <t>Pinzas Universal Corte Lateral Bahco</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29917</v>
+        <v>29895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-puntas-de-alto-impacto-con-mango-kit-x-12-milwaukee-4832-4507/</t>
+          <t>https://electrocity.com.ar/productos/pinzas-universal-corte-lateral-bahco/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01BUL00300</t>
+          <t>01MIL00310</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pelacables automático frontal p/cables de 0.25 a 6mm2 (BULIT)</t>
+          <t>Set de Puntas de Alto Impacto con Mango Kit x 12 Milwaukee 4832-4507</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19182</v>
+        <v>29917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pelacables-automatico-frontal-pcables-de-025-a-6mm2/</t>
+          <t>https://electrocity.com.ar/productos/set-de-puntas-de-alto-impacto-con-mango-kit-x-12-milwaukee-4832-4507/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01HRT09100</t>
+          <t>01BUL00300</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Multi Herramienta Plegable De Aluminio 18 En 1 MTT121 (BAHCO)</t>
+          <t>Pelacables automático frontal p/cables de 0.25 a 6mm2 (BULIT)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>34328</v>
+        <v>19182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multi-herramienta-plegable-de-aluminio-18-en-1-mtt121-bahco/</t>
+          <t>https://electrocity.com.ar/productos/pelacables-automatico-frontal-pcables-de-025-a-6mm2/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01JAI00071</t>
+          <t>01HRT09100</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Soldador de estaño tipo lapiz 40w 220v (JA)</t>
+          <t>Multi Herramienta Plegable De Aluminio 18 En 1 MTT121 (BAHCO)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11930</v>
+        <v>34328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-40w-220v/</t>
+          <t>https://electrocity.com.ar/productos/multi-herramienta-plegable-de-aluminio-18-en-1-mtt121-bahco/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01VIY00055</t>
+          <t>01JAI00071</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica 15 mts 4mm viyilant</t>
+          <t>Soldador de estaño tipo lapiz 40w 220v (JA)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6350.4</v>
+        <v>11930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-15-mts-4mm-viyilant/</t>
+          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-40w-220v/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01JAI00060</t>
+          <t>01VIY00055</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EST7017 ESTAÑO EN TUBO 60/40 1MM 17GR -JA-</t>
+          <t>Cinta pasacable plástica 15 mts 4mm viyilant</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4483</v>
+        <v>6350.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/est7017-estanio-en-tubo-6040-1mm-17gr-ja/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-15-mts-4mm-viyilant/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01MIL00122</t>
+          <t>01JAI00060</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caja Modular con Puerta Frontal Packout Milwaukee 4822-8445</t>
+          <t>EST7017 ESTAÑO EN TUBO 60/40 1MM 17GR -JA-</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>528254</v>
+        <v>4483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/caja-modular-con-puerta-frontal-packout-milwaukee-4822-8445/</t>
+          <t>https://electrocity.com.ar/productos/est7017-estanio-en-tubo-6040-1mm-17gr-ja/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01HRT05128</t>
+          <t>01BUL02480</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Juego 2 Destornilladores Premium Blister P-3000/2h BAHCO</t>
+          <t>DES BP A DESTORNILLADOR BUSCAPOLO AISLADO 140MM PLANO 100 A 500V (BULIT)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16335</v>
+        <v>6679</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-2-destornilladores-premium-blister-p-3000-2h-bahco/</t>
+          <t>https://electrocity.com.ar/productos/des-bp-a-destornillador-buscapolo-aislado-140mm-plano-100-a-500v/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01JAI00402</t>
+          <t>01MIL00122</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Set herramientas 11 pzas aisladas 1000v c/valija (JA)</t>
+          <t>Caja Modular con Puerta Frontal Packout Milwaukee 4822-8445</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>60514</v>
+        <v>528254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-herramientas-11-pzas-aisladas-1000v-cvalija/</t>
+          <t>https://electrocity.com.ar/productos/caja-modular-con-puerta-frontal-packout-milwaukee-4822-8445/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01VIY00110</t>
+          <t>01HRT05128</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma acero ø4mm 20 metros</t>
+          <t>Juego 2 Destornilladores Premium Blister P-3000/2h BAHCO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20423</v>
+        <v>16335</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-20-metros/</t>
+          <t>https://electrocity.com.ar/productos/juego-2-destornilladores-premium-blister-p-3000-2h-bahco/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01MIL00614</t>
+          <t>01JAI00402</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Placa Compacta para Caja Packout Milwaukee 4822-8608</t>
+          <t>Set herramientas 11 pzas aisladas 1000v c/valija (JA)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>65711.5</v>
+        <v>60514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/placa-compacta-para-caja-packout-milwaukee-4822-8608-1sjqc/</t>
+          <t>https://electrocity.com.ar/productos/set-herramientas-11-pzas-aisladas-1000v-cvalija/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01BUL00080</t>
+          <t>01SIC06081</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Destornillador profesional #2x38mm punta phillips (BULIT)</t>
+          <t>Destornillador buscapolo chico ø3 140mm 100/250 vca (SICA)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9485</v>
+        <v>2363</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-2x38mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-buscapolo-chico-3-140mm-100250-vca/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01HRT06650</t>
+          <t>01VIY00105</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Punta de atornillar phillips 1/4 n°1 49mm p/taladro blister x 3unidades</t>
+          <t>Cinta pasacable plástica con alma acero ø4mm 15 metros</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7850</v>
+        <v>16000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-de-atornillar-phillips-14-n1-49mm-ptaladro-blister-3unidades/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-15-metros/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01SEG08010</t>
+          <t>01VIY00110</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guante tactil nylon - poliuretano talle 8 (TACTIL)</t>
+          <t>Cinta pasacable plástica con alma acero ø4mm 20 metros</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2050</v>
+        <v>20423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/guante-tactil-nylon-poliuretano-talle-8/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-20-metros/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01SIC06081</t>
+          <t>01MIL00614</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Destornillador buscapolo chico ø3 140mm 100/250 vca (SICA)</t>
+          <t>Placa Compacta para Caja Packout Milwaukee 4822-8608</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2363</v>
+        <v>65711.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-buscapolo-chico-3-140mm-100250-vca/</t>
+          <t>https://electrocity.com.ar/productos/placa-compacta-para-caja-packout-milwaukee-4822-8608-1sjqc/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01VIY00100</t>
+          <t>01BUL00080</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma acero ø4mm 10 metros</t>
+          <t>Destornillador profesional #2x38mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11630</v>
+        <v>9485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-10-metros/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-2x38mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01VIY00105</t>
+          <t>01HRT06650</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma acero ø4mm 15 metros</t>
+          <t>Punta de atornillar phillips 1/4 n°1 49mm p/taladro blister x 3unidades</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16000</v>
+        <v>7850</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-15-metros/</t>
+          <t>https://electrocity.com.ar/productos/punta-de-atornillar-phillips-14-n1-49mm-ptaladro-blister-3unidades/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>01BUL02480</t>
+          <t>01SEG08010</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DES BP A DESTORNILLADOR BUSCAPOLO AISLADO 140MM PLANO 100 A 500V (BULIT)</t>
+          <t>Guante tactil nylon - poliuretano talle 8 (TACTIL)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6679</v>
+        <v>2050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/des-bp-a-destornillador-buscapolo-aislado-140mm-plano-100-a-500v/</t>
+          <t>https://electrocity.com.ar/productos/guante-tactil-nylon-poliuretano-talle-8/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>01MIL00624</t>
+          <t>01VIY00100</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Combo Taladro Atornillador + Atornillador de Impacto M18 Milwaukee 2691-259A</t>
+          <t>Cinta pasacable plástica con alma acero ø4mm 10 metros</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1176739</v>
+        <v>11630</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-taladro-atornillador-atornillador-de-impacto-m18-milwaukee-2691-259a-sw3tn/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-10-metros/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>01MIL00636</t>
+          <t>01MIL00624</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Combo Taladro Percutor + Atornillador de Impacto M12 Milwaukee 2497-259A</t>
+          <t>Combo Taladro Atornillador + Atornillador de Impacto M18 Milwaukee 2691-259A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1306642</v>
+        <v>1176739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-taladro-percutor-atornillador-de-impacto-m12-milwaukee-2497-259a-14ceb/</t>
+          <t>https://electrocity.com.ar/productos/combo-taladro-atornillador-atornillador-de-impacto-m18-milwaukee-2691-259a-sw3tn/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01HRT09050</t>
+          <t>01MIL00636</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pinza Alicate Corte Diagonal Bahco</t>
+          <t>Combo Taladro Percutor + Atornillador de Impacto M12 Milwaukee 2497-259A</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23653</v>
+        <v>1306642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-alicate-corte-diagonal-bahco/</t>
+          <t>https://electrocity.com.ar/productos/combo-taladro-percutor-atornillador-de-impacto-m12-milwaukee-2497-259a-14ceb/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01MIL00603</t>
+          <t>01HRT09050</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amoladora Inalámbrica Milwaukee 2880-20 M18 4 1/2</t>
+          <t>Pinza Alicate Corte Diagonal Bahco</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1165180</v>
+        <v>23653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/amoladora-inalambrica-milwaukee-2880-20-m18-4-1-2-wosid/</t>
+          <t>https://electrocity.com.ar/productos/pinza-alicate-corte-diagonal-bahco/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>01BUL00064</t>
+          <t>01MIL00603</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SET DE 6 DESTORNILLADORES AISLADOS 1000V PUNTA RECTA Y PHILLIPS (BULIT)</t>
+          <t>Amoladora Inalámbrica Milwaukee 2880-20 M18 4 1/2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>49814</v>
+        <v>1165180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-aislados-1000v-punta-recta-y-phillips/</t>
+          <t>https://electrocity.com.ar/productos/amoladora-inalambrica-milwaukee-2880-20-m18-4-1-2-wosid/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01BUL00127</t>
+          <t>01BUL00064</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Set de llaves allen de 9 piezas en mm (BULIT)</t>
+          <t>SET DE 6 DESTORNILLADORES AISLADOS 1000V PUNTA RECTA Y PHILLIPS (BULIT)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>20403</v>
+        <v>49814</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-llaves-allen-de-9-piezas-en-mm/</t>
+          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-aislados-1000v-punta-recta-y-phillips/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>01SIC06080</t>
+          <t>01BUL00127</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Destornillador buscapolo grande ø3.5 190mm 100/250 vca</t>
+          <t>Set de llaves allen de 9 piezas en mm (BULIT)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3008</v>
+        <v>20403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-buscapolo-grande-35-190mm-100250-vca/</t>
+          <t>https://electrocity.com.ar/productos/set-de-llaves-allen-de-9-piezas-en-mm/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>01JAI00076</t>
+          <t>01SIC06080</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BASE SOPORTE PARA SOLDADOR</t>
+          <t>Destornillador buscapolo grande ø3.5 190mm 100/250 vca</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7044</v>
+        <v>3008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soporte-multiproposito-con-lupa-ja/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-buscapolo-grande-35-190mm-100250-vca/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01MIL00040</t>
+          <t>01JAI00076</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TALADRO C/PERCUSION ATORNILLADOR 13MM 680W 220V 3000RPM MILWAUKEE 5374-59A</t>
+          <t>BASE SOPORTE PARA SOLDADOR</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>248041</v>
+        <v>7044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-cpercusion-atornillador-13mm-680w-220v-3000rpm-milwaukee-537459a/</t>
+          <t>https://electrocity.com.ar/productos/soporte-multiproposito-con-lupa-ja/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01MIL00601</t>
+          <t>01MIL00040</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ATORNILLADOR TALADRO MILWAUKEE 2606-20 M18 3MM 1800RPM</t>
+          <t>TALADRO C/PERCUSION ATORNILLADOR 13MM 680W 220V 3000RPM MILWAUKEE 5374-59A</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>691499</v>
+        <v>248041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/atornillador-taladro-sin-baterias-13mm-1800rpm-milwaukee-260620/</t>
+          <t>https://electrocity.com.ar/productos/taladro-cpercusion-atornillador-13mm-680w-220v-3000rpm-milwaukee-537459a/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01MIL00609</t>
+          <t>01MIL00601</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Batería Compacta RedLithium 3.0 M12 Milwaukee 4811-2430</t>
+          <t>ATORNILLADOR TALADRO MILWAUKEE 2606-20 M18 3MM 1800RPM</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>131426</v>
+        <v>691499</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-compacta-redlithium-3-0-m12-milwaukee-4811-2430-1f8gs/</t>
+          <t>https://electrocity.com.ar/productos/atornillador-taladro-sin-baterias-13mm-1800rpm-milwaukee-260620/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01MIL00615</t>
+          <t>01MIL00609</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Placa de Pared Compacta Packout Milwaukee 4822-8496</t>
+          <t>Batería Compacta RedLithium 3.0 M12 Milwaukee 4811-2430</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>90294.39999999999</v>
+        <v>131426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/placa-de-pared-compacta-packout-milwaukee-4822-8496-1rr49/</t>
+          <t>https://electrocity.com.ar/productos/bateria-compacta-redlithium-3-0-m12-milwaukee-4811-2430-1f8gs/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>01MIL00212</t>
+          <t>01MIL00615</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bateria Milwaukee M18 De Litio 3.0 Ah 4811-1835</t>
+          <t>Placa de Pared Compacta Packout Milwaukee 4822-8496</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>232277</v>
+        <v>90294.39999999999</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-milwaukee-m18-de-litio-3-0-ah-4811-1835-cyiny/</t>
+          <t>https://electrocity.com.ar/productos/placa-de-pared-compacta-packout-milwaukee-4822-8496-1rr49/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>01HRT09046</t>
+          <t>01MIL00212</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pinza Alicate Punta Plana Larga Bahco</t>
+          <t>Bateria Milwaukee M18 De Litio 3.0 Ah 4811-1835</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>28983</v>
+        <v>232277</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-alicate-punta-plana-larga-bahco/</t>
+          <t>https://electrocity.com.ar/productos/bateria-milwaukee-m18-de-litio-3-0-ah-4811-1835-cyiny/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>01MIL00072</t>
+          <t>01HRT09046</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Atornillador Hexagonal 12v con Cargador y 2 Baterías Milwaukee 2401-259A</t>
+          <t>Pinza Alicate Punta Plana Larga Bahco</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>474615</v>
+        <v>28983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/atornillador-hexagonal-12v-con-cargador-y-2-baterias-milwaukee-2401-259a/</t>
+          <t>https://electrocity.com.ar/productos/pinza-alicate-punta-plana-larga-bahco/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>01MIL00607</t>
+          <t>01MIL00072</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ATORNILLADOR DE IMPACTO MILWAUKEE 3453-20 M12 FUEL</t>
+          <t>Atornillador Hexagonal 12v con Cargador y 2 Baterías Milwaukee 2401-259A</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>518374</v>
+        <v>474615</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/atornillador-de-impacto-milwaukee-3453-20-m12-fuel-137ol/</t>
+          <t>https://electrocity.com.ar/productos/atornillador-hexagonal-12v-con-cargador-y-2-baterias-milwaukee-2401-259a/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01BUL00256</t>
+          <t>01MIL00607</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Martillo galponero con mango de goma (BULIT)</t>
+          <t>ATORNILLADOR DE IMPACTO MILWAUKEE 3453-20 M12 FUEL</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>26496</v>
+        <v>518374</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/martillo-galponero-con-mango-de-goma/</t>
+          <t>https://electrocity.com.ar/productos/atornillador-de-impacto-milwaukee-3453-20-m12-fuel-137ol/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01BUL00465</t>
+          <t>01BUL00256</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Repuesto hoja para cutter profesional grande ( x5 unidades )</t>
+          <t>Martillo galponero con mango de goma (BULIT)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3299</v>
+        <v>26496</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/repuesto-hoja-para-cutter-profesional-grande-x5-unidades-/</t>
+          <t>https://electrocity.com.ar/productos/martillo-galponero-con-mango-de-goma/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01BUL01650</t>
+          <t>01BUL00456</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Remachadora uso intensivo serie 500 bulit (BULIT)</t>
+          <t>Cutter navaja con repuestos serie 600 (BULIT)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>29404</v>
+        <v>24716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/remachadora-uso-intensivo-serie-500-bulit/</t>
+          <t>https://electrocity.com.ar/productos/cutter-navaja-con-repuestos-serie-600/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>01BUL02266</t>
+          <t>01BUL00465</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pinza pta.sem.red. curva 6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Repuesto hoja para cutter profesional grande ( x5 unidades )</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12815</v>
+        <v>3299</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-ptasemred-curva-6-acerocarbono-serie-600-bulit/</t>
+          <t>https://electrocity.com.ar/productos/repuesto-hoja-para-cutter-profesional-grande-x5-unidades-/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>01JAI00385</t>
+          <t>01BUL01650</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Set destornilladores 6 pzas 1000v aislados (JA)</t>
+          <t>Remachadora uso intensivo serie 500 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>21644</v>
+        <v>29404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-destornilladores-6-pzas-1000v-aislados/</t>
+          <t>https://electrocity.com.ar/productos/remachadora-uso-intensivo-serie-500-bulit/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>01SIC00090</t>
+          <t>01BUL02068</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pinza amperometrica digital con termocupla SICA</t>
+          <t>Kit llaves criquet juego de 5 llaves c/20 medidas serie 700 (BULIT)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>78587</v>
+        <v>72308.7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-con-termocupla-sica/</t>
+          <t>https://electrocity.com.ar/productos/kit-llaves-criquet-juego-de-5-llaves-c20-medidas-serie-700/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01VIY00050</t>
+          <t>01BUL02266</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica 10 mts 4mm</t>
+          <t>Pinza pta.sem.red. curva 6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6241</v>
+        <v>12815</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-10-mts-4mm/</t>
+          <t>https://electrocity.com.ar/productos/pinza-ptasemred-curva-6-acerocarbono-serie-600-bulit/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>01JAI00306</t>
+          <t>01JAI00385</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TESTER MULTIMETRO DIGITAL PROFESIONAL 600CC/CA C/BUZZ. DIODO Y TRANS. S/BAT.9V -JA- (JA)</t>
+          <t>Set destornilladores 6 pzas 1000v aislados (JA)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>15088</v>
+        <v>21644</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-profesional-600ccca-cbuzz-diodo-y-trans-sbat9v-ja/</t>
+          <t>https://electrocity.com.ar/productos/set-destornilladores-6-pzas-1000v-aislados/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01MIL00210</t>
+          <t>01VIY00050</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BATERIA M18 18v 2Ah MILWAUKEE (MILWAUKEE)</t>
+          <t>Cinta pasacable plástica 10 mts 4mm</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>184719</v>
+        <v>6241</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-m18-18v-2ah-milwaukee/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-10-mts-4mm/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01BUL00025</t>
+          <t>01JAI00306</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cinta metrica c/freno metálica 3mt. x 16mm (BULIT)</t>
+          <t>TESTER MULTIMETRO DIGITAL PROFESIONAL 600CC/CA C/BUZZ. DIODO Y TRANS. S/BAT.9V -JA- (JA)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>12848</v>
+        <v>15088</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-cfreno-metalica-3mt-16mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-profesional-600ccca-cbuzz-diodo-y-trans-sbat9v-ja/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01MIL00634</t>
+          <t>01MIL00210</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Taladro Atornillador M18 Milwaukee 2606-20</t>
+          <t>BATERIA M18 18v 2Ah MILWAUKEE (MILWAUKEE)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>238452</v>
+        <v>184719</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-atornillador-m18-milwaukee-2606-20-577re/</t>
+          <t>https://electrocity.com.ar/productos/bateria-m18-18v-2ah-milwaukee/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01MIL00629</t>
+          <t>01BUL00025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sierra Sable Inalámbrica Batería 12v Milwaukee 2420-259A</t>
+          <t>Cinta metrica c/freno metálica 3mt. x 16mm (BULIT)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>446191.35</v>
+        <v>12848</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sierra-sable-inalambrica-bateria-12v-milwaukee-2420-259a-dc95c/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-cfreno-metalica-3mt-16mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01MIL00631</t>
+          <t>01MIL00634</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Batería M12 XC 3Ah RedLithuim Milwaukee 4811-2402</t>
+          <t>Taladro Atornillador M18 Milwaukee 2606-20</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>128733.3</v>
+        <v>238452</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-m12-xc-3ah-redlithuim-milwaukee-4811-2402-1fe5j/</t>
+          <t>https://electrocity.com.ar/productos/taladro-atornillador-m18-milwaukee-2606-20-577re/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01MIL00211</t>
+          <t>01MIL00629</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Batería M12 2ah Litio para Herramientas Milwaukee 4811-2420</t>
+          <t>Sierra Sable Inalámbrica Batería 12v Milwaukee 2420-259A</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>89699.39999999999</v>
+        <v>446191.35</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-m12-2ah-litio-para-herramientas-milwaukee-4811-2420-va1z1/</t>
+          <t>https://electrocity.com.ar/productos/sierra-sable-inalambrica-bateria-12v-milwaukee-2420-259a-dc95c/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01HRT09026</t>
+          <t>01MIL00631</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pinza Universal Aislación 1000v Bahco</t>
+          <t>Batería M12 XC 3Ah RedLithuim Milwaukee 4811-2402</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>58800</v>
+        <v>128733.3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-aislacion-1000v-bahco/</t>
+          <t>https://electrocity.com.ar/productos/bateria-m12-xc-3ah-redlithuim-milwaukee-4811-2402-1fe5j/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01HRT09016</t>
+          <t>01MIL00211</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kit Destornilladores x 5 Piezas 1000v Bahco 800IEC/5-RN</t>
+          <t>Batería M12 2ah Litio para Herramientas Milwaukee 4811-2420</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>63573</v>
+        <v>89699.39999999999</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-destornilladores-x-5-piezas-1000v-bahco-800iec-5-rn/</t>
+          <t>https://electrocity.com.ar/productos/bateria-m12-2ah-litio-para-herramientas-milwaukee-4811-2420-va1z1/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01MIL00350</t>
+          <t>01HRT09026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Set de Destornilladores Premium 6 Piezas Milwaukee 4822-2706</t>
+          <t>Pinza Universal Aislación 1000v Bahco</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>62036</v>
+        <v>58800</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-destornilladores-premium-6-piezas-milwaukee-4822-2706/</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-aislacion-1000v-bahco/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>01MIL00303</t>
+          <t>01HRT09016</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Punta Atornillador Phillips Impacto Ph2 x 50mm Kit x 5 Milwaukee 4832-4602</t>
+          <t>Kit Destornilladores x 5 Piezas 1000v Bahco 800IEC/5-RN</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11885</v>
+        <v>63573</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph2-x-50mm-kit-x-5-milwaukee-4832-4602/</t>
+          <t>https://electrocity.com.ar/productos/kit-destornilladores-x-5-piezas-1000v-bahco-800iec-5-rn/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>01BUL00030</t>
+          <t>01MIL00350</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mini arco de sierra 6 -serie 200- (BULIT)</t>
+          <t>Set de Destornilladores Premium 6 Piezas Milwaukee 4822-2706</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>14892</v>
+        <v>62036</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mini-arco-de-sierra-6-serie-200/</t>
+          <t>https://electrocity.com.ar/productos/set-de-destornilladores-premium-6-piezas-milwaukee-4822-2706/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>01BUL00456</t>
+          <t>01MIL00303</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cutter navaja con repuestos serie 600 (BULIT)</t>
+          <t>Punta Atornillador Phillips Impacto Ph2 x 50mm Kit x 5 Milwaukee 4832-4602</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>24716</v>
+        <v>11885</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-navaja-con-repuestos-serie-600/</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph2-x-50mm-kit-x-5-milwaukee-4832-4602/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>01BUL00464</t>
+          <t>01BUL00030</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hojas de repuesto p/cutter profesional serie 800 (BULIT)</t>
+          <t>Mini arco de sierra 6 -serie 200- (BULIT)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6594</v>
+        <v>14892</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/hojas-de-repuesto-pcutter-profesional-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/mini-arco-de-sierra-6-serie-200/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01BUL00891</t>
+          <t>01BUL00464</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 segmentado 115mm bulit (BULIT)</t>
+          <t>Hojas de repuesto p/cutter profesional serie 800 (BULIT)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10905</v>
+        <v>6594</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-segmentado-115mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/hojas-de-repuesto-pcutter-profesional-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01BUL02170</t>
+          <t>01BUL00891</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Llave ajustable 6 cromada c/mango ergonomico antideslizante (BULIT)</t>
+          <t>Disco diamantado serie 400 segmentado 115mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>18355</v>
+        <v>10905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-ajustable-6-cromada-cmango-ergonomico-antideslizante/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-segmentado-115mm-bulit/</t>
         </is>
       </c>
     </row>
@@ -1881,6020 +1881,6020 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>01SIC00104</t>
+          <t>01BAW10950</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Detector indicador luminoso de voltaje catiii 70-1000vca (SICA)</t>
+          <t>Juego de puntas de prueba para tester (BAW)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>22990</v>
+        <v>4992</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/detector-indicador-luminoso-de-voltaje-catiii-701000vca/</t>
+          <t>https://electrocity.com.ar/productos/juego-de-puntas-de-prueba-para-tester/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>01BAW10950</t>
+          <t>01BAW11282</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Juego de puntas de prueba para tester (BAW)</t>
+          <t>SM852B SECUENCIMETRO COMPROBADOR DE ROTACION DE FASES BAW (BAW)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4992</v>
+        <v>60304</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-de-puntas-de-prueba-para-tester/</t>
+          <t>https://electrocity.com.ar/productos/sm852b-secuencimetro-comprobador-de-rotacion-de-fases-baw/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>01BAW11282</t>
+          <t>01BAW11285</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SM852B SECUENCIMETRO COMPROBADOR DE ROTACION DE FASES BAW (BAW)</t>
+          <t>TÉLEMETRO DIGITAL LASER DISTANCIA-AREA-VOLUMEN LCD BAWTL40M (BAW)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>60304</v>
+        <v>65965</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sm852b-secuencimetro-comprobador-de-rotacion-de-fases-baw/</t>
+          <t>https://electrocity.com.ar/productos/telemetro-digital-laser-distanciaareavolumen-lcd-bawtl40m/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>01BAW11285</t>
+          <t>01JAI00075</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TÉLEMETRO DIGITAL LASER DISTANCIA-AREA-VOLUMEN LCD BAWTL40M (BAW)</t>
+          <t>DESOLDADOR A PISTON METALICO CHICO JA (JA)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>65965</v>
+        <v>6532</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/telemetro-digital-laser-distanciaareavolumen-lcd-bawtl40m/</t>
+          <t>https://electrocity.com.ar/productos/desoldador-a-piston-metalico-chico-ja/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>01BUL02090</t>
+          <t>01BUL00028</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NVL S6 3B 40 A NIVEL 3 BURBUJAS 400MM ALUMINIO BULIT (BULIT)</t>
+          <t>Cinta metrica doble freno metálica 7.5mt. x 25mm (BULIT)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>27841</v>
+        <v>34669</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/nvl-s6-3b-40-a-nivel-3-burbujas-400mm-aluminio-bulit/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-doble-freno-metalica-75mt-25mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>01JAI00075</t>
+          <t>01BUL00052</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DESOLDADOR A PISTON METALICO CHICO JA (JA)</t>
+          <t>Destornillador aislado 1000v phillips cromo-vanadio 2 x 150mm serie 800 (BULIT)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>6532</v>
+        <v>10348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/desoldador-a-piston-metalico-chico-ja/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-phillips-cromovanadio-2-150mm-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>01BUL00028</t>
+          <t>01MIL00635</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cinta metrica doble freno metálica 7.5mt. x 25mm (BULIT)</t>
+          <t>Llave Criquet de Impacto 1/2" M12 Fuel Milwaukee 2565-20</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>34669</v>
+        <v>996042</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-doble-freno-metalica-75mt-25mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/llave-criquet-de-impacto-1-2-m12-fuel-milwaukee-2565-20-uiat6/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>01BUL00052</t>
+          <t>01MIL00213</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v phillips cromo-vanadio 2 x 150mm serie 800 (BULIT)</t>
+          <t>Súper Cargador Simultáneo Doble Compartimento M18 Milwaukee 48-59-1859A</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10348</v>
+        <v>667054.5</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-phillips-cromovanadio-2-150mm-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/super-cargador-simultaneo-doble-compartimento-m18-milwaukee-48-59-1859a-rf8s4/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>01MIL00635</t>
+          <t>01MIL00613</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Llave Criquet de Impacto 1/2" M12 Fuel Milwaukee 2565-20</t>
+          <t>Soporte para Baterías M18 Packout Milwaukee 4822-8603</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>996042</v>
+        <v>62339</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-criquet-de-impacto-1-2-m12-fuel-milwaukee-2565-20-uiat6/</t>
+          <t>https://electrocity.com.ar/productos/soporte-para-baterias-m18-packout-milwaukee-4822-8603-1f31p/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>01MIL00213</t>
+          <t>01BLO00026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Súper Cargador Simultáneo Doble Compartimento M18 Milwaukee 48-59-1859A</t>
+          <t>Bloqueador Eléctrico a Tornillo Universal Blook RTET600S-M</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>667054.5</v>
+        <v>22590</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/super-cargador-simultaneo-doble-compartimento-m18-milwaukee-48-59-1859a-rf8s4/</t>
+          <t>https://electrocity.com.ar/productos/bloqueador-electrico-a-tornillo-universal-blook-rtet600s-m-h7v6u/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>01MIL00613</t>
+          <t>01HRT09076</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Soporte para Baterías M18 Packout Milwaukee 4822-8603</t>
+          <t>Destornillador Perillero Phillips PH0 60 mm Bahco KR3000/50</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>62339</v>
+        <v>5912</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soporte-para-baterias-m18-packout-milwaukee-4822-8603-1f31p/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-perillero-phillips-ph0-60-mm-bahco-kr3000-50/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01BLO00026</t>
+          <t>01HRT09022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bloqueador Eléctrico a Tornillo Universal Blook RTET600S-M</t>
+          <t>Pinza Punta Semiredonda 6 Aislada 1000v Bahco 2430S-160A-RN</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>22590</v>
+        <v>61765</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bloqueador-electrico-a-tornillo-universal-blook-rtet600s-m-h7v6u/</t>
+          <t>https://electrocity.com.ar/productos/pinza-punta-semiredonda-6-aislada-1000v-bahco-2430s-160a-rn/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>01HRT09076</t>
+          <t>01HRT09020</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Destornillador Perillero Phillips PH0 60 mm Bahco KR3000/50</t>
+          <t>Pinza Alicate 7 Aislación 1000v Bahco 2151S-7A-RN</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5912</v>
+        <v>75834</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-perillero-phillips-ph0-60-mm-bahco-kr3000-50/</t>
+          <t>https://electrocity.com.ar/productos/pinza-alicate-7-aislacion-1000v-bahco-2151s-7a-rn/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>01HRT09020</t>
+          <t>01MIL00304</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pinza Alicate 7 Aislación 1000v Bahco 2151S-7A-RN</t>
+          <t>Punta Atornillador Phillips Impacto Ph3 x 25mm Kit x 2 Milwaukee 4832-4413</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>75834</v>
+        <v>3231</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-alicate-7-aislacion-1000v-bahco-2151s-7a-rn/</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph3-x-25mm-kit-x-2-milwaukee-4832-4413/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>01MIL00304</t>
+          <t>01MIL00302</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Punta Atornillador Phillips Impacto Ph3 x 25mm Kit x 2 Milwaukee 4832-4413</t>
+          <t>Punta Atornillador Phillips Impacto Ph2 x 25mm Kit x 5 Milwaukee 4832-4601</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3231</v>
+        <v>6111</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph3-x-25mm-kit-x-2-milwaukee-4832-4413/</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph2-x-25mm-kit-x-5-milwaukee-4832-4601/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01MIL00302</t>
+          <t>01MIL00064</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Punta Atornillador Phillips Impacto Ph2 x 25mm Kit x 5 Milwaukee 4832-4601</t>
+          <t>TALADRO PERCUTOR 12V C/CARGADOR + 2 BATERIAS MILWAUKEE 2408-259A</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6111</v>
+        <v>627298</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph2-x-25mm-kit-x-5-milwaukee-4832-4601/</t>
+          <t>https://electrocity.com.ar/productos/taladro-percutor-12v-c-cargador-2-baterias-milwaukee-2408-259a/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>01MIL00064</t>
+          <t>01HRT05126</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TALADRO PERCUTOR 12V C/CARGADOR + 2 BATERIAS MILWAUKEE 2408-259A</t>
+          <t>Juego Destornilladores 12 Piezas 3000/12h (BAHCO)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>627298</v>
+        <v>81079</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-percutor-12v-c-cargador-2-baterias-milwaukee-2408-259a/</t>
+          <t>https://electrocity.com.ar/productos/juego-destornilladores-12-piezas-3000-12h-bahco/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>01HRT05126</t>
+          <t>01BUL00063</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Juego Destornilladores 12 Piezas 3000/12h (BAHCO)</t>
+          <t>SET DE 3 DESTORNILLADORES AISLADOS 1000V PUNTA RECTA (BULIT)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>81079</v>
+        <v>24608</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-destornilladores-12-piezas-3000-12h-bahco/</t>
+          <t>https://electrocity.com.ar/productos/set-de-3-destornilladores-aislados-1000v-punta-recta/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>01BUL00063</t>
+          <t>01BUL00074</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SET DE 3 DESTORNILLADORES AISLADOS 1000V PUNTA RECTA (BULIT)</t>
+          <t>Destornillador profesional #0x75mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>24608</v>
+        <v>4834</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-3-destornilladores-aislados-1000v-punta-recta/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-0x75mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>01BUL00074</t>
+          <t>01BUL00082</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Destornillador profesional #0x75mm punta phillips (BULIT)</t>
+          <t>Destornillador profesional #1x300mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4834</v>
+        <v>9580</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-0x75mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-1x300mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>01BUL00082</t>
+          <t>01BUL00100</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Destornillador profesional #1x300mm punta phillips (BULIT)</t>
+          <t>Destornillador profesional #6x150mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9580</v>
+        <v>11559</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-1x300mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-6x150mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>01BUL00100</t>
+          <t>01BUL00128</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Destornillador profesional #6x150mm punta plana (BULIT)</t>
+          <t>Set de llaves allen de 9 piezas en pulgadas (BULIT)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11559</v>
+        <v>20403</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-6x150mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/set-de-llaves-allen-de-9-piezas-en-pulgadas/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>01BUL00128</t>
+          <t>01BUL00694</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Set de llaves allen de 9 piezas en pulgadas (BULIT)</t>
+          <t>Alicate de corte frontal de precision de 45 p/artesanias y electrónica (BULIT)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>20403</v>
+        <v>11295</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-llaves-allen-de-9-piezas-en-pulgadas/</t>
+          <t>https://electrocity.com.ar/productos/alicate-de-corte-frontal-de-precision-de-45-partesanias-y-electronica/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>01BUL00694</t>
+          <t>01BUL00782</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Alicate de corte frontal de precision de 45 p/artesanias y electrónica (BULIT)</t>
+          <t>Pinza pico de loro cromada acero 6 (BULIT)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11295</v>
+        <v>18452</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/alicate-de-corte-frontal-de-precision-de-45-partesanias-y-electronica/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pico-de-loro-cromada-acero-6/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>01BUL00780</t>
+          <t>01BUL00808</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pinza pico de loro profesional de 10 serie 700 (BULIT)</t>
+          <t>Pistola encoladora dosificadora de pegamento 30w profesional (SUPRABOND)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>33794</v>
+        <v>74796</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pico-de-loro-profesional-de-10-serie-700/</t>
+          <t>https://electrocity.com.ar/productos/pistola-encoladora-dosificadora-de-pegamento-30w-profesional/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>01BUL00782</t>
+          <t>01BUL00810</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pinza pico de loro cromada acero 6 (BULIT)</t>
+          <t>Pistola dosificadora de pegamento 40w 220v c/pico aislante (SUPRABOND)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>18452</v>
+        <v>30176</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pico-de-loro-cromada-acero-6/</t>
+          <t>https://electrocity.com.ar/productos/pistola-dosificadora-de-pegamento-40w-220v-cpico-aislante/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>01BUL00808</t>
+          <t>01BUL00892</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pistola encoladora dosificadora de pegamento 30w profesional (SUPRABOND)</t>
+          <t>Disco diamantado serie 400 turbo 115mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>74796</v>
+        <v>12890</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-encoladora-dosificadora-de-pegamento-30w-profesional/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-115mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>01BUL00810</t>
+          <t>01BUL01625</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pistola dosificadora de pegamento 40w 220v c/pico aislante (SUPRABOND)</t>
+          <t>KIT 3 LIMAS DE 8 ENTREFINAS ACERO FORJADO PLANA + REDONDA + MEDIA CAÑA MANGO ERGONOMICO</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>30176</v>
+        <v>47986</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-dosificadora-de-pegamento-40w-220v-cpico-aislante/</t>
+          <t>https://electrocity.com.ar/productos/kit-3-limas-de-8-entrefinas-acero-forjado-plana-redonda-media-cania-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>01BUL00892</t>
+          <t>01BUL01720</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 turbo 115mm bulit (BULIT)</t>
+          <t>Llave p/caños con mordazas 1 c/tope seguridad</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>12890</v>
+        <v>32930</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-115mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/llave-pcanios-con-mordazas-1-ctope-seguridad/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>01BUL01625</t>
+          <t>01BUL01989</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KIT 3 LIMAS DE 8 ENTREFINAS ACERO FORJADO PLANA + REDONDA + MEDIA CAÑA MANGO ERGONOMICO</t>
+          <t>Set de llaves tipo t de 16 unidades bulit</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>47986</v>
+        <v>110298</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-3-limas-de-8-entrefinas-acero-forjado-plana-redonda-media-cania-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/set-de-llaves-tipo-t-de-16-unidades-bulit/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>01BUL01720</t>
+          <t>01EXP00001</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Llave p/caños con mordazas 1 c/tope seguridad</t>
+          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 10 metros c/porta-pasacable</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>32930</v>
+        <v>61550</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-pcanios-con-mordazas-1-ctope-seguridad/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-10-metros-cportapasacable/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>01BUL02068</t>
+          <t>01HRT04715</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kit llaves criquet juego de 5 llaves c/20 medidas serie 700 (BULIT)</t>
+          <t>Pinza semi-automatica p/terminales desnudos hasta 10mm</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>72308.7</v>
+        <v>163043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-llaves-criquet-juego-de-5-llaves-c20-medidas-serie-700/</t>
+          <t>https://electrocity.com.ar/productos/pinza-semiautomatica-pterminales-desnudos-hasta-10mm/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>01EXP00001</t>
+          <t>01HRT05105</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 10 metros c/porta-pasacable</t>
+          <t>Destornillador plano standard chico 5.5 x 125mm (BAHCO)</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>53857</v>
+        <v>7567</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-10-metros-cportapasacable/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-plano-standard-chico-55-125mm/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>01HRT04715</t>
+          <t>01HRT05106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Pinza semi-automatica p/terminales desnudos hasta 10mm</t>
+          <t>Destornillador plano standard chico 6.5 x 150mm (BAHCO)</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>163043</v>
+        <v>7567</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-semiautomatica-pterminales-desnudos-hasta-10mm/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-plano-standard-chico-65-150mm/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01HRT05105</t>
+          <t>01HRT05110</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Destornillador plano standard chico 5.5 x 125mm (BAHCO)</t>
+          <t>Destornillador phillips standard chico 3 x 75mm (BAHCO)</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7567</v>
+        <v>6236</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-plano-standard-chico-55-125mm/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-phillips-standard-chico-3-75mm/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01HRT05106</t>
+          <t>01HRT05600</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Destornillador plano standard chico 6.5 x 150mm (BAHCO)</t>
+          <t>Sierra copa bimetálica traspasadora hss ø19mm 3/4</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7567</v>
+        <v>9778</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-plano-standard-chico-65-150mm/</t>
+          <t>https://electrocity.com.ar/productos/sierra-copa-bimetalica-traspasadora-hss-19mm-34/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01HRT05110</t>
+          <t>01HRT05625</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Destornillador phillips standard chico 3 x 75mm (BAHCO)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø51mm 2</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6236</v>
+        <v>24359</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-phillips-standard-chico-3-75mm/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-51mm-2/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>01HRT05600</t>
+          <t>01HRT05628</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sierra copa bimetálica traspasadora hss ø19mm 3/4</t>
+          <t>Mecha copa bimetálica traspasadora hss ø79mm 3 1/8</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9778</v>
+        <v>37509</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sierra-copa-bimetalica-traspasadora-hss-19mm-34/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-79mm-3-18/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01HRT05625</t>
+          <t>01HRT05630</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø51mm 2</t>
+          <t>Soporte para sierra de copa bimtalica traspasadora de 14 a 30mm 3/8 (SIN-PAR)</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>24359</v>
+        <v>21494</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-51mm-2/</t>
+          <t>https://electrocity.com.ar/productos/soporte-para-sierra-de-copa-bimtalica-traspasadora-de-14-a-30mm-38/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>01HRT05628</t>
+          <t>01HRT05635</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø79mm 3 1/8</t>
+          <t>Soporte para sierra de copa bimtalica traspasadora de 33 a 152mm 1/2 (IMPORTADO)</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>37509</v>
+        <v>28237</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-79mm-3-18/</t>
+          <t>https://electrocity.com.ar/productos/soporte-para-sierra-de-copa-bimtalica-traspasadora-de-33-a-152mm-12/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>01HRT05630</t>
+          <t>01INS00280</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Soporte para sierra de copa bimtalica traspasadora de 14 a 30mm 3/8 (SIN-PAR)</t>
+          <t>Detector comprobador electronico luminoso sonoro 90/1000v 1ac-a1-ii-5pk (FLUKE)</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>21494</v>
+        <v>135797</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soporte-para-sierra-de-copa-bimtalica-traspasadora-de-14-a-30mm-38/</t>
+          <t>https://electrocity.com.ar/productos/detector-comprobador-electronico-luminoso-sonoro-901000v-1aca1ii5pk/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>01HRT05635</t>
+          <t>01JAI00072</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Soporte para sierra de copa bimtalica traspasadora de 33 a 152mm 1/2 (IMPORTADO)</t>
+          <t>Soldador de estaño tipo lapiz 60w 220v (JA)</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>28237</v>
+        <v>13041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soporte-para-sierra-de-copa-bimtalica-traspasadora-de-33-a-152mm-12/</t>
+          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-60w-220v/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>01INS00015</t>
+          <t>01RED04062</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Multimetro digital 600v + frecuencia + diodo fluke-107 esp (FLUKE)</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø10MM 160MM LARGO</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>523386</v>
+        <v>6514</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-digital-600v-frecuencia-diodo-fluke107-esp/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-10mm-160mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01INS00280</t>
+          <t>01RED04064</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Detector comprobador electronico luminoso sonoro 90/1000v 1ac-a1-ii-5pk (FLUKE)</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø12MM 160MM LARGO</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>135797</v>
+        <v>9086</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/detector-comprobador-electronico-luminoso-sonoro-901000v-1aca1ii5pk/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-12mm-160mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01JAI00072</t>
+          <t>01RED04066</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Soldador de estaño tipo lapiz 60w 220v (JA)</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø20MM 460MM LARGO</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>13041</v>
+        <v>45097</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-60w-220v/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-20mm-460mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>01RED04062</t>
+          <t>01SIC00091</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø10MM 160MM LARGO</t>
+          <t>Multimetro digital 600v con termocupla SICA</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6514</v>
+        <v>40804</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-10mm-160mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-digital-600v-con-termocupla-sica/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>01RED04064</t>
+          <t>01SIC00100</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø12MM 160MM LARGO</t>
+          <t>Detector 3 en 1 - detección de tabiques metal y tensión- SICA</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>9086</v>
+        <v>44681</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-12mm-160mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/detector-3-en-1-deteccion-de-tabiques-metal-y-tension-sica/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>01RED04066</t>
+          <t>01TOO01020</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø20MM 460MM LARGO</t>
+          <t>Porta-herramientas cartuchera p/electricistas grande</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>45097</v>
+        <v>47025</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-20mm-460mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-grande/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>01SIC00091</t>
+          <t>01TOO01092</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Multimetro digital 600v con termocupla SICA</t>
+          <t>Porta-herramientas cartuchera p/electricistas mediano (TOOLMEN)</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>40804</v>
+        <v>31572</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-digital-600v-con-termocupla-sica/</t>
+          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-mediano/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>01SIC00100</t>
+          <t>01TOO01093</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Detector 3 en 1 - detección de tabiques metal y tensión- SICA</t>
+          <t>Porta herramientas electricista super (TOOLMEN)</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>44681</v>
+        <v>60146</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/detector-3-en-1-deteccion-de-tabiques-metal-y-tension-sica/</t>
+          <t>https://electrocity.com.ar/productos/porta-herramientas-electricista-super/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>01TOO01020</t>
+          <t>01TOO01110</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Porta-herramientas cartuchera p/electricistas grande</t>
+          <t>Porta taladro - atornilladora - cartuchera durlock (TOOLMEN)</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>47025</v>
+        <v>26279</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-grande/</t>
+          <t>https://electrocity.com.ar/productos/porta-taladro-atornilladora-cartuchera-durlock/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>01TOO01092</t>
+          <t>01USH00030</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Porta-herramientas cartuchera p/electricistas mediano (TOOLMEN)</t>
+          <t>Dobladora de caños tipo tijera dos palancas para caños 5/8" 3/4" 7/8"</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>31572</v>
+        <v>380061</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-mediano/</t>
+          <t>https://electrocity.com.ar/productos/dobladora-de-canios-tipo-tijera-dos-palancas-para-canios-58-34-78/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>01TOO01093</t>
+          <t>01USH00040</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Porta herramientas electricista super (TOOLMEN)</t>
+          <t>Dobladora de caños 7/8" y 1" con trípode y resorte adaptador para caños 3/4"</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>60146</v>
+        <v>649475</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/porta-herramientas-electricista-super/</t>
+          <t>https://electrocity.com.ar/productos/dobladora-de-canios-78-y-1-con-tripode-y-resorte-adaptador-para-canios-34/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>01TOO01110</t>
+          <t>01VIY00015</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Porta taladro - atornilladora - cartuchera durlock (TOOLMEN)</t>
+          <t>Cinta pasacable nylon ø4mm resistencia 165kgf 15 metros</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>26279</v>
+        <v>31012</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/porta-taladro-atornilladora-cartuchera-durlock/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-nylon-4mm-resistencia-165kgf-15-metros/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>01USH00030</t>
+          <t>01VIY00115</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dobladora de caños tipo tijera dos palancas para caños 5/8" 3/4" 7/8"</t>
+          <t>Cinta pasacable plástica con alma acero ø4mm 30 metros</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>380061</v>
+        <v>29332</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/dobladora-de-canios-tipo-tijera-dos-palancas-para-canios-58-34-78/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-30-metros/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>01USH00040</t>
+          <t>01VIY00205</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dobladora de caños 7/8" y 1" con trípode y resorte adaptador para caños 3/4"</t>
+          <t>Cinta pasacable poliester ø5mm resistencia 150kgf 15 metros</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>649475</v>
+        <v>52390</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/dobladora-de-canios-78-y-1-con-tripode-y-resorte-adaptador-para-canios-34/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-poliester-5mm-resistencia-150kgf-15-metros/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>01VIY00015</t>
+          <t>01BAW06037</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cinta pasacable nylon ø4mm resistencia 165kgf 15 metros</t>
+          <t>Multimetro multirrango manual 600vcc/vca (BAW)</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>31012</v>
+        <v>32249</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-nylon-4mm-resistencia-165kgf-15-metros/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-600vccvca/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>01VIY00115</t>
+          <t>01BAW06044</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma acero ø4mm 30 metros</t>
+          <t>Meghometro digital hasta 1000v / 2 g ohms + display lcd</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>29332</v>
+        <v>186588</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-acero-4mm-30-metros/</t>
+          <t>https://electrocity.com.ar/productos/meghometro-digital-hasta-1000v-2-g-ohms-display-lcd/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>01VIY00205</t>
+          <t>01RED04121</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cinta pasacable poliester ø5mm resistencia 150kgf 15 metros</t>
+          <t>MECHA ACERO RAPIDO Ø 8MM EZETA</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>52390</v>
+        <v>11803</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-poliester-5mm-resistencia-150kgf-15-metros/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-8mm-ezeta/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>01BAW06037</t>
+          <t>01RED04101</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Multimetro multirrango manual 600vcc/vca (BAW)</t>
+          <t>MECHA ACERO RAPIDO Ø 3MM EZETA</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>32249</v>
+        <v>3601</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-600vccvca/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-3mm-ezeta/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>01BAW06044</t>
+          <t>01BUL00041</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Meghometro digital hasta 1000v / 2 g ohms + display lcd</t>
+          <t>ENGRAMPADORA USO INTENSIVO P/6MM-8MM BULIT (BULIT)</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>186588</v>
+        <v>40457</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/meghometro-digital-hasta-1000v-2-g-ohms-display-lcd/</t>
+          <t>https://electrocity.com.ar/productos/engrampadora-uso-intensivo-p6mm8mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01RED04121</t>
+          <t>01JAI00074</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MECHA ACERO RAPIDO Ø 8MM EZETA</t>
+          <t>SOLDADOR PUNTA CHANFLE TIPO LAPIZ 100W 220V PREMIUN -JA-</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10574</v>
+        <v>24702</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-8mm-ezeta/</t>
+          <t>https://electrocity.com.ar/productos/soldador-punta-chanfle-tipo-lapiz-100w-220v-premiun-ja/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>01RED04101</t>
+          <t>01BUL00698</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MECHA ACERO RAPIDO Ø 3MM EZETA</t>
+          <t>SET DE 5 PINZAS DE 4.5" + ESTUCHE BORDADO BULIT PZA S6 SET PRE</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3600</v>
+        <v>54611</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-3mm-ezeta/</t>
+          <t>https://electrocity.com.ar/productos/set-de-5-pinzas-de-45-estuche-bordado-bulit-pza-s6-set-pre/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>01BUL00041</t>
+          <t>01MIL00300</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ENGRAMPADORA USO INTENSIVO P/6MM-8MM BULIT (BULIT)</t>
+          <t>Punta Shockwave Impact Phillips Ph1 X 5 Milwaukee 4832-4661 (MILWAUKEE)</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>40457</v>
+        <v>5978</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/engrampadora-uso-intensivo-p6mm8mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/punta-shockwave-impact-phillips-ph1-5-milwaukee-48324661/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>01JAI00074</t>
+          <t>01BAW06033</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SOLDADOR PUNTA CHANFLE TIPO LAPIZ 100W 220V PREMIUN -JA-</t>
+          <t>Pinza amperometrica 400aca 600vca/cc 200k (BAW)</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>24702</v>
+        <v>15353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-punta-chanfle-tipo-lapiz-100w-220v-premiun-ja/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-400aca-600vcacc-200k-baw/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>01BUL00698</t>
+          <t>01BUL00026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SET DE 5 PINZAS DE 4.5" + ESTUCHE BORDADO BULIT PZA S6 SET PRE</t>
+          <t>Cinta metrica c/freno metálica 5mt. x 19mm (BULIT)</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>54611</v>
+        <v>21334</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-5-pinzas-de-45-estuche-bordado-bulit-pza-s6-set-pre/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-cfreno-metalica-5mt-19mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>01MIL00300</t>
+          <t>01BUL00053</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Punta Shockwave Impact Phillips Ph1 X 5 Milwaukee 4832-4661 (MILWAUKEE)</t>
+          <t>Destornillador aislado 1000v punta phillips #0 x 75mm (BULIT)</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5978</v>
+        <v>6553</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-shockwave-impact-phillips-ph1-5-milwaukee-48324661/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-punta-phillips-0-75mm/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>01BAW06033</t>
+          <t>01BUL00054</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 400aca 600vca/cc 200k (BAW)</t>
+          <t>Destornillador aislado 1000v punta phillips #1 x 100mm (BULIT)</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>15353</v>
+        <v>8305</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-400aca-600vcacc-200k-baw/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-punta-phillips-1-100mm/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>01BUL00026</t>
+          <t>01BUL00126</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cinta metrica c/freno metálica 5mt. x 19mm (BULIT)</t>
+          <t>Set de llaves torx de 9 piezas (BULIT)</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>21334</v>
+        <v>20403</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-cfreno-metalica-5mt-19mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/set-de-llaves-torde-9-piezas/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>01BUL00053</t>
+          <t>01BUL00463</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v punta phillips #0 x 75mm (BULIT)</t>
+          <t>Cutter profesional grande metalico p/corte de fuerza (BULIT)</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>6553</v>
+        <v>20272</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-punta-phillips-0-75mm/</t>
+          <t>https://electrocity.com.ar/productos/cutter-profesional-grande-metalico-pcorte-de-fuerza/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>01BUL00054</t>
+          <t>01BUL01985</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v punta phillips #1 x 100mm (BULIT)</t>
+          <t>Juego 8 destornilladores philips y plano aislados 1000v + mango + linterna +estuche (BULIT)</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>8305</v>
+        <v>66130</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-punta-phillips-1-100mm/</t>
+          <t>https://electrocity.com.ar/productos/juego-8-destornilladores-philips-y-plano-aislados-1000v-mango-linterna-estuche/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>01BUL00126</t>
+          <t>01MIL00633</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Set de llaves torx de 9 piezas (BULIT)</t>
+          <t>Pistola Aplicadora para Silicona M18 Milwaukee 2641-159A</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>20403</v>
+        <v>870358.35</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-llaves-torde-9-piezas/</t>
+          <t>https://electrocity.com.ar/productos/pistola-aplicadora-para-silicona-m18-milwaukee-2641-159a-1wha8/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>01BUL00463</t>
+          <t>01MIL00012</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Cutter profesional grande metalico p/corte de fuerza (BULIT)</t>
+          <t>Amoladora Gatillo Doble M18 Fuel One Key 5" Milwaukee 2986-20</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>20272</v>
+        <v>924015.6</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-profesional-grande-metalico-pcorte-de-fuerza/</t>
+          <t>https://electrocity.com.ar/productos/amoladora-gatillo-doble-m18-fuel-one-key-5-milwaukee-2986-20-1phqz/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01BUL01985</t>
+          <t>01MIL00630</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Juego 8 destornilladores philips y plano aislados 1000v + mango + linterna +estuche (BULIT)</t>
+          <t>Batería M12 RedLithium CP1.5 Ah Milwaukee 4811-2401</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>66130</v>
+        <v>64541.35</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-8-destornilladores-philips-y-plano-aislados-1000v-mango-linterna-estuche/</t>
+          <t>https://electrocity.com.ar/productos/bateria-m12-redlithium-cp1-5-ah-milwaukee-4811-2401-tjhq2/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01MIL00633</t>
+          <t>01MIL00628</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Pistola Aplicadora para Silicona M18 Milwaukee 2641-159A</t>
+          <t>Rotomartillo SDS Max 1100W 3 Modos Milwaukee 5317-59A</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>870358.35</v>
+        <v>1174987.8</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-aplicadora-para-silicona-m18-milwaukee-2641-159a-1wha8/</t>
+          <t>https://electrocity.com.ar/productos/rotomartillo-sds-max-1100w-3-modos-milwaukee-5317-59a-i5xat/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01MIL00012</t>
+          <t>01MIL00627</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Amoladora Gatillo Doble M18 Fuel One Key 5" Milwaukee 2986-20</t>
+          <t>Amoladora Angular 115mm 1550w Velocidad Variable Milwaukee 6117-59A</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>924015.6</v>
+        <v>389112.15</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/amoladora-gatillo-doble-m18-fuel-one-key-5-milwaukee-2986-20-1phqz/</t>
+          <t>https://electrocity.com.ar/productos/amoladora-angular-115mm-1550w-velocidad-variable-milwaukee-6117-59a-10u5a/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01MIL00630</t>
+          <t>01MIL00616</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Batería M12 RedLithium CP1.5 Ah Milwaukee 4811-2401</t>
+          <t>Taladro Rotopercutor SDS Bateria M18 Fuel Milwaukee 2717-20 M18</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>64541.35</v>
+        <v>1274348.05</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-m12-redlithium-cp1-5-ah-milwaukee-4811-2401-tjhq2/</t>
+          <t>https://electrocity.com.ar/productos/taladro-rotopercutor-sds-bateria-m18-fuel-milwaukee-2717-20-m18-r9smp/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01MIL00628</t>
+          <t>01BUL00805</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rotomartillo SDS Max 1100W 3 Modos Milwaukee 5317-59A</t>
+          <t>Pistola Encoladora Inalámbrica 10w con Base y Cable USB Suprabond C PHX B10</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1174987.8</v>
+        <v>78612</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/rotomartillo-sds-max-1100w-3-modos-milwaukee-5317-59a-i5xat/</t>
+          <t>https://electrocity.com.ar/productos/pistola-encoladora-inalambrica-10w-con-base-y-cable-usb-suprabond-c-phx-b10-z9nj7/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>01MIL00627</t>
+          <t>01BLO00032</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Amoladora Angular 115mm 1550w Velocidad Variable Milwaukee 6117-59A</t>
+          <t>Bloqueador de Térmica Bipolar Transparente E2 Blook ELE-2111</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>389112.15</v>
+        <v>40452</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/amoladora-angular-115mm-1550w-velocidad-variable-milwaukee-6117-59a-10u5a/</t>
+          <t>https://electrocity.com.ar/productos/bloqueador-de-termica-bipolar-transparente-e2-blook-ele-2111-rdbhj/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01MIL00616</t>
+          <t>01BLO00024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Taladro Rotopercutor SDS Bateria M18 Fuel Milwaukee 2717-20 M18</t>
+          <t>Bloqueador Eléctrico Rojo a Tornillo Bioseif ELE-1140</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1274348.05</v>
+        <v>33710</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-rotopercutor-sds-bateria-m18-fuel-milwaukee-2717-20-m18-r9smp/</t>
+          <t>https://electrocity.com.ar/productos/bloqueador-electrico-rojo-a-tornillo-bioseif-ele-1140-ubvdp/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>01BUL00805</t>
+          <t>01JAI01424</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Pistola Encoladora Inalámbrica 10w con Base y Cable USB Suprabond C PHX B10</t>
+          <t>Pinza Pelacable Redondo hasta 240 mm de Diámetro Ja PZC5360</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>78612</v>
+        <v>191470</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-encoladora-inalambrica-10w-con-base-y-cable-usb-suprabond-c-phx-b10-z9nj7/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pelacable-redondo-hasta-240-mm-de-diametro-ja-pzc5360/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>01BLO00032</t>
+          <t>01JAI00304</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Bloqueador de Térmica Bipolar Transparente E2 Blook ELE-2111</t>
+          <t>Tester Multimetro Digital Compacto Ja INT0033</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>40452</v>
+        <v>19298</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bloqueador-de-termica-bipolar-transparente-e2-blook-ele-2111-rdbhj/</t>
+          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-compacto-ja-int0033/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>01BLO00024</t>
+          <t>01BAW06038</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Bloqueador Eléctrico Rojo a Tornillo Bioseif ELE-1140</t>
+          <t>Tester Multimetro Multirango Manual Baw RM113D</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>33710</v>
+        <v>56546</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bloqueador-electrico-rojo-a-tornillo-bioseif-ele-1140-ubvdp/</t>
+          <t>https://electrocity.com.ar/productos/tester-multimetro-multirango-manual-baw-rm113d/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>01ZOL04207</t>
+          <t>01HRT09010</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Pinza Crimpeadora Terminales Tiff para Cables 0.25 a 10mm Zoloda CRIMP-10</t>
+          <t>Destornillador Punta Plana Aislado 1000v Bahco</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>155663</v>
+        <v>26027</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-terminales-tiff-para-cables-0-25-a-10mm-zoloda-crimp-10-sqxcn/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-aislado-1000v-bahco/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>01JAI01424</t>
+          <t>01HRT05602</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Pinza Pelacable Redondo hasta 240 mm de Diámetro Ja PZC5360</t>
+          <t>Sierra Copa Bimetálica 20mm Profesional HRT 885347</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>191470</v>
+        <v>10115</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pelacable-redondo-hasta-240-mm-de-diametro-ja-pzc5360/</t>
+          <t>https://electrocity.com.ar/productos/sierra-copa-bimetalica-20mm-profesional-hrt-885347/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01JAI00304</t>
+          <t>01MIL00306</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tester Multimetro Digital Compacto Ja INT0033</t>
+          <t>Punta Atornillador Phillips Impacto Ph3 x 50mm Kit x Unidad Milwaukee 4832-4463</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>19298</v>
+        <v>4337</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-compacto-ja-int0033/</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph3-x-50mm-kit-x-unidad-milwaukee-4832-4463/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>01BAW06047</t>
+          <t>01MIL00063</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Termómetro Infrarrojo Láser +800°C Baw RM800PRO</t>
+          <t>Taladro Angular Recto con Batería Milwaukee 2415-159A</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>92391</v>
+        <v>514840</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/termometro-infrarrojo-laser-800c-baw-rm800pro/</t>
+          <t>https://electrocity.com.ar/productos/taladro-angular-recto-con-bateria-milwaukee-2415-159a/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>01BAW06038</t>
+          <t>01HRT09103</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tester Multimetro Multirango Manual Baw RM113D</t>
+          <t>Cinta Métrica Retráctil Con Bloqueo 5m x 19mm Mtg-5-19ar (BAHCO)</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>56546</v>
+        <v>16992</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tester-multimetro-multirango-manual-baw-rm113d/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-retractil-con-bloqueo-5m-x-19mm-mtg-5-19ar-bahco/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>01HRT09010</t>
+          <t>01HRT09102</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Destornillador Punta Plana Aislado 1000v Bahco</t>
+          <t>Juego De Llaves Combinadas 11 Piezas Con Estuche Pu 95 (BAHCO)</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>26027</v>
+        <v>135382</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-aislado-1000v-bahco/</t>
+          <t>https://electrocity.com.ar/productos/juego-de-llaves-combinadas-11-piezas-con-estuche-pu-95-bahco/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>01HRT05602</t>
+          <t>01HRT05130</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Sierra Copa Bimetálica 20mm Profesional HRT 885347</t>
+          <t>Juego 6 Destornilladores Premium Blister P-3000/6h (BAHCO)</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>10115</v>
+        <v>49253</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sierra-copa-bimetalica-20mm-profesional-hrt-885347/</t>
+          <t>https://electrocity.com.ar/productos/juego-6-destornilladores-premium-blister-p-3000-6h-bahco/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>01MIL00306</t>
+          <t>01HRT05124</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Punta Atornillador Phillips Impacto Ph3 x 50mm Kit x Unidad Milwaukee 4832-4463</t>
+          <t>Juego Destornilladores 6 Piezas 3000/6h (BAHCO)</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4337</v>
+        <v>49253</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-phillips-impacto-ph3-x-50mm-kit-x-unidad-milwaukee-4832-4463/</t>
+          <t>https://electrocity.com.ar/productos/juego-destornilladores-6-piezas-3000-6h-bahco/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>01MIL00063</t>
+          <t>01HRT05122</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Taladro Angular Recto con Batería Milwaukee 2415-159A</t>
+          <t>Juego Destornilladores 5 Piezas Blister BAHCO</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>514840</v>
+        <v>33822</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-angular-recto-con-bateria-milwaukee-2415-159a/</t>
+          <t>https://electrocity.com.ar/productos/juego-destornilladores-5-piezas-blister-bahco/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>01HRT09103</t>
+          <t>01LQF02370</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Cinta Métrica Retráctil Con Bloqueo 5m x 19mm Mtg-5-19ar (BAHCO)</t>
+          <t>DESTONILLADOR MULTIPUNTA ENCASTRE 1/4 CON 33 PUNTAS - TRUPER -13595</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>16992</v>
+        <v>18103</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-retractil-con-bloqueo-5m-x-19mm-mtg-5-19ar-bahco/</t>
+          <t>https://electrocity.com.ar/productos/destonillador-multipunta-encastre-14-con-33-puntas-truper-13595/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>01HRT09102</t>
+          <t>01HRT06061</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Juego De Llaves Combinadas 11 Piezas Con Estuche Pu 95 (BAHCO)</t>
+          <t>DESTORNILLADOR PLANO 3.5 X 75MM AISLADOS 1000V STANLEY STMT60163 (STANLEY)</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>135382</v>
+        <v>9197</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-de-llaves-combinadas-11-piezas-con-estuche-pu-95-bahco/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-plano-35-75mm-aislados-1000v-stanley-stmt60163/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>01HRT05130</t>
+          <t>01BUL00017</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Juego 6 Destornilladores Premium Blister P-3000/6h (BAHCO)</t>
+          <t>Engrampadora profesional potencia regulable p/grampas 8 a 12mm y clavos 15mm (BULIT)</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>49253</v>
+        <v>90095</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-6-destornilladores-premium-blister-p-3000-6h-bahco/</t>
+          <t>https://electrocity.com.ar/productos/engrampadora-profesional-potencia-regulable-p-grampas-8-a-12mm-y-clavos-15mm/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>01HRT05124</t>
+          <t>01BUL00023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Juego Destornilladores 6 Piezas 3000/6h (BAHCO)</t>
+          <t>Hoja de sierra junior sin-par (SIN-PAR)</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>49253</v>
+        <v>994</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-destornilladores-6-piezas-3000-6h-bahco/</t>
+          <t>https://electrocity.com.ar/productos/hoja-de-sierra-junior-sin-par/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>01HRT05122</t>
+          <t>01BUL00028</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Juego Destornilladores 5 Piezas Blister BAHCO</t>
+          <t>Cinta metrica doble freno metálica 7.5mt. x 25mm bulit</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>33822</v>
+        <v>34669</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-destornilladores-5-piezas-blister-bahco/</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-doble-freno-metalica-7-5mt-x-25mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>01LQF02370</t>
+          <t>01BUL00078</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DESTONILLADOR MULTIPUNTA ENCASTRE 1/4 CON 33 PUNTAS - TRUPER -13595</t>
+          <t>Destornillador profesional #1x75mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>18103</v>
+        <v>5723</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destonillador-multipunta-encastre-14-con-33-puntas-truper-13595/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-1x75mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>01HRT06061</t>
+          <t>01BUL00086</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DESTORNILLADOR PLANO 3.5 X 75MM AISLADOS 1000V STANLEY STMT60163 (STANLEY)</t>
+          <t>Destornillador profesional #3x125mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>9197</v>
+        <v>15367</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-plano-35-75mm-aislados-1000v-stanley-stmt60163/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-3x125mm-punta-phillips/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>01BUL00017</t>
+          <t>01BUL00088</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Engrampadora profesional potencia regulable p/grampas 8 a 12mm y clavos 15mm (BULIT)</t>
+          <t>Destornillador profesional #4x100mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>90095</v>
+        <v>5187</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/engrampadora-profesional-potencia-regulable-p-grampas-8-a-12mm-y-clavos-15mm/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x100mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>01BUL00023</t>
+          <t>01BUL00090</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Hoja de sierra junior sin-par (SIN-PAR)</t>
+          <t>Destornillador profesional #4x150mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>994</v>
+        <v>6553</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/hoja-de-sierra-junior-sin-par/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x150mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>01BUL00028</t>
+          <t>01BUL00092</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Cinta metrica doble freno metálica 7.5mt. x 25mm bulit</t>
+          <t>Destornillador profesional #4x200mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>34669</v>
+        <v>6570</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-doble-freno-metalica-7-5mt-x-25mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x200mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>01BUL00078</t>
+          <t>01BUL00098</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Destornillador profesional #1x75mm punta phillips (BULIT)</t>
+          <t>Destornillador profesional #6x38mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5723</v>
+        <v>9853</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-1x75mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-6x38mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>01BUL00086</t>
+          <t>01BUL00102</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Destornillador profesional #3x125mm punta phillips (BULIT)</t>
+          <t>Destornillador profesional #8x150mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>15367</v>
+        <v>15781</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-3x125mm-punta-phillips/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-8x150mm-punta-plana/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>01BUL00088</t>
+          <t>01BUL00104</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x100mm punta plana (BULIT)</t>
+          <t>Destornillador profesional #4x150mm punta recta (BULIT)</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5187</v>
+        <v>6405</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x100mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x150mm-punta-recta/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>01BUL00090</t>
+          <t>01BUL00106</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x150mm punta plana (BULIT)</t>
+          <t>Destornillador profesional #4x75mm punta recta (BULIT)</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>6553</v>
+        <v>5723</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x150mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x75mm-punta-recta/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>01BUL00092</t>
+          <t>01BUL00108</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x200mm punta plana (BULIT)</t>
+          <t>Destornillador profesional #4x200mm punta recta (BULIT)</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>6570</v>
+        <v>7713</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x200mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x200mm-punta-recta/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>01BUL00098</t>
+          <t>01BUL00164</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Destornillador profesional #6x38mm punta plana (BULIT)</t>
+          <t>Llave ajustable pavonada de 8 francesa profesional (BULIT)</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>9853</v>
+        <v>38920</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-6x38mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/llave-ajustable-pavonada-de-8-francesa-profesional/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>01BUL00102</t>
+          <t>01BUL00466</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Destornillador profesional #8x150mm punta plana (BULIT)</t>
+          <t>Cutter reforzado automático chico con repuesto serie 500 (BULIT)</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>15781</v>
+        <v>10721</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-8x150mm-punta-plana/</t>
+          <t>https://electrocity.com.ar/productos/cutter-reforzado-automatico-chico-con-repuesto-serie-500/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>01BUL00104</t>
+          <t>01BUL00670</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x150mm punta recta (BULIT)</t>
+          <t>Pinza universal de presicion de 45 p/artesanias y electrónica (BULIT)</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>6405</v>
+        <v>10394</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x150mm-punta-recta/</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-de-presicion-de-45-partesanias-y-electronica/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>01BUL00106</t>
+          <t>01BUL00672</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x75mm punta recta (BULIT)</t>
+          <t>Pinza de punta semi redonda de precision de 45 p/artesanias y electrónica (BULIT)</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>5723</v>
+        <v>10343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x75mm-punta-recta/</t>
+          <t>https://electrocity.com.ar/productos/pinza-de-punta-semi-redonda-de-precision-de-45-partesanias-y-electronica/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>01BUL00108</t>
+          <t>01BUL00674</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Destornillador profesional #4x200mm punta recta (BULIT)</t>
+          <t>Pinza de punta redonda de precision de 45 p/artesanias y electrónica</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7713</v>
+        <v>12189</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-4x200mm-punta-recta/</t>
+          <t>https://electrocity.com.ar/productos/pinza-de-punta-redonda-de-precision-de-45-partesanias-y-electronica/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>01BUL00164</t>
+          <t>01BUL00695</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Llave ajustable pavonada de 8 francesa profesional (BULIT)</t>
+          <t>SET COMBO PINZAS PRESICION UNIVERSAL + PUNTA SEMI REDONDA + ALICATE 45 P/ARTESANIAS Y E</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>38920</v>
+        <v>32031</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-ajustable-pavonada-de-8-francesa-profesional/</t>
+          <t>https://electrocity.com.ar/productos/set-combo-pinzas-presicion-universal-punta-semi-redonda-alicate-45-partesanias-y-e/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>01BUL00466</t>
+          <t>01BUL00696</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Cutter reforzado automático chico con repuesto serie 500 (BULIT)</t>
+          <t>SET COMBO PINZAS PRESICION UNIVERSAL + PUNTA REDONDA + PUNTA SEMI REDONDA + ALICATE FRONTA (BULIT)</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>10721</v>
+        <v>44220</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-reforzado-automatico-chico-con-repuesto-serie-500/</t>
+          <t>https://electrocity.com.ar/productos/set-combo-pinzas-presicion-universal-punta-redonda-punta-semi-redonda-alicate-fronta/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>01BUL00670</t>
+          <t>01BUL00809</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pinza universal de presicion de 45 p/artesanias y electrónica (BULIT)</t>
+          <t>Pistola encoladora dosificadora de pegamento 10w (SUPRABOND)</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>10394</v>
+        <v>20333</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-de-presicion-de-45-partesanias-y-electronica/</t>
+          <t>https://electrocity.com.ar/productos/pistola-encoladora-dosificadora-de-pegamento-10w/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>01BUL00672</t>
+          <t>01BUL00893</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pinza de punta semi redonda de precision de 45 p/artesanias y electrónica (BULIT)</t>
+          <t>Disco diamantado serie 400 turbo fino 115mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>10343</v>
+        <v>27170</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-de-punta-semi-redonda-de-precision-de-45-partesanias-y-electronica/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-fino-115mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>01BUL00674</t>
+          <t>01BUL00894</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Pinza de punta redonda de precision de 45 p/artesanias y electrónica</t>
+          <t>Disco diamantado serie 400 continuo 180mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>12189</v>
+        <v>21021</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-de-punta-redonda-de-precision-de-45-partesanias-y-electronica/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-continuo-180mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>01BUL00695</t>
+          <t>01BUL00895</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SET COMBO PINZAS PRESICION UNIVERSAL + PUNTA SEMI REDONDA + ALICATE 45 P/ARTESANIAS Y E</t>
+          <t>Disco diamantado serie 400 segmentado 180mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>32031</v>
+        <v>23788</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-combo-pinzas-presicion-universal-punta-semi-redonda-alicate-45-partesanias-y-e/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-segmentado-180mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>01BUL00696</t>
+          <t>01BUL00896</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SET COMBO PINZAS PRESICION UNIVERSAL + PUNTA REDONDA + PUNTA SEMI REDONDA + ALICATE FRONTA (BULIT)</t>
+          <t>Disco diamantado serie 400 turbo 180mm bulit (BULIT)</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>44220</v>
+        <v>27818</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-combo-pinzas-presicion-universal-punta-redonda-punta-semi-redonda-alicate-fronta/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-180mm-bulit/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>01BUL00809</t>
+          <t>01BUL00905</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Pistola encoladora dosificadora de pegamento 10w (SUPRABOND)</t>
+          <t>Disco corte extra fino 1 115mm serie 400 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>20333</v>
+        <v>1255</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-encoladora-dosificadora-de-pegamento-10w/</t>
+          <t>https://electrocity.com.ar/productos/disco-corte-extra-fino-1-115mm-serie-400-bulit/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>01BUL00893</t>
+          <t>01BUL01620</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 turbo fino 115mm bulit (BULIT)</t>
+          <t>Lima plana entrefina acero frojado 8 mango ergonómico (BULIT)</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>27170</v>
+        <v>16821</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-fino-115mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/lima-plana-entrefina-acero-frojado-8-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>01BUL00894</t>
+          <t>01BUL01621</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 continuo 180mm bulit (BULIT)</t>
+          <t>Lima redonda entrefina acero forjado 8 mango ergonómico (BULIT)</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>21021</v>
+        <v>13604</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-continuo-180mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/lima-redonda-entrefina-acero-forjado-8-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>01BUL00895</t>
+          <t>01BUL01622</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 segmentado 180mm bulit (BULIT)</t>
+          <t>Lima media caña entrefina acero forjado 8 mango ergonómico (BULIT)</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>23788</v>
+        <v>17561</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-segmentado-180mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/lima-media-cania-entrefina-acero-forjado-8-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>01BUL00896</t>
+          <t>01BUL01632</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Disco diamantado serie 400 turbo 180mm bulit (BULIT)</t>
+          <t>Serrucho profesional 500mm dientes cementados hoja extra ancha (BULIT)</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>27818</v>
+        <v>27533</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-serie-400-turbo-180mm-bulit/</t>
+          <t>https://electrocity.com.ar/productos/serrucho-profesional-500mm-dientes-cementados-hoja-extra-ancha/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>01BUL00905</t>
+          <t>01BUL01635</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Disco corte extra fino 1 115mm serie 400 bulit (BULIT)</t>
+          <t>Serrucho profesional costilla 300mm dientes cementados hoja extra ancha (BULIT)</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1255</v>
+        <v>18739</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-corte-extra-fino-1-115mm-serie-400-bulit/</t>
+          <t>https://electrocity.com.ar/productos/serrucho-profesional-costilla-300mm-dientes-cementados-hoja-extra-ancha/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>01BUL01620</t>
+          <t>01BUL01636</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lima plana entrefina acero frojado 8 mango ergonómico (BULIT)</t>
+          <t>Serrucho turbo pro p/durlero 165mm c/punta de corte y mango ergonomico (BULIT)</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>16821</v>
+        <v>30665</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/lima-plana-entrefina-acero-frojado-8-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/serrucho-turbo-pro-pdurlero-165mm-cpunta-de-corte-y-mango-ergonomico/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>01BUL01621</t>
+          <t>01BUL01721</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Lima redonda entrefina acero forjado 8 mango ergonómico (BULIT)</t>
+          <t>Llave p/caños con mordazas 1 1/2 c/tope seguridad</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>13604</v>
+        <v>51152</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/lima-redonda-entrefina-acero-forjado-8-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/llave-pcanios-con-mordazas-1-12-ctope-seguridad/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>01BUL01622</t>
+          <t>01BUL01840</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lima media caña entrefina acero forjado 8 mango ergonómico (BULIT)</t>
+          <t>KIT - PISTOLA PROFESIONAL DE PEGAMENTO + BARRAS TRANSP. 112MM X 10CM X 1kg EN BLIST</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>17561</v>
+        <v>138014</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/lima-media-cania-entrefina-acero-forjado-8-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-de-pegamento-barras-transp-112mm-10cm-1kg-en-blist/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>01BUL01632</t>
+          <t>01BUL01844</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Serrucho profesional 500mm dientes cementados hoja extra ancha (BULIT)</t>
+          <t>KIT - PISTOLA PROFESIONAL DE PEGAMENTO + BARRAS TRANSP. 112MM X 10CM X 5kg EN BLIST</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>27533</v>
+        <v>106405</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/serrucho-profesional-500mm-dientes-cementados-hoja-extra-ancha/</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-de-pegamento-barras-transp-112mm-10cm-5kg-en-blist/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>01BUL01635</t>
+          <t>01BUL01846</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Serrucho profesional costilla 300mm dientes cementados hoja extra ancha (BULIT)</t>
+          <t>KIT - PISTOLA DE PEG. 10W EDICION LUNARES + BARRAS TRANSP.074x10CM x 100Grs EN BLISTER (SUPRABOND)</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>18739</v>
+        <v>26655</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/serrucho-profesional-costilla-300mm-dientes-cementados-hoja-extra-ancha/</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-de-peg-10w-edicion-lunares-barras-transp074x10cm-100grs-en-blister/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>01BUL01636</t>
+          <t>01BUL01981</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Serrucho turbo pro p/durlero 165mm c/punta de corte y mango ergonomico (BULIT)</t>
+          <t>Set 7 destornilladores precisión serie 1000 (BULIT)</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>30665</v>
+        <v>30888</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/serrucho-turbo-pro-pdurlero-165mm-cpunta-de-corte-y-mango-ergonomico/</t>
+          <t>https://electrocity.com.ar/productos/set-7-destornilladores-precision-serie-1000/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>01BUL01721</t>
+          <t>01BUL02070</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Llave p/caños con mordazas 1 1/2 c/tope seguridad</t>
+          <t>Kit de 7 llaves criquet mm articuladas serie 800</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>51152</v>
+        <v>107122</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-pcanios-con-mordazas-1-12-ctope-seguridad/</t>
+          <t>https://electrocity.com.ar/productos/kit-de-7-llaves-criquet-mm-articuladas-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>01BUL01840</t>
+          <t>01BUL02171</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA PROFESIONAL DE PEGAMENTO + BARRAS TRANSP. 112MM X 10CM X 1kg EN BLIST</t>
+          <t>Llave ajustable 8 cromada c/mango ergonomico antideslizante (BULIT)</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>138014</v>
+        <v>26728</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-de-pegamento-barras-transp-112mm-10cm-1kg-en-blist/</t>
+          <t>https://electrocity.com.ar/productos/llave-ajustable-8-cromada-cmango-ergonomico-antideslizante/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>01BUL01844</t>
+          <t>01BUL02172</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA PROFESIONAL DE PEGAMENTO + BARRAS TRANSP. 112MM X 10CM X 5kg EN BLIST</t>
+          <t>Llave ajustable 10 cromada c/mango ergonomico antideslizante (BULIT)</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>106405</v>
+        <v>33835</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-de-pegamento-barras-transp-112mm-10cm-5kg-en-blist/</t>
+          <t>https://electrocity.com.ar/productos/llave-ajustable-10-cromada-cmango-ergonomico-antideslizante/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>01BUL01846</t>
+          <t>01BUL02330</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA DE PEG. 10W EDICION LUNARES + BARRAS TRANSP.074x10CM x 100Grs EN BLISTER (SUPRABOND)</t>
+          <t>CUTTER PROFESIONAL AUTOMATICO BULIT + REPUESTOS HOJAS (BULIT)</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>26655</v>
+        <v>29189</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-de-peg-10w-edicion-lunares-barras-transp074x10cm-100grs-en-blister/</t>
+          <t>https://electrocity.com.ar/productos/cutter-profesional-automatico-bulit-repuestos-hojas/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>01BUL01981</t>
+          <t>01BUL02332</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Set 7 destornilladores precisión serie 1000 (BULIT)</t>
+          <t>CUTTER PROFESIONAL METALICO BULIT + REPUESTOS (BULIT)</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>30888</v>
+        <v>26865</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-7-destornilladores-precision-serie-1000/</t>
+          <t>https://electrocity.com.ar/productos/cutter-profesional-metalico-bulit-repuestos/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>01BUL01989</t>
+          <t>01BUL02335</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Set de llaves tipo t de 16 unidades bulit</t>
+          <t>DESTORNILLADOR RECTO 4X150 + DESTORNILLADOR RECTO 4X75 + DESTORNILLADOR RECTO 4X200 (BULIT)</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>110298</v>
+        <v>19840</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-llaves-tipo-t-de-16-unidades-bulit/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-recto-4x150-destornillador-recto-4x75-destornillador-recto-4x200/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>01BUL02070</t>
+          <t>01EXP00002</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Kit de 7 llaves criquet mm articuladas serie 800</t>
+          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 20 metros c/porta-pasacable</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>107122</v>
+        <v>98883</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-de-7-llaves-criquet-mm-articuladas-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-20-metros-cportapasacable/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>01BUL02171</t>
+          <t>01HRT04720</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Llave ajustable 8 cromada c/mango ergonomico antideslizante (BULIT)</t>
+          <t>Pinza semi-automatica p/terminales desnudos hasta 16mm</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>26728</v>
+        <v>163043</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-ajustable-8-cromada-cmango-ergonomico-antideslizante/</t>
+          <t>https://electrocity.com.ar/productos/pinza-semiautomatica-pterminales-desnudos-hasta-16mm/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>01BUL02172</t>
+          <t>01HRT04742</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Llave ajustable 10 cromada c/mango ergonomico antideslizante (BULIT)</t>
+          <t>Pinza p/terminales identacion profunda de 16-50mm (GABEXEL)</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>33835</v>
+        <v>388198</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-ajustable-10-cromada-cmango-ergonomico-antideslizante/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pterminales-identacion-profunda-de-1650mm/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>01BUL02330</t>
+          <t>01HRT04744</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CUTTER PROFESIONAL AUTOMATICO BULIT + REPUESTOS HOJAS (BULIT)</t>
+          <t>Pinza p/terminales identacion profunda de 25-120mm (GABEXEL)</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>29189</v>
+        <v>560947</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-profesional-automatico-bulit-repuestos-hojas/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pterminales-identacion-profunda-de-25120mm/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>01BUL02332</t>
+          <t>01HRT04830</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CUTTER PROFESIONAL METALICO BULIT + REPUESTOS (BULIT)</t>
+          <t>Mecha sds plus tipo cincel plano 20mm chato angosto 250mm largo (GENERICO)</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>26865</v>
+        <v>13477</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-profesional-metalico-bulit-repuestos/</t>
+          <t>https://electrocity.com.ar/productos/mecha-sds-plus-tipo-cincel-plano-20mm-chato-angosto-250mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>01BUL02335</t>
+          <t>01HRT04835</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DESTORNILLADOR RECTO 4X150 + DESTORNILLADOR RECTO 4X75 + DESTORNILLADOR RECTO 4X200 (BULIT)</t>
+          <t>Mecha sds plus tipo cincel punta 25omm largo</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>19840</v>
+        <v>12718</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-recto-4x150-destornillador-recto-4x75-destornillador-recto-4x200/</t>
+          <t>https://electrocity.com.ar/productos/mecha-sds-plus-tipo-cincel-punta-25omm-largo/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>01EXP00002</t>
+          <t>01HRT05100</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 20 metros c/porta-pasacable</t>
+          <t>Destornillador plano standard.chico 4 x 75mm (BAHCO)</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>86522</v>
+        <v>6236</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-20-metros-cportapasacable/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-plano-standardchico-4-75mm/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>01HRT04720</t>
+          <t>01HRT05117</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Pinza semi-automatica p/terminales desnudos hasta 16mm</t>
+          <t>Destornillador phillips standard mediano 6 x 150mm (BAHCO)</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>163043</v>
+        <v>7567</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-semiautomatica-pterminales-desnudos-hasta-16mm/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-phillips-standard-mediano-6-150mm/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>01HRT04742</t>
+          <t>01HRT05615</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Pinza p/terminales identacion profunda de 16-50mm (GABEXEL)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø27mm 1 1/16</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>388198</v>
+        <v>13486</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pterminales-identacion-profunda-de-1650mm/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-27mm-1-116/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>01HRT04744</t>
+          <t>01HRT05616</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Pinza p/terminales identacion profunda de 25-120mm (GABEXEL)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø32mm 1 1/4</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>560947</v>
+        <v>15678</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pterminales-identacion-profunda-de-25120mm/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-32mm-1-14/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>01HRT04830</t>
+          <t>01HRT05620</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Mecha sds plus tipo cincel plano 20mm chato angosto 250mm largo (GENERICO)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø38mm 1 1/2</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>13477</v>
+        <v>18459</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-sds-plus-tipo-cincel-plano-20mm-chato-angosto-250mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-38mm-1-12/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>01HRT04835</t>
+          <t>01HRT05623</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Mecha sds plus tipo cincel punta 25omm largo</t>
+          <t>Mecha copa bimetálica traspasadora hss ø 41mm 1 5/8</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>12718</v>
+        <v>19808</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-sds-plus-tipo-cincel-punta-25omm-largo/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-41mm-1-58/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>01HRT05100</t>
+          <t>01HRT05626</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Destornillador plano standard.chico 4 x 75mm (BAHCO)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø60mm 2 3/8</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>6236</v>
+        <v>28827</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-plano-standardchico-4-75mm/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-60mm-2-38/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>01HRT05117</t>
+          <t>01HRT05627</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Destornillador phillips standard mediano 6 x 150mm (BAHCO)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø67mm 2 5/8</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>7567</v>
+        <v>32367</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-phillips-standard-mediano-6-150mm/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-67mm-2-58/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>01HRT05615</t>
+          <t>01HRT05629</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø27mm 1 1/16</t>
+          <t>Mecha copa bimetálica traspasadora hss ø86mm 3 3/8</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>13486</v>
+        <v>40712</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-27mm-1-116/</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-86mm-3-38/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>01HRT05616</t>
+          <t>01INS00010</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø32mm 1 1/4</t>
+          <t>Multimetro digital compacto 600v fluke-106 esp</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>15678</v>
+        <v>319690</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-32mm-1-14/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-digital-compacto-600v-fluke106-esp/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>01HRT05620</t>
+          <t>01INS00030</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø38mm 1 1/2</t>
+          <t>Multimetro digital trms 600v profesional fluke-115/em esp (FLUKE)</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>18459</v>
+        <v>1055260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-38mm-1-12/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-digital-trms-600v-profesional-fluke115em-esp/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>01HRT05623</t>
+          <t>01INS00105</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø 41mm 1 5/8</t>
+          <t>Pinza amperometrica 600a ac 600 vca/vcc fluke-303 (FLUKE)</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>19808</v>
+        <v>512070</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-41mm-1-58/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-600a-ac-600-vcavcc-fluke303/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>01HRT05626</t>
+          <t>01INS00205</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø60mm 2 3/8</t>
+          <t>Comprobador tension continua 12v-690v c/rotacion de fases fluke-t110 (FLUKE)</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>28827</v>
+        <v>475291</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-60mm-2-38/</t>
+          <t>https://electrocity.com.ar/productos/comprobador-tension-continua-12v690v-crotacion-de-fases-fluket110/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>01HRT05627</t>
+          <t>01INS00290</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø67mm 2 5/8</t>
+          <t>Detector comprobador electronico luminoso con linterna 90/600v ca lvd2</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>32367</v>
+        <v>198038</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-67mm-2-58/</t>
+          <t>https://electrocity.com.ar/productos/detector-comprobador-electronico-luminoso-con-linterna-90600v-ca-lvd2/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>01HRT05629</t>
+          <t>01INS00300</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø86mm 3 3/8</t>
+          <t>Pistola de medicion temperatura infraroja -30 °c a 500 °c fluke-62 max</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>40712</v>
+        <v>638176</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-86mm-3-38/</t>
+          <t>https://electrocity.com.ar/productos/pistola-de-medicion-temperatura-infraroja-30-c-a-500-c-fluke62-max/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>01INS00010</t>
+          <t>01INS01015</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Multimetro digital compacto 600v fluke-106 esp</t>
+          <t>Multimetro digital trms 600v ca/cc profesional am-530</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>319690</v>
+        <v>632448</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-digital-compacto-600v-fluke106-esp/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-digital-trms-600v-cacc-profesional-am530/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>01INS00030</t>
+          <t>01INS01200</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Multimetro digital trms 600v profesional fluke-115/em esp (FLUKE)</t>
+          <t>Luxometro medidor de luminosidad digital de 20 a 200.000 lux lm-100</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1055260</v>
+        <v>729911</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-digital-trms-600v-profesional-fluke115em-esp/</t>
+          <t>https://electrocity.com.ar/productos/luxometro-medidor-de-luminosidad-digital-de-20-a-200000-lulm100/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>01INS00105</t>
+          <t>01INS01300</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 600a ac 600 vca/vcc fluke-303 (FLUKE)</t>
+          <t>Megohmetro digital probador de resistencia de aislamiento h/1000v amb-25</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>512070</v>
+        <v>2564788</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-600a-ac-600-vcavcc-fluke303/</t>
+          <t>https://electrocity.com.ar/productos/megohmetro-digital-probador-de-resistencia-de-aislamiento-h1000v-amb25/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>01INS00205</t>
+          <t>01INS01400</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Comprobador tension continua 12v-690v c/rotacion de fases fluke-t110 (FLUKE)</t>
+          <t>Pinza amperométrica digital 1000a ac 600 vca/vcc (AMPROBE)</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>475291</v>
+        <v>582797</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/comprobador-tension-continua-12v690v-crotacion-de-fases-fluket110/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-1000a-ac-600-vcavcc/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>01INS00290</t>
+          <t>01INS01800</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Detector comprobador electronico luminoso con linterna 90/600v ca lvd2</t>
+          <t>Sonda y generador de tonos analogos pro3000 (FLUKE)</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>198038</v>
+        <v>758203</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/detector-comprobador-electronico-luminoso-con-linterna-90600v-ca-lvd2/</t>
+          <t>https://electrocity.com.ar/productos/sonda-y-generador-de-tonos-analogos-pro3000/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>01INS00300</t>
+          <t>01INS01802</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Pistola de medicion temperatura infraroja -30 °c a 500 °c fluke-62 max</t>
+          <t>Comprobador verificador portatil de cableado redes lan micro mapper (FLUKE)</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>638176</v>
+        <v>636551</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-de-medicion-temperatura-infraroja-30-c-a-500-c-fluke62-max/</t>
+          <t>https://electrocity.com.ar/productos/comprobador-verificador-portatil-de-cableado-redes-lan-micro-mapper/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>01INS01015</t>
+          <t>01INS01855</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Multimetro digital trms 600v ca/cc profesional am-530</t>
+          <t>KIT -DETECTOR ELECTRONICO LUMINOSO/SONORO + PISTOLA INFRAROJA -30 a 500 °C C/AJUSTE DE R</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>632448</v>
+        <v>773974</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-digital-trms-600v-cacc-profesional-am530/</t>
+          <t>https://electrocity.com.ar/productos/kit-detector-electronico-luminososonoro-pistola-infraroja-30-a-500-c-cajuste-de-r/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>01INS01200</t>
+          <t>01JAI00070</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Luxometro medidor de luminosidad digital de 20 a 200.000 lux lm-100</t>
+          <t>Soldador de estaño tipo lapiz 30w 220v (JA)</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>729911</v>
+        <v>11521</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/luxometro-medidor-de-luminosidad-digital-de-20-a-200000-lulm100/</t>
+          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-30w-220v/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>01INS01300</t>
+          <t>01JAI00073</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Megohmetro digital probador de resistencia de aislamiento h/1000v amb-25</t>
+          <t>Soldador de estaño 20/80w 220v (JA)</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>2564788</v>
+        <v>23041</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/megohmetro-digital-probador-de-resistencia-de-aislamiento-h1000v-amb25/</t>
+          <t>https://electrocity.com.ar/productos/soldador-de-estanio-2080w-220v/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>01INS01400</t>
+          <t>01JAI00320</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Pinza amperométrica digital 1000a ac 600 vca/vcc (AMPROBE)</t>
+          <t>Pinza amperometrica digital 750ca/1000vcc c/buzz s/pila (JA)</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>582797</v>
+        <v>16491</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-1000a-ac-600-vcavcc/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-750ca1000vcc-cbuzz-spila/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>01INS01800</t>
+          <t>01JAI00400</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Sonda y generador de tonos analogos pro3000 (FLUKE)</t>
+          <t>Set herramientas 45 pzas c/valija (JA)</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>758203</v>
+        <v>70569</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sonda-y-generador-de-tonos-analogos-pro3000/</t>
+          <t>https://electrocity.com.ar/productos/set-herramientas-45-pzas-cvalija/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>01INS01802</t>
+          <t>01JAI00422</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Comprobador verificador portatil de cableado redes lan micro mapper (FLUKE)</t>
+          <t>Probador de cables de red rj11/12/45 s/bat. -ja- (JA)</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>636551</v>
+        <v>18129</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/comprobador-verificador-portatil-de-cableado-redes-lan-micro-mapper/</t>
+          <t>https://electrocity.com.ar/productos/probador-de-cables-de-red-rj111245-sbat-ja/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>01INS01855</t>
+          <t>01JAI01400</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>KIT -DETECTOR ELECTRONICO LUMINOSO/SONORO + PISTOLA INFRAROJA -30 a 500 °C C/AJUSTE DE R</t>
+          <t>Pinza crimpeadora metálica rj11/45 c/cortacable</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>773974</v>
+        <v>19979</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-detector-electronico-luminososonoro-pistola-infraroja-30-a-500-c-cajuste-de-r/</t>
+          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-metalica-rj1145-ccortacable/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>01JAI00070</t>
+          <t>01JAI01402</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Soldador de estaño tipo lapiz 30w 220v (JA)</t>
+          <t>Pinza crimpeadora metálica rj45 c/cortacable</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>11521</v>
+        <v>13960</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-de-estanio-tipo-lapiz-30w-220v/</t>
+          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-metalica-rj45-ccortacable/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>01JAI00073</t>
+          <t>01JAI01406</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Soldador de estaño 20/80w 220v (JA)</t>
+          <t>Pinza crimpeadora metálica p/terminales tif 0.5/4mm</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>23041</v>
+        <v>38038</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/soldador-de-estanio-2080w-220v/</t>
+          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-metalica-pterminales-tif-054mm/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>01JAI00320</t>
+          <t>01JAI01422</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Pinza amperometrica digital 750ca/1000vcc c/buzz s/pila (JA)</t>
+          <t>Pinza pelacable presicion 0.2 a 6mm c/crimpeadora</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>16491</v>
+        <v>32915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-750ca1000vcc-cbuzz-spila/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pelacable-presicion-02-a-6mm-ccrimpeadora/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>01JAI00400</t>
+          <t>01RED04050</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Set herramientas 45 pzas c/valija (JA)</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø5MM 110MM LARGO</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>70569</v>
+        <v>4782</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-herramientas-45-pzas-cvalija/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-5mm-110mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>01JAI00422</t>
+          <t>01RED04052</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Probador de cables de red rj11/12/45 s/bat. -ja- (JA)</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø6MM 110MM LARGO</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>18129</v>
+        <v>4629</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/probador-de-cables-de-red-rj111245-sbat-ja/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-6mm-110mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>01JAI01400</t>
+          <t>01RED04056</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Pinza crimpeadora metálica rj11/45 c/cortacable</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø8MM 110MM LARGO</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>19979</v>
+        <v>5546</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-metalica-rj1145-ccortacable/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-8mm-110mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>01JAI01402</t>
+          <t>01RED04058</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Pinza crimpeadora metálica rj45 c/cortacable</t>
+          <t>MECHA WIDIA BROCA SDS-PLUS Ø8MM 160MM LARGO</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>13960</v>
+        <v>6238</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-metalica-rj45-ccortacable/</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-8mm-160mm-largo/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>01JAI01406</t>
+          <t>01RED10550</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Pinza crimpeadora metálica p/terminales tif 0.5/4mm</t>
+          <t>Mecha acero broca tipo escalonada de 7 medidas 14-16-18-20-22-24-25mm p/taladros (DEWALT)</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>38038</v>
+        <v>109882</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-metalica-pterminales-tif-054mm/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-broca-tipo-escalonada-de-7-medidas-14161820222425mm-ptaladros/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>01JAI01422</t>
+          <t>01SEG07010</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Pinza pelacable presicion 0.2 a 6mm c/crimpeadora</t>
+          <t>Guante de seguridad dielectrico 2500v talle mediano iram 3604:1998 (KRAFTEK)</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>32915</v>
+        <v>121166</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pelacable-presicion-02-a-6mm-ccrimpeadora/</t>
+          <t>https://electrocity.com.ar/productos/guante-de-seguridad-dielectrico-2500v-talle-mediano-iram-36041998/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>01RED04050</t>
+          <t>01SIC00103</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø5MM 110MM LARGO</t>
+          <t>Puntas de prueba de tensón 100/500vca SICA</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>4782</v>
+        <v>7323</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-5mm-110mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/puntas-de-prueba-de-tenson-100500vca-sica/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>01RED04052</t>
+          <t>01SIC11520</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø6MM 110MM LARGO</t>
+          <t>KIT - 4 DESTORNILLADORES PUNTA PLANA CERO CROMO-VAN SICA (SICA)</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>4629</v>
+        <v>11058</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-6mm-110mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/kit-4-destornilladores-punta-plana-cero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>01RED04056</t>
+          <t>01SIC23590</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø8MM 110MM LARGO</t>
+          <t>Destornillador punta plana 4x75mm acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>5546</v>
+        <v>2471</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-8mm-110mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-4x75mm-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>01RED04058</t>
+          <t>01SIC23591</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>MECHA WIDIA BROCA SDS-PLUS Ø8MM 160MM LARGO</t>
+          <t>Destornillador punta plana 5.5x100mm acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>6238</v>
+        <v>3183</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-broca-sdsplus-8mm-160mm-largo/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-55x100mm-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>01RED10550</t>
+          <t>01SIC23592</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Mecha acero broca tipo escalonada de 7 medidas 14-16-18-20-22-24-25mm p/taladros (DEWALT)</t>
+          <t>Destornillador punta plana 6.5x100mm acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>109882</v>
+        <v>3537</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-broca-tipo-escalonada-de-7-medidas-14161820222425mm-ptaladros/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-65x100mm-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>01SEG07010</t>
+          <t>01SIC23600</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Guante de seguridad dielectrico 2500v talle mediano iram 3604:1998 (KRAFTEK)</t>
+          <t>Destornillador punta plana 6.5x150mm acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>121166</v>
+        <v>3820</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/guante-de-seguridad-dielectrico-2500v-talle-mediano-iram-36041998/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-65x150mm-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>01SIC00103</t>
+          <t>01SIC23642</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Puntas de prueba de tensón 100/500vca SICA</t>
+          <t>Pinza de punta 8 200mm 1000v acero cromo-van SICA</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>7323</v>
+        <v>42755</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/puntas-de-prueba-de-tenson-100500vca-sica/</t>
+          <t>https://electrocity.com.ar/productos/pinza-de-punta-8-200mm-1000v-acero-cromovan-sica/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>01SIC11520</t>
+          <t>01SIC24160</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>KIT - 4 DESTORNILLADORES PUNTA PLANA CERO CROMO-VAN SICA (SICA)</t>
+          <t>Pistola encoladora 100w p/barras adhesivas 11mm 220v 170°</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>11058</v>
+        <v>24853</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-4-destornilladores-punta-plana-cero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/pistola-encoladora-100w-pbarras-adhesivas-11mm-220v-170/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>01SIC23590</t>
+          <t>01TOO01125</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Destornillador punta plana 4x75mm acero cromo-van SICA</t>
+          <t>PORTA CINTA METRICA P/5 8 10 Y 15METROS (TOOLMEN)</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>2471</v>
+        <v>18617</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-4x75mm-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/porta-cinta-metrica-p5-8-10-y-15metros/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>01SIC23591</t>
+          <t>01ZOL04200</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Destornillador punta plana 5.5x100mm acero cromo-van SICA</t>
+          <t>Pinza pelacable 0.2 a 6mm autoajustable - regulable 5 a 12mm</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>3183</v>
+        <v>123031</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-55x100mm-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/pinza-pelacable-02-a-6mm-autoajustable-regulable-5-a-12mm/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>01SIC23592</t>
+          <t>01BAW06036</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Destornillador punta plana 6.5x100mm acero cromo-van SICA</t>
+          <t>Multimetro multirrango manual h/600vcc/vca 10acc 20m cat iii 600v - BAW</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>3537</v>
+        <v>27021</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-65x100mm-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-h600vccvca-10acc-20m-cat-iii-600v-baw/</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>01SIC23600</t>
+          <t>01BAW06039</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Destornillador punta plana 6.5x150mm acero cromo-van SICA</t>
+          <t>Multimetro multirrango manual vca: 80mv/800mv/8v/80v/750.0v. cat iii 600v 1 rms (BAW)</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3820</v>
+        <v>66594</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-punta-plana-65x150mm-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-vca-80mv800mv8v80v7500v-cat-iii-600v-1-rms/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>01SIC23642</t>
+          <t>01BAW06040</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Pinza de punta 8 200mm 1000v acero cromo-van SICA</t>
+          <t>Comprobador digital cables y terminales de red rj45 y usb (BAW)</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>42755</v>
+        <v>60304</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-de-punta-8-200mm-1000v-acero-cromovan-sica/</t>
+          <t>https://electrocity.com.ar/productos/comprobador-digital-cables-y-terminales-de-red-rj45-y-usb/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>01SIC24160</t>
+          <t>01BAW06054</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Pistola encoladora 100w p/barras adhesivas 11mm 220v 170°</t>
+          <t>Pinza amperometrica 1 rms para ambas corrientes ca/cc 60a/600a (BAW)</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>24853</v>
+        <v>131945</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-encoladora-100w-pbarras-adhesivas-11mm-220v-170/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-para-ambas-corrientes-cacc-60a600a/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>01TOO01125</t>
+          <t>01BAW11252</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PORTA CINTA METRICA P/5 8 10 Y 15METROS (TOOLMEN)</t>
+          <t>BAWMS115 MULTIMETRO MEDICION AUTORRANGO SMART 1 RMS (BAW)</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>18617</v>
+        <v>76657</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/porta-cinta-metrica-p5-8-10-y-15metros/</t>
+          <t>https://electrocity.com.ar/productos/bawms115-multimetro-medicion-autorrango-smart-1-rms/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>01ZOL04200</t>
+          <t>01HOM01201</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Pinza pelacable 0.2 a 6mm autoajustable - regulable 5 a 12mm</t>
+          <t>TIJERA CORTA TUBOS PVC genrod (GEN ROD)</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>123031</v>
+        <v>34029</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pelacable-02-a-6mm-autoajustable-regulable-5-a-12mm/</t>
+          <t>https://electrocity.com.ar/productos/tijera-corta-tubos-pvc-genrod/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>01BAW06036</t>
+          <t>01RED04126</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Multimetro multirrango manual h/600vcc/vca 10acc 20m cat iii 600v - BAW</t>
+          <t>MECHA ACERO RAPIDO Ø 10MM EZETA</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>27021</v>
+        <v>20154</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-h600vccvca-10acc-20m-cat-iii-600v-baw/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-10mm-ezeta/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>01BAW06039</t>
+          <t>01RED04106</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Multimetro multirrango manual vca: 80mv/800mv/8v/80v/750.0v. cat iii 600v 1 rms (BAW)</t>
+          <t>MECHA ACERO RAPIDO Ø 4MM EZETA</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>66594</v>
+        <v>4464</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-multirrango-manual-vca-80mv800mv8v80v7500v-cat-iii-600v-1-rms/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-4mm-ezeta/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>01BAW06040</t>
+          <t>01RED04111</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Comprobador digital cables y terminales de red rj45 y usb (BAW)</t>
+          <t>MECHA ACERO RAPIDO Ø 5MM EZETA</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>60304</v>
+        <v>5907</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/comprobador-digital-cables-y-terminales-de-red-rj45-y-usb/</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-5mm-ezeta/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>01HOM01201</t>
+          <t>01JAI00404</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>TIJERA CORTA TUBOS PVC genrod (GEN ROD)</t>
+          <t>DES8600 SET HERRAMIENTAS 2 PZAS + 2 DESTORN. C/BRAZALETE MAGNETICO -JA- (JA)</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>34029</v>
+        <v>23694</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tijera-corta-tubos-pvc-genrod/</t>
+          <t>https://electrocity.com.ar/productos/des8600-set-herramientas-2-pzas-2-destorn-cbrazalete-magnetico-ja/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>01RED04126</t>
+          <t>01JAI00324</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>MECHA ACERO RAPIDO Ø 10MM EZETA</t>
+          <t>INT2010 PINZA AMPEROMETRICA DIGITAL AC 1000A SIN BATERIA -JA- (JA)</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>18056</v>
+        <v>59416</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-10mm-ezeta/</t>
+          <t>https://electrocity.com.ar/productos/int2010-pinza-amperometrica-digital-ac-1000a-sin-bateria-ja/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>01RED04106</t>
+          <t>01JAI00322</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MECHA ACERO RAPIDO Ø 4MM EZETA</t>
+          <t>PINZA AMPEROMETRICA DIGITAL COMPACTA 600CC 450CA S/PILAS -JA- OFERTA-</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>3999</v>
+        <v>18597</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-4mm-ezeta/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-compacta-600cc-450ca-spilas-ja-oferta/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>01RED04111</t>
+          <t>01JAI00310</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>MECHA ACERO RAPIDO Ø 5MM EZETA</t>
+          <t>TESTER MULTIMETRO DIGITAL C/PROBADOR CABLES S/BAT.9V -JA-</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>5292</v>
+        <v>18597</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-rapido-5mm-ezeta/</t>
+          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-cprobador-cables-sbat9v-ja/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>01JAI00404</t>
+          <t>01JAI00066</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DES8600 SET HERRAMIENTAS 2 PZAS + 2 DESTORN. C/BRAZALETE MAGNETICO -JA- (JA)</t>
+          <t>EST7280 ESTAÑO EN CARRETE 60/40 0.8MM 250GR -JA- (JA)</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>23694</v>
+        <v>42264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/des8600-set-herramientas-2-pzas-2-destorn-cbrazalete-magnetico-ja/</t>
+          <t>https://electrocity.com.ar/productos/est7280-estanio-en-carrete-6040-08mm-250gr-ja/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>01JAI00324</t>
+          <t>01EXP00020</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>INT2010 PINZA AMPEROMETRICA DIGITAL AC 1000A SIN BATERIA -JA- (JA)</t>
+          <t>CONJUNTO 122 PIEZAS. 1/4 CROMO-VAN EXTRAPOL (EXTRAPOL)</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>59416</v>
+        <v>68905</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/int2010-pinza-amperometrica-digital-ac-1000a-sin-bateria-ja/</t>
+          <t>https://electrocity.com.ar/productos/conjunto-122-piezas-14-cromovan-extrapol/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>01JAI00322</t>
+          <t>01BUL00147</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PINZA AMPEROMETRICA DIGITAL COMPACTA 600CC 450CA S/PILAS -JA- OFERTA-</t>
+          <t>Juego 6 Destornillador Bulit Mango De Goma Phillips Planos (BULIT)</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>18597</v>
+        <v>47230</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-compacta-600cc-450ca-spilas-ja-oferta/</t>
+          <t>https://electrocity.com.ar/productos/juego-6-destornillador-bulit-mango-de-goma-phillips-planos/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>01JAI00310</t>
+          <t>01BAW06021</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>TESTER MULTIMETRO DIGITAL C/PROBADOR CABLES S/BAT.9V -JA-</t>
+          <t>PINZA AMPEROMETRICA RMS CA VCA: 6V/60V/600V- BAW - BAWCMD04</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>18597</v>
+        <v>85908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/tester-multimetro-digital-cprobador-cables-sbat9v-ja/</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-rms-ca-vca-6v60v600v-baw-bawcmd04/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>01EXP00020</t>
+          <t>01BAW11287</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CONJUNTO 122 PIEZAS. 1/4 CROMO-VAN EXTRAPOL (EXTRAPOL)</t>
+          <t>MULTIMETRO DIGITAL 500V/1000V/2500V C/MEDICION DE AISLACION h/1000V BAW BM3549</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>76561</v>
+        <v>212775</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/conjunto-122-piezas-14-cromovan-extrapol/</t>
+          <t>https://electrocity.com.ar/productos/multimetro-digital-500v1000v2500v-cmedicion-de-aislacion-h1000v-baw-bm3549/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>01BUL00147</t>
+          <t>01BUL00911</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Juego 6 Destornillador Bulit Mango De Goma Phillips Planos (BULIT)</t>
+          <t>Disco Diamantado Bulit Para Amoladora S80 Continuo 115mm (BULIT)</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>47230</v>
+        <v>21476</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-6-destornillador-bulit-mango-de-goma-phillips-planos/</t>
+          <t>https://electrocity.com.ar/productos/disco-diamantado-bulit-para-amoladora-s80-continuo-115mm/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>01BAW06021</t>
+          <t>01ZAP00103</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PINZA AMPEROMETRICA RMS CA VCA: 6V/60V/600V- BAW - BAWCMD04</t>
+          <t>Zapato punta de acero dielectrico cuero flor marron (BORIS)</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>85908</v>
+        <v>115098</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-rms-ca-vca-6v60v600v-baw-bawcmd04/</t>
+          <t>https://electrocity.com.ar/productos/zapato-punta-de-acero-dielectrico-cuero-flor-marron/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>01BAW11287</t>
+          <t>01ZAP00203</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>MULTIMETRO DIGITAL 500V/1000V/2500V C/MEDICION DE AISLACION h/1000V BAW BM3549</t>
+          <t>Botin punta de acero dielectrico cuero flor marron (BORIS)</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>212775</v>
+        <v>139200</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-digital-500v1000v2500v-cmedicion-de-aislacion-h1000v-baw-bm3549/</t>
+          <t>https://electrocity.com.ar/productos/botin-punta-de-acero-dielectrico-cuero-flor-marron/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>01BUL00911</t>
+          <t>01BAW06023</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Disco Diamantado Bulit Para Amoladora S80 Continuo 115mm (BULIT)</t>
+          <t>Pinza cofimetrica multifuncion 1 rms hasta 600 v ca/cc cat iii 600 v bm-157 (BAW)</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>21476</v>
+        <v>502584</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/disco-diamantado-bulit-para-amoladora-s80-continuo-115mm/</t>
+          <t>https://electrocity.com.ar/productos/pinza-cofimetrica-multifuncion-1-rms-hasta-600-v-cacc-cat-iii-600-v-baw-bm157/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>01ZAP00103</t>
+          <t>01BUL00017</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Zapato punta de acero dielectrico cuero flor marron (BORIS)</t>
+          <t>Engrampadora profesional potencia regulable p/grampas 8 a 12mm y clavos 15mm (BULIT)</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>115098</v>
+        <v>90095</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/zapato-punta-de-acero-dielectrico-cuero-flor-marron/</t>
+          <t>https://electrocity.com.ar/productos/engrampadora-profesional-potencia-regulable-pgrampas-8-a-12mm-y-clavos-15mm/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>01ZAP00203</t>
+          <t>01BUL00023</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Botin punta de acero dielectrico cuero flor marron (BORIS)</t>
+          <t>Hoja de sierra junior sin-par (SIN-PAR)</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>139200</v>
+        <v>994</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/botin-punta-de-acero-dielectrico-cuero-flor-marron/</t>
+          <t>https://electrocity.com.ar/productos/hoja-de-sierra-junior-sinpar/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>01BAW06023</t>
+          <t>01BUL00024</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Pinza cofimetrica multifuncion 1 rms hasta 600 v ca/cc cat iii 600 v bm-157 (BAW)</t>
+          <t>Hoja de sierra 24 dientes bimetálica repuesto sin-par (SIN-PAR)</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>502584</v>
+        <v>3573</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-cofimetrica-multifuncion-1-rms-hasta-600-v-cacc-cat-iii-600-v-baw-bm157/</t>
+          <t>https://electrocity.com.ar/productos/hoja-de-sierra-24-dientes-bimetalica-repuesto-sinpar/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>01BUL00017</t>
+          <t>01BUL00042</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Engrampadora profesional potencia regulable p/grampas 8 a 12mm y clavos 15mm (BULIT)</t>
+          <t>Grampas hobbista 6mm p/engrampadoras x 1000 unidades (BULIT)</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>90095</v>
+        <v>9812</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/engrampadora-profesional-potencia-regulable-pgrampas-8-a-12mm-y-clavos-15mm/</t>
+          <t>https://electrocity.com.ar/productos/grampas-hobbista-6mm-pengrampadoras-1000-unidades/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>01BUL00023</t>
+          <t>01BUL00043</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Hoja de sierra junior sin-par (SIN-PAR)</t>
+          <t>Grampas hobbista 8mm p/engrampadora x 1000 unidades (BULIT)</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>994</v>
+        <v>13242</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/hoja-de-sierra-junior-sinpar/</t>
+          <t>https://electrocity.com.ar/productos/grampas-hobbista-8mm-pengrampadora-1000-unidades/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>01BUL00024</t>
+          <t>01BUL00046</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Hoja de sierra 24 dientes bimetálica repuesto sin-par (SIN-PAR)</t>
+          <t>Grampas 8mm p/engrampadora profesional x 1000 unidades (BULIT)</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3573</v>
+        <v>15983</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/hoja-de-sierra-24-dientes-bimetalica-repuesto-sinpar/</t>
+          <t>https://electrocity.com.ar/productos/grampas-8mm-pengrampadora-profesional-1000-unidades/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>01BUL00042</t>
+          <t>01BUL00047</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Grampas hobbista 6mm p/engrampadoras x 1000 unidades (BULIT)</t>
+          <t>Grampas 12mm p/engrampadora profesional x 1000 unidades (BULIT)</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>9812</v>
+        <v>18911</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/grampas-hobbista-6mm-pengrampadoras-1000-unidades/</t>
+          <t>https://electrocity.com.ar/productos/grampas-12mm-pengrampadora-profesional-1000-unidades/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>01BUL00043</t>
+          <t>01BUL00049</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Grampas hobbista 8mm p/engrampadora x 1000 unidades (BULIT)</t>
+          <t>Clavos de 15mm p/engrampadora profesional x 500 unidades (BULIT)</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>13242</v>
+        <v>13475</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/grampas-hobbista-8mm-pengrampadora-1000-unidades/</t>
+          <t>https://electrocity.com.ar/productos/clavos-de-15mm-pengrampadora-profesional-500-unidades/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>01BUL00046</t>
+          <t>01BUL00050</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Grampas 8mm p/engrampadora profesional x 1000 unidades (BULIT)</t>
+          <t>Destornillador aislado 1000v phillips cromo-vanadio 2 x 100mm serie 800 (BULIT)</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>15983</v>
+        <v>10266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/grampas-8mm-pengrampadora-profesional-1000-unidades/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-phillips-cromovanadio-2-100mm-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>01BUL00047</t>
+          <t>01BUL00055</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Grampas 12mm p/engrampadora profesional x 1000 unidades (BULIT)</t>
+          <t>Destornillador aislado 1000v recto cromo-vanadio 4 x 100mm serie 800 (BULIT)</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>18911</v>
+        <v>6570</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/grampas-12mm-pengrampadora-profesional-1000-unidades/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-recto-cromovanadio-4-100mm-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>01BUL00049</t>
+          <t>01BUL00056</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Clavos de 15mm p/engrampadora profesional x 500 unidades (BULIT)</t>
+          <t>Destornillador aislado 1000v recto cromo-vanadio 5.5 x 125mm serie 800 (BULIT)</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>13475</v>
+        <v>8713</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/clavos-de-15mm-pengrampadora-profesional-500-unidades/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-recto-cromovanadio-55-125mm-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>01BUL00050</t>
+          <t>01BUL00058</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v phillips cromo-vanadio 2 x 100mm serie 800 (BULIT)</t>
+          <t>Destornillador aislado 1000v recto cromo-vanadio 6.5 x 150mm serie 800 (BULIT)</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>10266</v>
+        <v>9324</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-phillips-cromovanadio-2-100mm-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-recto-cromovanadio-65-150mm-serie-800/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>01BUL00055</t>
+          <t>01BUL00462</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v recto cromo-vanadio 4 x 100mm serie 800 (BULIT)</t>
+          <t>Cutter profesional automatico c/refuerzo y freno a rosca c/crique (BULIT)</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>6570</v>
+        <v>22595</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-recto-cromovanadio-4-100mm-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/cutter-profesional-automatico-crefuerzo-y-freno-a-rosca-ccrique/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>01BUL00056</t>
+          <t>01BUL01986</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v recto cromo-vanadio 5.5 x 125mm serie 800 (BULIT)</t>
+          <t>Set de puntas largas y tubos 24 piezas + tubo criquet +estuche bulit (BULIT)</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>8713</v>
+        <v>67760</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-recto-cromovanadio-55-125mm-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/set-de-puntas-largas-y-tubos-24-piezas-tubo-criquet-estuche-bulit/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>01BUL00058</t>
+          <t>01BAW06046</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Destornillador aislado 1000v recto cromo-vanadio 6.5 x 150mm serie 800 (BULIT)</t>
+          <t>Telurimetro medidor puesta tierra h/2000?</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>9324</v>
+        <v>379722</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-aislado-1000v-recto-cromovanadio-65-150mm-serie-800/</t>
+          <t>https://electrocity.com.ar/productos/telurimetro-medidor-puesta-tierra-h2000/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>01BUL00462</t>
+          <t>01MIL00152</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Cutter profesional automatico c/refuerzo y freno a rosca c/crique (BULIT)</t>
+          <t>MOCHILA PORTA HERRAMIENTAS C/48 BOLSILLOS 400x400x300MM IP65 MILWAUKEE 4822-8301</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>22595</v>
+        <v>327777.55</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cutter-profesional-automatico-crefuerzo-y-freno-a-rosca-ccrique/</t>
+          <t>https://electrocity.com.ar/productos/mochila-porta-herramientas-c48-bolsillos-400x400x300mm-ip65-milwaukee-48228301/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>01BUL01986</t>
+          <t>01MIL00639</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Set de puntas largas y tubos 24 piezas + tubo criquet +estuche bulit (BULIT)</t>
+          <t>Combo Organizador Packout 3 Cajas Milwaukee</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>67760</v>
+        <v>752274.6</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-puntas-largas-y-tubos-24-piezas-tubo-criquet-estuche-bulit/</t>
+          <t>https://electrocity.com.ar/productos/combo-organizador-packout-3-cajas-milwaukee-1gp47/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>01BAW06046</t>
+          <t>01MIL00110</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Telurimetro medidor puesta tierra h/2000?</t>
+          <t>Caja de Herramientas con 3 Cajones Packout Milwaukee 4822-8443</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>379722</v>
+        <v>451747</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/telurimetro-medidor-puesta-tierra-h2000/</t>
+          <t>https://electrocity.com.ar/productos/caja-de-herramientas-con-3-cajones-packout-milwaukee-4822-8443/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>01MIL00152</t>
+          <t>01MIL00360</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MOCHILA PORTA HERRAMIENTAS C/48 BOLSILLOS 400x400x300MM IP65 MILWAUKEE 4822-8301</t>
+          <t>Placa de Montaje Amurar Pared Piso Packout Milwaukee 4822- 8485</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>327777.55</v>
+        <v>123088</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mochila-porta-herramientas-c48-bolsillos-400x400x300mm-ip65-milwaukee-48228301/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/placa-de-montaje-amurar-pared-piso-packout-milwaukee-4822-8485/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>01MIL00639</t>
+          <t>01MIL00124</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Combo Organizador Packout 3 Cajas Milwaukee</t>
+          <t>Caja de Herramientas Packout 4 Cajones Milwaukee 4822-8444</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>752274.6</v>
+        <v>623183</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-organizador-packout-3-cajas-milwaukee-1gp47/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/caja-de-herramientas-packout-4-cajones-milwaukee-4822-8444/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>01MIL00110</t>
+          <t>01HRT09044</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Caja de Herramientas con 3 Cajones Packout Milwaukee 4822-8443</t>
+          <t>Pinza Punta Semi Redonda 160mm Bahco 2470 G-160</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>451747</v>
+        <v>24519</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/caja-de-herramientas-con-3-cajones-packout-milwaukee-4822-8443/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-punta-semi-redonda-160mm-bahco-2470-g-160/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>01MIL00360</t>
+          <t>01MIL00623</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Placa de Montaje Amurar Pared Piso Packout Milwaukee 4822- 8485</t>
+          <t>Caja Herramientas 2 Cajones Packout Milwaukee 4822-8442</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>123088</v>
+        <v>505461.75</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/placa-de-montaje-amurar-pared-piso-packout-milwaukee-4822-8485/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/caja-herramientas-2-cajones-packout-milwaukee-4822-8442-an020/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>01MIL00124</t>
+          <t>01BAW11250</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Caja de Herramientas Packout 4 Cajones Milwaukee 4822-8444</t>
+          <t>Multimetro Tester Digital BAW Medidor Display Led BAWm02</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>623183</v>
+        <v>18644</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/caja-de-herramientas-packout-4-cajones-milwaukee-4822-8444/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/multimetro-tester-digital-baw-medidor-display-led-bawm02/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>01BAW06010</t>
+          <t>01MIL00352</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Buscapolo inductivo detector de tension BAW sonido y luz</t>
+          <t>Set de Destornilladores Premium 10 Piezas Milwaukee 4822-2710</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>8932</v>
+        <v>85674</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/buscapolo-inductivo-detector-de-tension-baw-sonido-y-luz/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-de-destornilladores-premium-10-piezas-milwaukee-4822-2710/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>01HRT09044</t>
+          <t>01MIL00320</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Pinza Punta Semi Redonda 160mm Bahco 2470 G-160</t>
+          <t>Set Puntas Tubos Impacto x 26 Piezas Milwaukee 4832-4408</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>24519</v>
+        <v>99249</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-punta-semi-redonda-160mm-bahco-2470-g-160/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-puntas-tubos-impacto-x-26-piezas-milwaukee-4832-4408/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>01MIL00623</t>
+          <t>01HOM01200</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Caja Herramientas 2 Cajones Packout Milwaukee 4822-8442</t>
+          <t>MECHA ESCALONADA CALADORA MULTIPLE P/CAJAS plásticaS</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>505461.75</v>
+        <v>92143</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/caja-herramientas-2-cajones-packout-milwaukee-4822-8442-an020/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-escalonada-caladora-multiple-pcajas-plasticas/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>01BAW11250</t>
+          <t>01RED04453</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Multimetro Tester Digital BAW Medidor Display Led BAWm02</t>
+          <t>MECHA WIDIA Ø 6MM STANDARD CORTA 100MM FISCHER</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>18644</v>
+        <v>3824</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/multimetro-tester-digital-baw-medidor-display-led-bawm02/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-widia-6mm-standard-corta-100mm-fischer/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>01MIL00352</t>
+          <t>01MIL00617</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Set de Destornilladores Premium 10 Piezas Milwaukee 4822-2710</t>
+          <t>Taladro Atornillador Percutor a Batería 18v Milwaukee 2607-259A</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>85674</v>
+        <v>886200.65</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-destornilladores-premium-10-piezas-milwaukee-4822-2710/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/taladro-atornillador-percutor-a-bateria-18v-milwaukee-2607-259a-1uq1y/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>01MIL00320</t>
+          <t>01BAW11254</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Set Puntas Tubos Impacto x 26 Piezas Milwaukee 4832-4408</t>
+          <t>Pinza Amperométrica Digital Autorrango True Rms 600v Baw CM05</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>99249</v>
+        <v>35477</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-puntas-tubos-impacto-x-26-piezas-milwaukee-4832-4408/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-autorrango-true-rms-600v-baw-cm05/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>01HOM01200</t>
+          <t>01SIC00090</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MECHA ESCALONADA CALADORA MULTIPLE P/CAJAS plásticaS</t>
+          <t>Pinza amperometrica digital con termocupla SICA</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>92143</v>
+        <v>78587</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-escalonada-caladora-multiple-pcajas-plasticas/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-con-termocupla-sica/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>01RED04453</t>
+          <t>01MIL00612</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>MECHA WIDIA Ø 6MM STANDARD CORTA 100MM FISCHER</t>
+          <t>Caja Organizador Chato Packout Milwaukee 4822-8431</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3824</v>
+        <v>135327.5</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-widia-6mm-standard-corta-100mm-fischer/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/caja-organizador-chato-packout-milwaukee-4822-8431-ign4n/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>01MIL00617</t>
+          <t>01MIL00618</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Taladro Atornillador Percutor a Batería 18v Milwaukee 2607-259A</t>
+          <t>Llave de Impacto 3/4'' M18 Fuel Milwaukee 2864-20 SIN BATERIA</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>886200.65</v>
+        <v>1433092</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-atornillador-percutor-a-bateria-18v-milwaukee-2607-259a-1uq1y/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/llave-de-impacto-fuel-encastre-1-2-one-key-milwaukee-2863-20-mwmi8/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>01BAW11254</t>
+          <t>01TOO01094</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Pinza Amperométrica Digital Autorrango True Rms 600v Baw CM05</t>
+          <t>Cinturón Portaherramientas Toolmen T37</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>35477</v>
+        <v>69658</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-digital-autorrango-true-rms-600v-baw-cm05/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/cinturon-portaherramientas-toolmen-t37-jrliq/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>01MIL00612</t>
+          <t>01HRT06662</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Caja Organizador Chato Packout Milwaukee 4822-8431</t>
+          <t>Juego de Puntas x 31 Piezas Torx Phillips Plano Bahco 59S31B</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>135327.5</v>
+        <v>38442</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/caja-organizador-chato-packout-milwaukee-4822-8431-ign4n/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/juego-de-puntas-x-31-piezas-torx-phillips-plano-bahco-59s31b/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>01MIL00618</t>
+          <t>01BUL02170</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Llave de Impacto 3/4'' M18 Fuel Milwaukee 2864-20 SIN BATERIA</t>
+          <t>Llave ajustable 6 cromada c/mango ergonomico antideslizante (BULIT)</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>1433092</v>
+        <v>18355</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/llave-de-impacto-fuel-encastre-1-2-one-key-milwaukee-2863-20-mwmi8/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/llave-ajustable-6-cromada-cmango-ergonomico-antideslizante/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>01TOO01094</t>
+          <t>01HRT05640</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Cinturón Portaherramientas Toolmen T37</t>
+          <t>Mecha de acero repuesto para sierra copa bimetálica soporte a1 y a2</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>69658</v>
+        <v>6920</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinturon-portaherramientas-toolmen-t37-jrliq/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-de-acero-repuesto-para-sierra-copa-bimetalica-soporte-a1-y-a2/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>01HRT06662</t>
+          <t>01SIC00104</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Juego de Puntas x 31 Piezas Torx Phillips Plano Bahco 59S31B</t>
+          <t>Detector indicador luminoso de voltaje catiii 70-1000vca (SICA)</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>36612</v>
+        <v>22990</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/juego-de-puntas-x-31-piezas-torx-phillips-plano-bahco-59s31b/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/detector-indicador-luminoso-de-voltaje-catiii-701000vca/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>01HRT05640</t>
+          <t>01BUL02090</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Mecha de acero repuesto para sierra copa bimetálica soporte a1 y a2</t>
+          <t>NVL S6 3B 40 A NIVEL 3 BURBUJAS 400MM ALUMINIO BULIT (BULIT)</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>6920</v>
+        <v>27841</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-de-acero-repuesto-para-sierra-copa-bimetalica-soporte-a1-y-a2/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/nvl-s6-3b-40-a-nivel-3-burbujas-400mm-aluminio-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>01HRT09022</t>
+          <t>01ZOL04207</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Pinza Punta Semiredonda 6 Aislada 1000v Bahco 2430S-160A-RN</t>
+          <t>Pinza Crimpeadora Terminales Tiff para Cables 0.25 a 10mm Zoloda CRIMP-10</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>61765</v>
+        <v>155663</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-punta-semiredonda-6-aislada-1000v-bahco-2430s-160a-rn/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-crimpeadora-terminales-tiff-para-cables-0-25-a-10mm-zoloda-crimp-10-sqxcn/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>01MIL00400</t>
+          <t>01BAW06047</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Conservadora Compacta Packout 15 Litros Milwaukee 4822-8460</t>
+          <t>Termómetro Infrarrojo Láser +800°C Baw RM800PRO</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>326526</v>
+        <v>92391</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/conservadora-compacta-packout-15-litros-milwaukee-4822-8460/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/termometro-infrarrojo-laser-800c-baw-rm800pro/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>01BUL01854</t>
+          <t>01MIL00400</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA PROFESIONAL PEGAMENTO + 8 BARRAS 112MM X 30CM SUPRABOND</t>
+          <t>Conservadora Compacta Packout 15 Litros Milwaukee 4822-8460</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>91686</v>
+        <v>326526</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-pegamento-8-barras-112mm-30cm-suprabond/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/conservadora-compacta-packout-15-litros-milwaukee-4822-8460/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>01BUL02264</t>
+          <t>01BUL00780</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Pinza pta. redonda 6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Pinza pico de loro profesional de 10 serie 700 (BULIT)</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>13516</v>
+        <v>33794</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-pta-redonda-6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-pico-de-loro-profesional-de-10-serie-700/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>01HRT05605</t>
+          <t>01BUL01854</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Mecha copa bimetálica traspasadora hss ø22mm 7/8</t>
+          <t>KIT - PISTOLA PROFESIONAL PEGAMENTO + 8 BARRAS 112MM X 30CM SUPRABOND</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>11126</v>
+        <v>91686</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-22mm-78/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-profesional-pegamento-8-barras-112mm-30cm-suprabond/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>01INS00100</t>
+          <t>01BUL02264</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 400a ac 600 vca/vcc fluke-302 (FLUKE)</t>
+          <t>Pinza pta. redonda 6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>455487</v>
+        <v>13516</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-400a-ac-600-vcavcc-fluke302/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-pta-redonda-6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>01TOO01024</t>
+          <t>01HRT05605</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Porta-herramientas cartuchera p/electricistas mini (TOOLMEN)</t>
+          <t>Mecha copa bimetálica traspasadora hss ø22mm 7/8</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>15157</v>
+        <v>11126</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-mini/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-copa-bimetalica-traspasadora-hss-22mm-78/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>01TOO01095</t>
+          <t>01INS00015</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Cinto de 50mm p/ sujetar porta-herramientas naranja (TOOLMEN)</t>
+          <t>Multimetro digital 600v + frecuencia + diodo fluke-107 esp (FLUKE)</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>20431</v>
+        <v>523386</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinto-de-50mm-p-sujetar-portaherramientas-naranja/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/multimetro-digital-600v-frecuencia-diodo-fluke107-esp/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>01BAW06056</t>
+          <t>01INS00100</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 1 rms para corriente alterna 60a/600a/1000a (BAW)</t>
+          <t>Pinza amperometrica 400a ac 600 vca/vcc fluke-302 (FLUKE)</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>149541</v>
+        <v>455487</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-para-corriente-alterna-60a600a1000a/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-400a-ac-600-vcavcc-fluke302/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>01MIL00638</t>
+          <t>01TOO01024</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Combo Versátil Packout 4 Cajas Milwaukee</t>
+          <t>Porta-herramientas cartuchera p/electricistas mini (TOOLMEN)</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>944100.5</v>
+        <v>15157</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-versatil-packout-4-cajas-milwaukee-jyp50/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/portaherramientas-cartuchera-pelectricistas-mini/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>01MIL00502</t>
+          <t>01TOO01095</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Combo Completo Packout 6 Cajas Milwaukee</t>
+          <t>Cinto de 50mm p/ sujetar porta-herramientas naranja (TOOLMEN)</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1100359.35</v>
+        <v>20431</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-completo-packout-6-cajas-milwaukee-pwa2i/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/cinto-de-50mm-p-sujetar-portaherramientas-naranja/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>01MIL00504</t>
+          <t>01BAW06056</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Combo Básico Packout 3 Cajas Milwaukee 8424 + 8425 + 8427</t>
+          <t>Pinza amperometrica 1 rms para corriente alterna 60a/600a/1000a (BAW)</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>809816.1</v>
+        <v>149541</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/combo-basico-packout-milwaukee-3-cajas-8424-8425-8427-bq0m1/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-para-corriente-alterna-60a600a1000a/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>01MIL00610</t>
+          <t>01MIL00638</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Batería Capacidad Extendida M18 RedLithium XC 4.0 Milwaukee 4811-1840</t>
+          <t>Combo Versátil Packout 4 Cajas Milwaukee</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>245637</v>
+        <v>944100.5</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bateria-capacidad-extendida-m18-redlithium-xc-4-0-milwaukee-4811-1840-1h696/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/combo-versatil-packout-4-cajas-milwaukee-jyp50/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>01MIL00622</t>
+          <t>01MIL00502</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Cinta Métrica Magnetica Retráctil 8 Metros Milwaukee 4822-1026M</t>
+          <t>Combo Completo Packout 6 Cajas Milwaukee</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>66938</v>
+        <v>1100359.35</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-metrica-magnetica-retractil-8-metros-milwaukee-4822-1026m-1qoyn/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/combo-completo-packout-6-cajas-milwaukee-pwa2i/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>01BLO00030</t>
+          <t>01MIL00504</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Bloqueador de Térmica Unipolar Transparente E1 Blook ELE-2110</t>
+          <t>Combo Básico Packout 3 Cajas Milwaukee 8424 + 8425 + 8427</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>20971</v>
+        <v>809816.1</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bloqueador-de-termica-unipolar-transparente-e1-blook-ele-2110-z8wpw/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/combo-basico-packout-milwaukee-3-cajas-8424-8425-8427-bq0m1/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>01BLO00002</t>
+          <t>01MIL00610</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Candado Dieléctrico Arandela Plástica 40mm Bioseif CAN-1010</t>
+          <t>Batería Capacidad Extendida M18 RedLithium XC 4.0 Milwaukee 4811-1840</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>22911</v>
+        <v>245637</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/candado-dielectrico-arandela-plastica-40mm-bioseif-can-1010-9l1aq/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/bateria-capacidad-extendida-m18-redlithium-xc-4-0-milwaukee-4811-1840-1h696/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>01BUL02250</t>
+          <t>01MIL00622</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Alicate Extra Ancho 7" Serie 600 Bulit PZA S6 AL7 E</t>
+          <t>Cinta Métrica Magnetica Retráctil 8 Metros Milwaukee 4822-1026M</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>19514</v>
+        <v>66938</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/alicate-extra-ancho-7-serie-600-bulit-pza-s6-al7-e/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/cinta-metrica-magnetica-retractil-8-metros-milwaukee-4822-1026m-1qoyn/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>01HRT06664</t>
+          <t>01BLO00030</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Punta Atornillador Pozidriv Largo 25mm Pz2 HRT 258253</t>
+          <t>Bloqueador de Térmica Unipolar Transparente E1 Blook ELE-2110</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>598</v>
+        <v>20971</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/punta-atornillador-pozidriv-largo-25mm-pz2-hrt-258253/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/bloqueador-de-termica-unipolar-transparente-e1-blook-ele-2110-z8wpw/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>01MIL00605</t>
+          <t>01BLO00002</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Taladro Atornillador Milwaukee 2607-20 Percutor</t>
+          <t>Candado Dieléctrico Arandela Plástica 40mm Bioseif CAN-1010</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>361069</v>
+        <v>22911</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/taladro-atornillador-milwaukee-2607-20-percutor-g8oop/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/candado-dielectrico-arandela-plastica-40mm-bioseif-can-1010-9l1aq/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>01HRT05132</t>
+          <t>01BUL02250</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Destornillador Crique Portapunta De 1/4 Stubby 808050S (BAHCO)</t>
+          <t>Alicate Extra Ancho 7" Serie 600 Bulit PZA S6 AL7 E</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>38269</v>
+        <v>19514</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-crique-portapunta-de-1-4-stubby-808050s-bahco/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/alicate-extra-ancho-7-serie-600-bulit-pza-s6-al7-e/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>01BAW06030</t>
+          <t>01HRT06664</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 1 rms ca cat iii 600v - BAW rm901d</t>
+          <t>Punta Atornillador Pozidriv Largo 25mm Pz2 HRT 258253</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>53401</v>
+        <v>597</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-ca-cat-iii-600v-baw-rm901d/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/punta-atornillador-pozidriv-largo-25mm-pz2-hrt-258253/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>01BAW06031</t>
+          <t>01MIL00605</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 1 rms ca vca/cc: 0001~600v- BAW rm900a</t>
+          <t>Taladro Atornillador Milwaukee 2607-20 Percutor</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>63548</v>
+        <v>361069</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-ca-vca-cc-0001600v-baw-rm900a/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/taladro-atornillador-milwaukee-2607-20-percutor-g8oop/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>01BUL00031</t>
+          <t>01HRT05132</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Sie s2 12 mini arco de sierra 12 serie 200 (BULIT)</t>
+          <t>Destornillador Crique Portapunta De 1/4 Stubby 808050S (BAHCO)</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>19457</v>
+        <v>38269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/sie-s2-12-mini-arco-de-sierra-12-serie-200/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/destornillador-crique-portapunta-de-1-4-stubby-808050s-bahco/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>01BUL00084</t>
+          <t>01BAW06030</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Destornillador profesional #2x100mm punta phillips (BULIT)</t>
+          <t>Pinza amperometrica 1 rms ca cat iii 600v - BAW rm901d</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>9656</v>
+        <v>53401</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-2x100mm-punta-phillips/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-ca-cat-iii-600v-baw-rm901d/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>01BUL00096</t>
+          <t>01BAW06031</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Destornillador profesional #5x150mm punta plana (BULIT)</t>
+          <t>Pinza amperometrica 1 rms ca vca/cc: 0001~600v- BAW rm900a</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>7835</v>
+        <v>63548</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/destornillador-profesional-5x150mm-punta-plana/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-ca-vca-cc-0001600v-baw-rm900a/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>01BUL00110</t>
+          <t>01BUL00031</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>SET DE 11 DESTORNILLADORES PROFESIONAL PUNTA PLANA Y PHILLIPS (BULIT)</t>
+          <t>Sie s2 12 mini arco de sierra 12 serie 200 (BULIT)</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>95648</v>
+        <v>19457</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-11-destornilladores-profesional-punta-plana-y-phillips/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/sie-s2-12-mini-arco-de-sierra-12-serie-200/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>01BUL00111</t>
+          <t>01BUL00084</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>SET DE 6 DESTORNILLADORES PROFESIONAL PUNTA PHILLIPS (BULIT)</t>
+          <t>Destornillador profesional #2x100mm punta phillips (BULIT)</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>54644</v>
+        <v>9656</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-profesional-punta-phillips/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-2x100mm-punta-phillips/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>01BUL00113</t>
+          <t>01BUL00096</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>SET DE 6 DESTORNILLADORES PROFESIONAL PUNTA PHILLIPS Y RECTO (BULIT)</t>
+          <t>Destornillador profesional #5x150mm punta plana (BULIT)</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>74485</v>
+        <v>7835</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-profesional-punta-phillips-y-recto/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/destornillador-profesional-5x150mm-punta-plana/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>01BUL01848</t>
+          <t>01BUL00110</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>KIT - PISTOLA DE PEGAMENTO 40W + 10 BARRAS TRANSPARENTE 112x30CM EN BLISTER</t>
+          <t>SET DE 11 DESTORNILLADORES PROFESIONAL PUNTA PLANA Y PHILLIPS (BULIT)</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>51289</v>
+        <v>95648</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-pistola-de-pegamento-40w-10-barras-transparente-112x30cm-en-blister/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-de-11-destornilladores-profesional-punta-plana-y-phillips/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>01BUL01849</t>
+          <t>01BUL00111</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PISTOLA DE PEGAMENTO BULIT 40W + 50 BARRAS TRANSPARENTE 112x30CM</t>
+          <t>SET DE 6 DESTORNILLADORES PROFESIONAL PUNTA PHILLIPS (BULIT)</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>135741</v>
+        <v>54644</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pistola-de-pegamento-bulit-40w-50-barras-transparente-112x30cm/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-profesional-punta-phillips/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>01BUL02249</t>
+          <t>01BUL00113</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Alicate 6 aisl. acero-carbono mango aislado serie 600 bulit (BULIT)</t>
+          <t>SET DE 6 DESTORNILLADORES PROFESIONAL PUNTA PHILLIPS Y RECTO (BULIT)</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>14736</v>
+        <v>74485</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/alicate-6-aisl-acerocarbono-mango-aislado-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/set-de-6-destornilladores-profesional-punta-phillips-y-recto/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>01BUL02254</t>
+          <t>01BUL01848</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Pinza universal 6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>KIT - PISTOLA DE PEGAMENTO 40W + 10 BARRAS TRANSPARENTE 112x30CM EN BLISTER</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>17870</v>
+        <v>51289</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-pistola-de-pegamento-40w-10-barras-transparente-112x30cm-en-blister/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>01BUL02256</t>
+          <t>01BUL01849</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Pinza universal 7 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>PISTOLA DE PEGAMENTO BULIT 40W + 50 BARRAS TRANSPARENTE 112x30CM</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>19942</v>
+        <v>135741</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-7-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pistola-de-pegamento-bulit-40w-50-barras-transparente-112x30cm/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>01BUL02258</t>
+          <t>01BUL02249</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Pinza universal 8 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Alicate 6 aisl. acero-carbono mango aislado serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>22590</v>
+        <v>14736</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-universal-8-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/alicate-6-aisl-acerocarbono-mango-aislado-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>01BUL02260</t>
+          <t>01BUL02254</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Pinza pta.semi-red.6 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Pinza universal 6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>14330</v>
+        <v>17870</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-ptasemired6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>01BUL02262</t>
+          <t>01BUL02256</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Pinza pta.semi-red. 8 acero-carbono serie 600 bulit (BULIT)</t>
+          <t>Pinza universal 7 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>18273</v>
+        <v>19942</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-ptasemired-8-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-7-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>01EXP00004</t>
+          <t>01BUL02258</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 15 metros c/porta-pasacable</t>
+          <t>Pinza universal 8 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>69924</v>
+        <v>22590</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-15-metros-cportapasacable/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-universal-8-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>01HRT04920</t>
+          <t>01BUL02260</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Pinza corta pela-cable de cobre o aluminio hasta ø35mm</t>
+          <t>Pinza pta.semi-red.6 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>93168</v>
+        <v>14330</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-corta-pelacable-de-cobre-o-aluminio-hasta-35mm/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-ptasemired6-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>01INS00200</t>
+          <t>01BUL02262</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Comprobador tension continua 12v-690v h/400 fluke-t90</t>
+          <t>Pinza pta.semi-red. 8 acero-carbono serie 600 bulit (BULIT)</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>393247</v>
+        <v>18273</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/comprobador-tension-continua-12v690v-h400-fluket90/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-ptasemired-8-acerocarbono-serie-600-bulit/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>01INS01805</t>
+          <t>01EXP00004</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Crimpeadora rj-11/12/45 pelacable cortadora fluke (FLUKE)</t>
+          <t>Cinta pasacable plástica con alma de acero ø5mm 120kgf 15 metros c/porta-pasacable</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>486377</v>
+        <v>79913</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/crimpeadora-rj111245-pelacable-cortadora-fluke/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/cinta-pasacable-plastica-con-alma-de-acero-5mm-120kgf-15-metros-cportapasacable/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>01INS01807</t>
+          <t>01HRT04920</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Herramienta de impacto 110/66 c/cuchilla fluke</t>
+          <t>Pinza corta pela-cable de cobre o aluminio hasta ø35mm</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>613393</v>
+        <v>93168</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/herramienta-de-impacto-11066-ccuchilla-fluke/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/pinza-corta-pelacable-de-cobre-o-aluminio-hasta-35mm/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>01INS01854</t>
+          <t>01INS00200</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>KIT - CRIMPEADORA PELACABLE-CORTADOR + COMPROBADOR + GENERADR TONOS + HERR. IMPACTO - FLUK (FLUKE)</t>
+          <t>Comprobador tension continua 12v-690v h/400 fluke-t90</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>2494523</v>
+        <v>393247</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-crimpeadora-pelacablecortador-comprobador-generadr-tonos-herr-impacto-fluk/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/comprobador-tension-continua-12v690v-h400-fluket90/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>01RED10551</t>
+          <t>01INS01805</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Mecha acero broca tipo escalonada de 8 medidas 20-22-24-26-28-30-32-34mm p/taladros (DEWALT)</t>
+          <t>Crimpeadora rj-11/12/45 pelacable cortadora fluke (FLUKE)</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>179353</v>
+        <v>486377</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/mecha-acero-broca-tipo-escalonada-de-8-medidas-2022242628303234mm-ptaladros/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/crimpeadora-rj111245-pelacable-cortadora-fluke/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>01SIC11524</t>
+          <t>01INS01807</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>KIT - 4 DESTORNILLADORES PUNTA PLANA + 2 PUNTA PHILIPS ACERO CROMO-VAN SICA (SICA)</t>
+          <t>Herramienta de impacto 110/66 c/cuchilla fluke</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>11058</v>
+        <v>613393</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-4-destornilladores-punta-plana-2-punta-philips-acero-cromovan-sica/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/herramienta-de-impacto-11066-ccuchilla-fluke/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>01TOO00220</t>
+          <t>01INS01854</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Kit portaherramienta grande + cinto 50mm toolmen (TOOLMEN)</t>
+          <t>KIT - CRIMPEADORA PELACABLE-CORTADOR + COMPROBADOR + GENERADR TONOS + HERR. IMPACTO - FLUK (FLUKE)</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>67456</v>
+        <v>2494523</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/kit-portaherramienta-grande-cinto-50mm-toolmen/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-crimpeadora-pelacablecortador-comprobador-generadr-tonos-herr-impacto-fluk/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>01TOO01010</t>
+          <t>01RED10551</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Porta celular funda smart-phone grande hasta 160mm (TOOLMEN)</t>
+          <t>Mecha acero broca tipo escalonada de 8 medidas 20-22-24-26-28-30-32-34mm p/taladros (DEWALT)</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>19802</v>
+        <v>179353</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/porta-celular-funda-smartphone-grande-hasta-160mm/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/mecha-acero-broca-tipo-escalonada-de-8-medidas-2022242628303234mm-ptaladros/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>01USH00020</t>
+          <t>01SIC11524</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Dobladora de caños 3/4" una palanca con resorte adaptador para caños de 5/8"</t>
+          <t>KIT - 4 DESTORNILLADORES PUNTA PLANA + 2 PUNTA PHILIPS ACERO CROMO-VAN SICA (SICA)</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>117674</v>
+        <v>11058</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/dobladora-de-canios-34-una-palanca-con-resorte-adaptador-para-canios-de-58/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-4-destornilladores-punta-plana-2-punta-philips-acero-cromovan-sica/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>01BAW06054</t>
+          <t>01TOO00220</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Pinza amperometrica 1 rms para ambas corrientes ca/cc 60a/600a (BAW)</t>
+          <t>Kit portaherramienta grande + cinto 50mm toolmen (TOOLMEN)</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>131945</v>
+        <v>67456</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/pinza-amperometrica-1-rms-para-ambas-corrientes-cacc-60a600a/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/kit-portaherramienta-grande-cinto-50mm-toolmen/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>01BAW11252</t>
+          <t>01TOO01010</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>BAWMS115 MULTIMETRO MEDICION AUTORRANGO SMART 1 RMS (BAW)</t>
+          <t>Porta celular funda smart-phone grande hasta 160mm (TOOLMEN)</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>76657</v>
+        <v>19802</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/bawms115-multimetro-medicion-autorrango-smart-1-rms/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/porta-celular-funda-smartphone-grande-hasta-160mm/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>01SIC23630</t>
+          <t>01USH00020</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PINZA PELACABLES 6.5" CABLES DE 0.75 A 6MM SICA (SICA)</t>
+          <t>Dobladora de caños 3/4" una palanca con resorte adaptador para caños de 5/8"</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>25754</v>
+        <v>117674</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/380200-pinza-pelacables-65-pcables-de-075-a-6mm-sica/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/dobladora-de-canios-34-una-palanca-con-resorte-adaptador-para-canios-de-58/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>01JAI00066</t>
+          <t>01SIC23630</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>EST7280 ESTAÑO EN CARRETE 60/40 0.8MM 250GR -JA- (JA)</t>
+          <t>PINZA PELACABLES 6.5" CABLES DE 0.75 A 6MM SICA (SICA)</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>42264</v>
+        <v>25754</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://electrocity.com.ar/productos/est7280-estanio-en-carrete-6040-08mm-250gr-ja/?openNotificationDialog=true</t>
+          <t>https://electrocity.com.ar/productos/380200-pinza-pelacables-65-pcables-de-075-a-6mm-sica/?openNotificationDialog=true</t>
         </is>
       </c>
     </row>
